--- a/historical_xlpe_demand.xlsx
+++ b/historical_xlpe_demand.xlsx
@@ -13,11 +13,11 @@
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision">
   <authors>
-    <author>tc={6a756a16-fdb7-4282-b75d-d32200baa93b}</author>
-    <author>tc={782ab845-6811-4608-b233-0e3e416543f9}</author>
+    <author>tc={40fe6a31-1f31-419e-bfa6-8900449ed13e}</author>
+    <author>tc={8dd46b68-e860-41a0-97fc-755da7cbce17}</author>
   </authors>
   <commentList>
-    <comment authorId="0" xr:uid="{6a756a16-fdb7-4282-b75d-d32200baa93b}" ref="G1">
+    <comment authorId="0" xr:uid="{40fe6a31-1f31-419e-bfa6-8900449ed13e}" ref="G1">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -26,7 +26,7 @@
 </t>
       </text>
     </comment>
-    <comment authorId="1" xr:uid="{782ab845-6811-4608-b233-0e3e416543f9}" ref="G1">
+    <comment authorId="1" xr:uid="{8dd46b68-e860-41a0-97fc-755da7cbce17}" ref="G1">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -51,7 +51,7 @@
     <t>Month</t>
   </si>
   <si>
-    <t>xlpe_demand_tons</t>
+    <t>xlpe_demand_Million_tons</t>
   </si>
   <si>
     <t>polyethylene_price</t>
@@ -1145,7 +1145,7 @@
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments">
-  <x18tc:person displayName="Salma Waleed El Marakby" id="{770254e2-a9e1-41d2-8a2a-69e0ade956ca}" providerId="google-sheets"/>
+  <x18tc:person displayName="Salma Waleed El Marakby" id="{57e9841c-36df-4301-b20c-55843a971ac9}" providerId="google-sheets"/>
 </x18tc:personList>
 </file>
 
@@ -1345,10 +1345,10 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <x18tc:ThreadedComments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:xltc2="http://schemas.microsoft.com/office/spreadsheetml/2020/threadedcomments2" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <x18tc:threadedComment ref="G1" dT="2026-01-14T03:16:27.00" personId="{770254e2-a9e1-41d2-8a2a-69e0ade956ca}" id="{782ab845-6811-4608-b233-0e3e416543f9}" done="0">
+  <x18tc:threadedComment ref="G1" dT="2026-01-14T03:16:27.00" personId="{57e9841c-36df-4301-b20c-55843a971ac9}" id="{8dd46b68-e860-41a0-97fc-755da7cbce17}" done="0">
     <x18tc:text xml:space="preserve">Middle East, North Africa, Afghanistan &amp; Pakistan</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="G1" dT="2026-01-14T03:16:06.00" personId="{770254e2-a9e1-41d2-8a2a-69e0ade956ca}" id="{6a756a16-fdb7-4282-b75d-d32200baa93b}" done="1">
+  <x18tc:threadedComment ref="G1" dT="2026-01-14T03:16:06.00" personId="{57e9841c-36df-4301-b20c-55843a971ac9}" id="{40fe6a31-1f31-419e-bfa6-8900449ed13e}" done="1">
     <x18tc:text xml:space="preserve">Middle East, North Africa, Afghanistan &amp; Pakistan</x18tc:text>
   </x18tc:threadedComment>
 </x18tc:ThreadedComments>
@@ -1412,7 +1412,7 @@
         <v>1.0</v>
       </c>
       <c r="D2" s="2">
-        <v>0.225</v>
+        <v>0.212892</v>
       </c>
       <c r="E2" s="2">
         <v>8588.4</v>
@@ -1442,7 +1442,7 @@
         <v>2.0</v>
       </c>
       <c r="D3" s="2">
-        <v>0.225</v>
+        <v>0.215021</v>
       </c>
       <c r="E3" s="2">
         <v>8447.0</v>
@@ -1472,7 +1472,7 @@
         <v>3.0</v>
       </c>
       <c r="D4" s="2">
-        <v>0.225</v>
+        <v>0.217171</v>
       </c>
       <c r="E4" s="2">
         <v>9277.8</v>
@@ -1502,7 +1502,7 @@
         <v>4.0</v>
       </c>
       <c r="D5" s="2">
-        <v>0.225</v>
+        <v>0.219343</v>
       </c>
       <c r="E5" s="2">
         <v>9101.0</v>
@@ -1532,7 +1532,7 @@
         <v>5.0</v>
       </c>
       <c r="D6" s="2">
-        <v>0.225</v>
+        <v>0.221536</v>
       </c>
       <c r="E6" s="2">
         <v>9330.0</v>
@@ -1562,7 +1562,7 @@
         <v>6.0</v>
       </c>
       <c r="D7" s="2">
-        <v>0.225</v>
+        <v>0.223751</v>
       </c>
       <c r="E7" s="2">
         <v>9878.8</v>
@@ -1592,7 +1592,7 @@
         <v>7.0</v>
       </c>
       <c r="D8" s="2">
-        <v>0.225</v>
+        <v>0.225989</v>
       </c>
       <c r="E8" s="2">
         <v>9048.0</v>
@@ -1622,7 +1622,7 @@
         <v>8.0</v>
       </c>
       <c r="D9" s="2">
-        <v>0.225</v>
+        <v>0.228249</v>
       </c>
       <c r="E9" s="2">
         <v>8995.0</v>
@@ -1652,7 +1652,7 @@
         <v>9.0</v>
       </c>
       <c r="D10" s="2">
-        <v>0.225</v>
+        <v>0.230531</v>
       </c>
       <c r="E10" s="2">
         <v>9366.2</v>
@@ -1682,7 +1682,7 @@
         <v>10.0</v>
       </c>
       <c r="D11" s="2">
-        <v>0.225</v>
+        <v>0.232837</v>
       </c>
       <c r="E11" s="2">
         <v>9136.4</v>
@@ -1712,7 +1712,7 @@
         <v>11.0</v>
       </c>
       <c r="D12" s="2">
-        <v>0.225</v>
+        <v>0.235165</v>
       </c>
       <c r="E12" s="2">
         <v>9984.9</v>
@@ -1742,7 +1742,7 @@
         <v>12.0</v>
       </c>
       <c r="D13" s="2">
-        <v>0.225</v>
+        <v>0.237517</v>
       </c>
       <c r="E13" s="2">
         <v>9207.1</v>
@@ -1772,7 +1772,7 @@
         <v>1.0</v>
       </c>
       <c r="D14" s="2">
-        <v>0.21666666666</v>
+        <v>0.205007</v>
       </c>
       <c r="E14" s="2">
         <v>9507.6</v>
@@ -1802,7 +1802,7 @@
         <v>2.0</v>
       </c>
       <c r="D15" s="2">
-        <v>0.21666666666</v>
+        <v>0.207057</v>
       </c>
       <c r="E15" s="2">
         <v>9596.0</v>
@@ -1832,7 +1832,7 @@
         <v>3.0</v>
       </c>
       <c r="D16" s="2">
-        <v>0.21666666666</v>
+        <v>0.209127</v>
       </c>
       <c r="E16" s="2">
         <v>9790.4</v>
@@ -1862,7 +1862,7 @@
         <v>4.0</v>
       </c>
       <c r="D17" s="2">
-        <v>0.21666666666</v>
+        <v>0.211219</v>
       </c>
       <c r="E17" s="2">
         <v>8977.3</v>
@@ -1892,7 +1892,7 @@
         <v>5.0</v>
       </c>
       <c r="D18" s="2">
-        <v>0.21666666666</v>
+        <v>0.213331</v>
       </c>
       <c r="E18" s="2">
         <v>9596.0</v>
@@ -1922,7 +1922,7 @@
         <v>6.0</v>
       </c>
       <c r="D19" s="2">
-        <v>0.21666666666</v>
+        <v>0.215464</v>
       </c>
       <c r="E19" s="2">
         <v>9684.3</v>
@@ -1952,7 +1952,7 @@
         <v>7.0</v>
       </c>
       <c r="D20" s="2">
-        <v>0.21666666666</v>
+        <v>0.217619</v>
       </c>
       <c r="E20" s="2">
         <v>10338.4</v>
@@ -1982,7 +1982,7 @@
         <v>8.0</v>
       </c>
       <c r="D21" s="2">
-        <v>0.21666666666</v>
+        <v>0.219795</v>
       </c>
       <c r="E21" s="2">
         <v>9118.7</v>
@@ -2012,7 +2012,7 @@
         <v>9.0</v>
       </c>
       <c r="D22" s="2">
-        <v>0.21666666666</v>
+        <v>0.221993</v>
       </c>
       <c r="E22" s="2">
         <v>9472.2</v>
@@ -2042,7 +2042,7 @@
         <v>10.0</v>
       </c>
       <c r="D23" s="2">
-        <v>0.21666666666</v>
+        <v>0.224213</v>
       </c>
       <c r="E23" s="2">
         <v>9436.9</v>
@@ -2072,7 +2072,7 @@
         <v>11.0</v>
       </c>
       <c r="D24" s="2">
-        <v>0.21666666666</v>
+        <v>0.226455</v>
       </c>
       <c r="E24" s="2">
         <v>9277.8</v>
@@ -2102,7 +2102,7 @@
         <v>12.0</v>
       </c>
       <c r="D25" s="2">
-        <v>0.21666666666</v>
+        <v>0.22872</v>
       </c>
       <c r="E25" s="2">
         <v>9419.2</v>
@@ -2132,7 +2132,7 @@
         <v>1.0</v>
       </c>
       <c r="D26" s="2">
-        <v>0.23333333333</v>
+        <v>0.220777</v>
       </c>
       <c r="E26" s="2">
         <v>9048.0</v>
@@ -2162,7 +2162,7 @@
         <v>2.0</v>
       </c>
       <c r="D27" s="2">
-        <v>0.23333333333</v>
+        <v>0.222984</v>
       </c>
       <c r="E27" s="2">
         <v>8995.0</v>
@@ -2192,7 +2192,7 @@
         <v>3.0</v>
       </c>
       <c r="D28" s="2">
-        <v>0.23333333333</v>
+        <v>0.225214</v>
       </c>
       <c r="E28" s="2">
         <v>8853.3</v>
@@ -2222,7 +2222,7 @@
         <v>4.0</v>
       </c>
       <c r="D29" s="2">
-        <v>0.23333333333</v>
+        <v>0.227466</v>
       </c>
       <c r="E29" s="2">
         <v>8447.0</v>
@@ -2252,7 +2252,7 @@
         <v>5.0</v>
       </c>
       <c r="D30" s="2">
-        <v>0.23333333333</v>
+        <v>0.229741</v>
       </c>
       <c r="E30" s="2">
         <v>8623.7</v>
@@ -2282,7 +2282,7 @@
         <v>6.0</v>
       </c>
       <c r="D31" s="2">
-        <v>0.23333333333</v>
+        <v>0.232038</v>
       </c>
       <c r="E31" s="2">
         <v>8287.9</v>
@@ -2312,7 +2312,7 @@
         <v>7.0</v>
       </c>
       <c r="D32" s="2">
-        <v>0.23333333333</v>
+        <v>0.234359</v>
       </c>
       <c r="E32" s="2">
         <v>7952.0</v>
@@ -2342,7 +2342,7 @@
         <v>8.0</v>
       </c>
       <c r="D33" s="2">
-        <v>0.23333333333</v>
+        <v>0.236702</v>
       </c>
       <c r="E33" s="2">
         <v>7722.2</v>
@@ -2372,7 +2372,7 @@
         <v>9.0</v>
       </c>
       <c r="D34" s="2">
-        <v>0.23333333333</v>
+        <v>0.239069</v>
       </c>
       <c r="E34" s="2">
         <v>7545.4</v>
@@ -2402,7 +2402,7 @@
         <v>10.0</v>
       </c>
       <c r="D35" s="2">
-        <v>0.23333333333</v>
+        <v>0.24146</v>
       </c>
       <c r="E35" s="2">
         <v>7121.2</v>
@@ -2432,7 +2432,7 @@
         <v>11.0</v>
       </c>
       <c r="D36" s="2">
-        <v>0.23333333333</v>
+        <v>0.243875</v>
       </c>
       <c r="E36" s="2">
         <v>7510.1</v>
@@ -2462,7 +2462,7 @@
         <v>12.0</v>
       </c>
       <c r="D37" s="2">
-        <v>0.23333333333</v>
+        <v>0.246313</v>
       </c>
       <c r="E37" s="2">
         <v>7298.0</v>
@@ -2492,7 +2492,7 @@
         <v>1.0</v>
       </c>
       <c r="D38" s="2">
-        <v>0.25</v>
+        <v>0.236546</v>
       </c>
       <c r="E38" s="2">
         <v>7191.9</v>
@@ -2522,7 +2522,7 @@
         <v>2.0</v>
       </c>
       <c r="D39" s="2">
-        <v>0.25</v>
+        <v>0.238912</v>
       </c>
       <c r="E39" s="2">
         <v>7244.9</v>
@@ -2552,7 +2552,7 @@
         <v>3.0</v>
       </c>
       <c r="D40" s="2">
-        <v>0.25</v>
+        <v>0.241301</v>
       </c>
       <c r="E40" s="2">
         <v>7050.5</v>
@@ -2582,7 +2582,7 @@
         <v>4.0</v>
       </c>
       <c r="D41" s="2">
-        <v>0.25</v>
+        <v>0.243714</v>
       </c>
       <c r="E41" s="2">
         <v>6042.9</v>
@@ -2612,7 +2612,7 @@
         <v>5.0</v>
       </c>
       <c r="D42" s="2">
-        <v>0.25</v>
+        <v>0.246151</v>
       </c>
       <c r="E42" s="2">
         <v>5714.6</v>
@@ -2642,7 +2642,7 @@
         <v>6.0</v>
       </c>
       <c r="D43" s="2">
-        <v>0.25</v>
+        <v>0.248613</v>
       </c>
       <c r="E43" s="2">
         <v>6295.4</v>
@@ -2672,7 +2672,7 @@
         <v>7.0</v>
       </c>
       <c r="D44" s="2">
-        <v>0.25</v>
+        <v>0.251099</v>
       </c>
       <c r="E44" s="2">
         <v>6800.5</v>
@@ -2702,7 +2702,7 @@
         <v>8.0</v>
       </c>
       <c r="D45" s="2">
-        <v>0.25</v>
+        <v>0.25361</v>
       </c>
       <c r="E45" s="2">
         <v>6824.8</v>
@@ -2732,7 +2732,7 @@
         <v>9.0</v>
       </c>
       <c r="D46" s="2">
-        <v>0.25</v>
+        <v>0.256146</v>
       </c>
       <c r="E46" s="2">
         <v>6914.1</v>
@@ -2762,7 +2762,7 @@
         <v>10.0</v>
       </c>
       <c r="D47" s="2">
-        <v>0.25</v>
+        <v>0.258707</v>
       </c>
       <c r="E47" s="2">
         <v>7318.2</v>
@@ -2792,7 +2792,7 @@
         <v>11.0</v>
       </c>
       <c r="D48" s="2">
-        <v>0.25</v>
+        <v>0.261294</v>
       </c>
       <c r="E48" s="2">
         <v>7179.3</v>
@@ -2822,7 +2822,7 @@
         <v>12.0</v>
       </c>
       <c r="D49" s="2">
-        <v>0.25</v>
+        <v>0.263907</v>
       </c>
       <c r="E49" s="2">
         <v>7255.1</v>
@@ -2852,7 +2852,7 @@
         <v>1.0</v>
       </c>
       <c r="D50" s="2">
-        <v>0.225</v>
+        <v>0.212892</v>
       </c>
       <c r="E50" s="2">
         <v>8075.8</v>
@@ -2882,7 +2882,7 @@
         <v>2.0</v>
       </c>
       <c r="D51" s="2">
-        <v>0.225</v>
+        <v>0.215021</v>
       </c>
       <c r="E51" s="2">
         <v>7646.5</v>
@@ -2912,7 +2912,7 @@
         <v>3.0</v>
       </c>
       <c r="D52" s="2">
-        <v>0.225</v>
+        <v>0.217171</v>
       </c>
       <c r="E52" s="2">
         <v>7949.5</v>
@@ -2942,7 +2942,7 @@
         <v>4.0</v>
       </c>
       <c r="D53" s="2">
-        <v>0.225</v>
+        <v>0.219343</v>
       </c>
       <c r="E53" s="2">
         <v>8820.7</v>
@@ -2972,7 +2972,7 @@
         <v>5.0</v>
       </c>
       <c r="D54" s="2">
-        <v>0.225</v>
+        <v>0.221536</v>
       </c>
       <c r="E54" s="2">
         <v>8707.1</v>
@@ -3002,7 +3002,7 @@
         <v>6.0</v>
       </c>
       <c r="D55" s="2">
-        <v>0.225</v>
+        <v>0.223751</v>
       </c>
       <c r="E55" s="2">
         <v>8416.7</v>
@@ -3032,7 +3032,7 @@
         <v>7.0</v>
       </c>
       <c r="D56" s="2">
-        <v>0.225</v>
+        <v>0.225989</v>
       </c>
       <c r="E56" s="2">
         <v>7633.8</v>
@@ -3062,7 +3062,7 @@
         <v>8.0</v>
       </c>
       <c r="D57" s="2">
-        <v>0.225</v>
+        <v>0.228249</v>
       </c>
       <c r="E57" s="2">
         <v>8075.8</v>
@@ -3092,7 +3092,7 @@
         <v>9.0</v>
       </c>
       <c r="D58" s="2">
-        <v>0.225</v>
+        <v>0.230531</v>
       </c>
       <c r="E58" s="2">
         <v>8252.5</v>
@@ -3122,7 +3122,7 @@
         <v>10.0</v>
       </c>
       <c r="D59" s="2">
-        <v>0.225</v>
+        <v>0.232837</v>
       </c>
       <c r="E59" s="2">
         <v>8378.8</v>
@@ -3152,7 +3152,7 @@
         <v>11.0</v>
       </c>
       <c r="D60" s="2">
-        <v>0.225</v>
+        <v>0.235165</v>
       </c>
       <c r="E60" s="2">
         <v>9590.9</v>
@@ -3182,7 +3182,7 @@
         <v>12.0</v>
       </c>
       <c r="D61" s="2">
-        <v>0.225</v>
+        <v>0.237517</v>
       </c>
       <c r="E61" s="2">
         <v>8795.5</v>
@@ -3212,7 +3212,7 @@
         <v>1.0</v>
       </c>
       <c r="D62" s="2">
-        <v>0.23333333333</v>
+        <v>0.220777</v>
       </c>
       <c r="E62" s="2">
         <v>8505.0</v>
@@ -3242,7 +3242,7 @@
         <v>2.0</v>
       </c>
       <c r="D63" s="2">
-        <v>0.23333333333</v>
+        <v>0.222984</v>
       </c>
       <c r="E63" s="2">
         <v>8593.4</v>
@@ -3272,7 +3272,7 @@
         <v>3.0</v>
       </c>
       <c r="D64" s="2">
-        <v>0.23333333333</v>
+        <v>0.225214</v>
       </c>
       <c r="E64" s="2">
         <v>9060.6</v>
@@ -3302,7 +3302,7 @@
         <v>4.0</v>
       </c>
       <c r="D65" s="2">
-        <v>0.23333333333</v>
+        <v>0.227466</v>
       </c>
       <c r="E65" s="2">
         <v>9035.4</v>
@@ -3332,7 +3332,7 @@
         <v>5.0</v>
       </c>
       <c r="D66" s="2">
-        <v>0.23333333333</v>
+        <v>0.229741</v>
       </c>
       <c r="E66" s="2">
         <v>9048.0</v>
@@ -3362,7 +3362,7 @@
         <v>6.0</v>
       </c>
       <c r="D67" s="2">
-        <v>0.23333333333</v>
+        <v>0.232038</v>
       </c>
       <c r="E67" s="2">
         <v>8820.7</v>
@@ -3392,7 +3392,7 @@
         <v>7.0</v>
       </c>
       <c r="D68" s="2">
-        <v>0.23333333333</v>
+        <v>0.234359</v>
       </c>
       <c r="E68" s="2">
         <v>8984.9</v>
@@ -3422,7 +3422,7 @@
         <v>8.0</v>
       </c>
       <c r="D69" s="2">
-        <v>0.23333333333</v>
+        <v>0.236702</v>
       </c>
       <c r="E69" s="2">
         <v>8366.2</v>
@@ -3452,7 +3452,7 @@
         <v>9.0</v>
       </c>
       <c r="D70" s="2">
-        <v>0.23333333333</v>
+        <v>0.239069</v>
       </c>
       <c r="E70" s="2">
         <v>8063.1</v>
@@ -3482,7 +3482,7 @@
         <v>10.0</v>
       </c>
       <c r="D71" s="2">
-        <v>0.23333333333</v>
+        <v>0.24146</v>
       </c>
       <c r="E71" s="2">
         <v>7936.9</v>
@@ -3512,7 +3512,7 @@
         <v>11.0</v>
       </c>
       <c r="D72" s="2">
-        <v>0.23333333333</v>
+        <v>0.243875</v>
       </c>
       <c r="E72" s="2">
         <v>8164.1</v>
@@ -3542,7 +3542,7 @@
         <v>12.0</v>
       </c>
       <c r="D73" s="2">
-        <v>0.23333333333</v>
+        <v>0.246313</v>
       </c>
       <c r="E73" s="2">
         <v>7962.1</v>
@@ -3572,7 +3572,7 @@
         <v>1.0</v>
       </c>
       <c r="D74" s="2">
-        <v>0.26666666666</v>
+        <v>0.252316</v>
       </c>
       <c r="E74" s="2">
         <v>8159.1</v>
@@ -3602,7 +3602,7 @@
         <v>2.0</v>
       </c>
       <c r="D75" s="2">
-        <v>0.26666666666</v>
+        <v>0.254839</v>
       </c>
       <c r="E75" s="2">
         <v>8075.8</v>
@@ -3632,7 +3632,7 @@
         <v>3.0</v>
       </c>
       <c r="D76" s="2">
-        <v>0.26666666666</v>
+        <v>0.257388</v>
       </c>
       <c r="E76" s="2">
         <v>8234.9</v>
@@ -3662,7 +3662,7 @@
         <v>4.0</v>
       </c>
       <c r="D77" s="2">
-        <v>0.26666666666</v>
+        <v>0.259962</v>
       </c>
       <c r="E77" s="2">
         <v>8356.1</v>
@@ -3692,7 +3692,7 @@
         <v>5.0</v>
       </c>
       <c r="D78" s="2">
-        <v>0.26666666666</v>
+        <v>0.262561</v>
       </c>
       <c r="E78" s="2">
         <v>8151.5</v>
@@ -3722,7 +3722,7 @@
         <v>6.0</v>
       </c>
       <c r="D79" s="2">
-        <v>0.26666666666</v>
+        <v>0.265187</v>
       </c>
       <c r="E79" s="2">
         <v>8272.7</v>
@@ -3752,7 +3752,7 @@
         <v>7.0</v>
       </c>
       <c r="D80" s="2">
-        <v>0.26666666666</v>
+        <v>0.267839</v>
       </c>
       <c r="E80" s="2">
         <v>7757.6</v>
@@ -3782,7 +3782,7 @@
         <v>8.0</v>
       </c>
       <c r="D81" s="2">
-        <v>0.26666666666</v>
+        <v>0.270517</v>
       </c>
       <c r="E81" s="2">
         <v>7992.4</v>
@@ -3812,7 +3812,7 @@
         <v>9.0</v>
       </c>
       <c r="D82" s="2">
-        <v>0.26666666666</v>
+        <v>0.273222</v>
       </c>
       <c r="E82" s="2">
         <v>8212.1</v>
@@ -3842,7 +3842,7 @@
         <v>10.0</v>
       </c>
       <c r="D83" s="2">
-        <v>0.26666666666</v>
+        <v>0.275954</v>
       </c>
       <c r="E83" s="2">
         <v>8386.4</v>
@@ -3872,7 +3872,7 @@
         <v>11.0</v>
       </c>
       <c r="D84" s="2">
-        <v>0.26666666666</v>
+        <v>0.278714</v>
       </c>
       <c r="E84" s="2">
         <v>8265.1</v>
@@ -3902,7 +3902,7 @@
         <v>12.0</v>
       </c>
       <c r="D85" s="2">
-        <v>0.26666666666</v>
+        <v>0.281501</v>
       </c>
       <c r="E85" s="2">
         <v>8075.8</v>
@@ -3932,7 +3932,7 @@
         <v>1.0</v>
       </c>
       <c r="D86" s="2">
-        <v>0.25833333333</v>
+        <v>0.244431</v>
       </c>
       <c r="E86" s="2">
         <v>7875.0</v>
@@ -3962,7 +3962,7 @@
         <v>2.0</v>
       </c>
       <c r="D87" s="2">
-        <v>0.25833333333</v>
+        <v>0.246876</v>
       </c>
       <c r="E87" s="2">
         <v>8181.8</v>
@@ -3992,7 +3992,7 @@
         <v>3.0</v>
       </c>
       <c r="D88" s="2">
-        <v>0.25833333333</v>
+        <v>0.249344</v>
       </c>
       <c r="E88" s="2">
         <v>8136.4</v>
@@ -4022,7 +4022,7 @@
         <v>4.0</v>
       </c>
       <c r="D89" s="2">
-        <v>0.25833333333</v>
+        <v>0.251838</v>
       </c>
       <c r="E89" s="2">
         <v>8096.6</v>
@@ -4052,7 +4052,7 @@
         <v>5.0</v>
       </c>
       <c r="D90" s="2">
-        <v>0.25833333333</v>
+        <v>0.254356</v>
       </c>
       <c r="E90" s="2">
         <v>8187.5</v>
@@ -4082,7 +4082,7 @@
         <v>6.0</v>
       </c>
       <c r="D91" s="2">
-        <v>0.25833333333</v>
+        <v>0.2569</v>
       </c>
       <c r="E91" s="2">
         <v>8460.2</v>
@@ -4112,7 +4112,7 @@
         <v>7.0</v>
       </c>
       <c r="D92" s="2">
-        <v>0.25833333333</v>
+        <v>0.259469</v>
       </c>
       <c r="E92" s="2">
         <v>8517.0</v>
@@ -4142,7 +4142,7 @@
         <v>8.0</v>
       </c>
       <c r="D93" s="2">
-        <v>0.25833333333</v>
+        <v>0.262063</v>
       </c>
       <c r="E93" s="2">
         <v>8483.0</v>
@@ -4172,7 +4172,7 @@
         <v>9.0</v>
       </c>
       <c r="D94" s="2">
-        <v>0.25833333333</v>
+        <v>0.264684</v>
       </c>
       <c r="E94" s="2">
         <v>8295.5</v>
@@ -4202,7 +4202,7 @@
         <v>10.0</v>
       </c>
       <c r="D95" s="2">
-        <v>0.25833333333</v>
+        <v>0.267331</v>
       </c>
       <c r="E95" s="2">
         <v>8193.2</v>
@@ -4232,7 +4232,7 @@
         <v>11.0</v>
       </c>
       <c r="D96" s="2">
-        <v>0.25833333333</v>
+        <v>0.270004</v>
       </c>
       <c r="E96" s="2">
         <v>8136.4</v>
@@ -4262,7 +4262,7 @@
         <v>12.0</v>
       </c>
       <c r="D97" s="2">
-        <v>0.25833333333</v>
+        <v>0.272704</v>
       </c>
       <c r="E97" s="2">
         <v>8238.6</v>
@@ -4292,7 +4292,7 @@
         <v>1.0</v>
       </c>
       <c r="D98" s="2">
-        <v>0.26666666666</v>
+        <v>0.252316</v>
       </c>
       <c r="E98" s="2">
         <v>8642.0</v>
@@ -4322,7 +4322,7 @@
         <v>2.0</v>
       </c>
       <c r="D99" s="2">
-        <v>0.26666666666</v>
+        <v>0.254839</v>
       </c>
       <c r="E99" s="2">
         <v>8545.5</v>
@@ -4352,7 +4352,7 @@
         <v>3.0</v>
       </c>
       <c r="D100" s="2">
-        <v>0.26666666666</v>
+        <v>0.257388</v>
       </c>
       <c r="E100" s="2">
         <v>7846.6</v>
@@ -4382,7 +4382,7 @@
         <v>4.0</v>
       </c>
       <c r="D101" s="2">
-        <v>0.26666666666</v>
+        <v>0.259962</v>
       </c>
       <c r="E101" s="2">
         <v>8113.6</v>
@@ -4412,7 +4412,7 @@
         <v>5.0</v>
       </c>
       <c r="D102" s="2">
-        <v>0.26666666666</v>
+        <v>0.262561</v>
       </c>
       <c r="E102" s="2">
         <v>7738.6</v>
@@ -4442,7 +4442,7 @@
         <v>6.0</v>
       </c>
       <c r="D103" s="2">
-        <v>0.26666666666</v>
+        <v>0.265187</v>
       </c>
       <c r="E103" s="2">
         <v>7318.2</v>
@@ -4472,7 +4472,7 @@
         <v>7.0</v>
       </c>
       <c r="D104" s="2">
-        <v>0.26666666666</v>
+        <v>0.267839</v>
       </c>
       <c r="E104" s="2">
         <v>6982.9</v>
@@ -4502,7 +4502,7 @@
         <v>8.0</v>
       </c>
       <c r="D105" s="2">
-        <v>0.26666666666</v>
+        <v>0.270517</v>
       </c>
       <c r="E105" s="2">
         <v>7335.2</v>
@@ -4532,7 +4532,7 @@
         <v>9.0</v>
       </c>
       <c r="D106" s="2">
-        <v>0.26666666666</v>
+        <v>0.273222</v>
       </c>
       <c r="E106" s="2">
         <v>7343.4</v>
@@ -4562,7 +4562,7 @@
         <v>10.0</v>
       </c>
       <c r="D107" s="2">
-        <v>0.26666666666</v>
+        <v>0.275954</v>
       </c>
       <c r="E107" s="2">
         <v>7299.2</v>
@@ -4592,7 +4592,7 @@
         <v>11.0</v>
       </c>
       <c r="D108" s="2">
-        <v>0.26666666666</v>
+        <v>0.278714</v>
       </c>
       <c r="E108" s="2">
         <v>7078.3</v>
@@ -4622,7 +4622,7 @@
         <v>12.0</v>
       </c>
       <c r="D109" s="2">
-        <v>0.26666666666</v>
+        <v>0.281501</v>
       </c>
       <c r="E109" s="2">
         <v>6928.0</v>
@@ -4652,7 +4652,7 @@
         <v>1.0</v>
       </c>
       <c r="D110" s="2">
-        <v>0.25</v>
+        <v>0.236546</v>
       </c>
       <c r="E110" s="2">
         <v>6751.3</v>
@@ -4682,7 +4682,7 @@
         <v>2.0</v>
       </c>
       <c r="D111" s="2">
-        <v>0.25</v>
+        <v>0.238912</v>
       </c>
       <c r="E111" s="2">
         <v>6300.5</v>
@@ -4712,7 +4712,7 @@
         <v>3.0</v>
       </c>
       <c r="D112" s="2">
-        <v>0.25</v>
+        <v>0.241301</v>
       </c>
       <c r="E112" s="2">
         <v>6800.5</v>
@@ -4742,7 +4742,7 @@
         <v>4.0</v>
       </c>
       <c r="D113" s="2">
-        <v>0.25</v>
+        <v>0.243714</v>
       </c>
       <c r="E113" s="2">
         <v>7179.3</v>
@@ -4772,7 +4772,7 @@
         <v>5.0</v>
       </c>
       <c r="D114" s="2">
-        <v>0.25</v>
+        <v>0.246151</v>
       </c>
       <c r="E114" s="2">
         <v>7545.4</v>
@@ -4802,7 +4802,7 @@
         <v>6.0</v>
       </c>
       <c r="D115" s="2">
-        <v>0.25</v>
+        <v>0.248613</v>
       </c>
       <c r="E115" s="2">
         <v>7952.0</v>
@@ -4832,7 +4832,7 @@
         <v>7.0</v>
       </c>
       <c r="D116" s="2">
-        <v>0.25</v>
+        <v>0.251099</v>
       </c>
       <c r="E116" s="2">
         <v>8252.5</v>
@@ -4862,7 +4862,7 @@
         <v>8.0</v>
       </c>
       <c r="D117" s="2">
-        <v>0.25</v>
+        <v>0.25361</v>
       </c>
       <c r="E117" s="2">
         <v>8416.7</v>
@@ -4892,7 +4892,7 @@
         <v>9.0</v>
       </c>
       <c r="D118" s="2">
-        <v>0.25</v>
+        <v>0.256146</v>
       </c>
       <c r="E118" s="2">
         <v>8707.1</v>
@@ -4922,7 +4922,7 @@
         <v>10.0</v>
       </c>
       <c r="D119" s="2">
-        <v>0.25</v>
+        <v>0.258707</v>
       </c>
       <c r="E119" s="2">
         <v>8984.9</v>
@@ -4952,7 +4952,7 @@
         <v>11.0</v>
       </c>
       <c r="D120" s="2">
-        <v>0.25</v>
+        <v>0.261294</v>
       </c>
       <c r="E120" s="2">
         <v>9277.8</v>
@@ -4982,7 +4982,7 @@
         <v>12.0</v>
       </c>
       <c r="D121" s="2">
-        <v>0.25</v>
+        <v>0.263907</v>
       </c>
       <c r="E121" s="2">
         <v>9590.9</v>
@@ -5012,7 +5012,7 @@
         <v>1.0</v>
       </c>
       <c r="D122" s="2">
-        <v>0.24166666666</v>
+        <v>0.228661</v>
       </c>
       <c r="E122" s="2">
         <v>9878.8</v>
@@ -5042,7 +5042,7 @@
         <v>2.0</v>
       </c>
       <c r="D123" s="2">
-        <v>0.24166666666</v>
+        <v>0.230948</v>
       </c>
       <c r="E123" s="2">
         <v>9984.9</v>
@@ -5072,7 +5072,7 @@
         <v>3.0</v>
       </c>
       <c r="D124" s="2">
-        <v>0.24166666666</v>
+        <v>0.233258</v>
       </c>
       <c r="E124" s="2">
         <v>10338.4</v>
@@ -5102,7 +5102,7 @@
         <v>4.0</v>
       </c>
       <c r="D125" s="2">
-        <v>0.24166666666</v>
+        <v>0.23559</v>
       </c>
       <c r="E125" s="2">
         <v>9684.3</v>
@@ -5132,7 +5132,7 @@
         <v>5.0</v>
       </c>
       <c r="D126" s="2">
-        <v>0.24166666666</v>
+        <v>0.237946</v>
       </c>
       <c r="E126" s="2">
         <v>9596.0</v>
@@ -5162,7 +5162,7 @@
         <v>6.0</v>
       </c>
       <c r="D127" s="2">
-        <v>0.24166666666</v>
+        <v>0.240326</v>
       </c>
       <c r="E127" s="2">
         <v>9472.2</v>
@@ -5192,7 +5192,7 @@
         <v>7.0</v>
       </c>
       <c r="D128" s="2">
-        <v>0.24166666666</v>
+        <v>0.242729</v>
       </c>
       <c r="E128" s="2">
         <v>9366.2</v>
@@ -5222,7 +5222,7 @@
         <v>8.0</v>
       </c>
       <c r="D129" s="2">
-        <v>0.24166666666</v>
+        <v>0.245156</v>
       </c>
       <c r="E129" s="2">
         <v>9207.1</v>
@@ -5252,7 +5252,7 @@
         <v>9.0</v>
       </c>
       <c r="D130" s="2">
-        <v>0.24166666666</v>
+        <v>0.247608</v>
       </c>
       <c r="E130" s="2">
         <v>9060.6</v>
@@ -5282,7 +5282,7 @@
         <v>10.0</v>
       </c>
       <c r="D131" s="2">
-        <v>0.24166666666</v>
+        <v>0.250084</v>
       </c>
       <c r="E131" s="2">
         <v>9035.4</v>
@@ -5312,7 +5312,7 @@
         <v>11.0</v>
       </c>
       <c r="D132" s="2">
-        <v>0.24166666666</v>
+        <v>0.252585</v>
       </c>
       <c r="E132" s="2">
         <v>8984.9</v>
@@ -5342,7 +5342,7 @@
         <v>12.0</v>
       </c>
       <c r="D133" s="2">
-        <v>0.24166666666</v>
+        <v>0.25511</v>
       </c>
       <c r="E133" s="2">
         <v>8820.7</v>
@@ -5372,7 +5372,7 @@
         <v>1.0</v>
       </c>
       <c r="D134" s="2">
-        <v>0.24166666666</v>
+        <v>0.228661</v>
       </c>
       <c r="E134" s="2">
         <v>8707.1</v>
@@ -5402,7 +5402,7 @@
         <v>2.0</v>
       </c>
       <c r="D135" s="2">
-        <v>0.24166666666</v>
+        <v>0.230948</v>
       </c>
       <c r="E135" s="2">
         <v>8593.4</v>
@@ -5432,7 +5432,7 @@
         <v>3.0</v>
       </c>
       <c r="D136" s="2">
-        <v>0.24166666666</v>
+        <v>0.233258</v>
       </c>
       <c r="E136" s="2">
         <v>8505.0</v>
@@ -5462,7 +5462,7 @@
         <v>4.0</v>
       </c>
       <c r="D137" s="2">
-        <v>0.24166666666</v>
+        <v>0.23559</v>
       </c>
       <c r="E137" s="2">
         <v>8460.2</v>
@@ -5492,7 +5492,7 @@
         <v>5.0</v>
       </c>
       <c r="D138" s="2">
-        <v>0.24166666666</v>
+        <v>0.237946</v>
       </c>
       <c r="E138" s="2">
         <v>8416.7</v>
@@ -5522,7 +5522,7 @@
         <v>6.0</v>
       </c>
       <c r="D139" s="2">
-        <v>0.24166666666</v>
+        <v>0.240326</v>
       </c>
       <c r="E139" s="2">
         <v>8378.8</v>
@@ -5552,7 +5552,7 @@
         <v>7.0</v>
       </c>
       <c r="D140" s="2">
-        <v>0.24166666666</v>
+        <v>0.242729</v>
       </c>
       <c r="E140" s="2">
         <v>8366.2</v>
@@ -5582,7 +5582,7 @@
         <v>8.0</v>
       </c>
       <c r="D141" s="2">
-        <v>0.24166666666</v>
+        <v>0.245156</v>
       </c>
       <c r="E141" s="2">
         <v>8356.1</v>
@@ -5612,7 +5612,7 @@
         <v>9.0</v>
       </c>
       <c r="D142" s="2">
-        <v>0.24166666666</v>
+        <v>0.247608</v>
       </c>
       <c r="E142" s="2">
         <v>8295.5</v>
@@ -5642,7 +5642,7 @@
         <v>10.0</v>
       </c>
       <c r="D143" s="2">
-        <v>0.24166666666</v>
+        <v>0.250084</v>
       </c>
       <c r="E143" s="2">
         <v>8272.7</v>
@@ -5672,7 +5672,7 @@
         <v>11.0</v>
       </c>
       <c r="D144" s="2">
-        <v>0.24166666666</v>
+        <v>0.252585</v>
       </c>
       <c r="E144" s="2">
         <v>8265.1</v>
@@ -5702,7 +5702,7 @@
         <v>12.0</v>
       </c>
       <c r="D145" s="2">
-        <v>0.24166666666</v>
+        <v>0.25511</v>
       </c>
       <c r="E145" s="2">
         <v>8238.6</v>
@@ -5732,7 +5732,7 @@
         <v>1.0</v>
       </c>
       <c r="D146" s="2">
-        <v>0.23333333333</v>
+        <v>0.220777</v>
       </c>
       <c r="E146" s="2">
         <v>8212.1</v>
@@ -5762,7 +5762,7 @@
         <v>2.0</v>
       </c>
       <c r="D147" s="2">
-        <v>0.23333333333</v>
+        <v>0.222984</v>
       </c>
       <c r="E147" s="2">
         <v>8193.2</v>
@@ -5792,7 +5792,7 @@
         <v>3.0</v>
       </c>
       <c r="D148" s="2">
-        <v>0.23333333333</v>
+        <v>0.225214</v>
       </c>
       <c r="E148" s="2">
         <v>8187.5</v>
@@ -5822,7 +5822,7 @@
         <v>4.0</v>
       </c>
       <c r="D149" s="2">
-        <v>0.23333333333</v>
+        <v>0.227466</v>
       </c>
       <c r="E149" s="2">
         <v>8181.8</v>
@@ -5852,7 +5852,7 @@
         <v>5.0</v>
       </c>
       <c r="D150" s="2">
-        <v>0.23333333333</v>
+        <v>0.229741</v>
       </c>
       <c r="E150" s="2">
         <v>8164.1</v>
@@ -5882,7 +5882,7 @@
         <v>6.0</v>
       </c>
       <c r="D151" s="2">
-        <v>0.23333333333</v>
+        <v>0.232038</v>
       </c>
       <c r="E151" s="2">
         <v>8159.1</v>
@@ -5912,7 +5912,7 @@
         <v>7.0</v>
       </c>
       <c r="D152" s="2">
-        <v>0.23333333333</v>
+        <v>0.234359</v>
       </c>
       <c r="E152" s="2">
         <v>8151.5</v>
@@ -5942,7 +5942,7 @@
         <v>8.0</v>
       </c>
       <c r="D153" s="2">
-        <v>0.23333333333</v>
+        <v>0.236702</v>
       </c>
       <c r="E153" s="2">
         <v>8136.4</v>
@@ -5972,7 +5972,7 @@
         <v>9.0</v>
       </c>
       <c r="D154" s="2">
-        <v>0.23333333333</v>
+        <v>0.239069</v>
       </c>
       <c r="E154" s="2">
         <v>8113.6</v>
@@ -6002,7 +6002,7 @@
         <v>10.0</v>
       </c>
       <c r="D155" s="2">
-        <v>0.23333333333</v>
+        <v>0.24146</v>
       </c>
       <c r="E155" s="2">
         <v>8096.6</v>
@@ -6032,7 +6032,7 @@
         <v>11.0</v>
       </c>
       <c r="D156" s="2">
-        <v>0.23333333333</v>
+        <v>0.243875</v>
       </c>
       <c r="E156" s="2">
         <v>8075.8</v>
@@ -6062,7 +6062,7 @@
         <v>12.0</v>
       </c>
       <c r="D157" s="2">
-        <v>0.23333333333</v>
+        <v>0.246313</v>
       </c>
       <c r="E157" s="2">
         <v>8063.1</v>
@@ -6092,7 +6092,7 @@
         <v>1.0</v>
       </c>
       <c r="D158" s="2">
-        <v>0.275</v>
+        <v>0.260201</v>
       </c>
       <c r="E158" s="2">
         <v>8075.8</v>
@@ -6122,7 +6122,7 @@
         <v>2.0</v>
       </c>
       <c r="D159" s="2">
-        <v>0.275</v>
+        <v>0.262803</v>
       </c>
       <c r="E159" s="2">
         <v>8136.4</v>
@@ -6152,7 +6152,7 @@
         <v>3.0</v>
       </c>
       <c r="D160" s="2">
-        <v>0.275</v>
+        <v>0.265431</v>
       </c>
       <c r="E160" s="2">
         <v>8181.8</v>
@@ -6182,7 +6182,7 @@
         <v>4.0</v>
       </c>
       <c r="D161" s="2">
-        <v>0.275</v>
+        <v>0.268085</v>
       </c>
       <c r="E161" s="2">
         <v>8234.9</v>
@@ -6212,7 +6212,7 @@
         <v>5.0</v>
       </c>
       <c r="D162" s="2">
-        <v>0.275</v>
+        <v>0.270766</v>
       </c>
       <c r="E162" s="2">
         <v>8272.7</v>
@@ -6242,7 +6242,7 @@
         <v>6.0</v>
       </c>
       <c r="D163" s="2">
-        <v>0.275</v>
+        <v>0.273474</v>
       </c>
       <c r="E163" s="2">
         <v>8295.5</v>
@@ -6272,7 +6272,7 @@
         <v>7.0</v>
       </c>
       <c r="D164" s="2">
-        <v>0.275</v>
+        <v>0.276209</v>
       </c>
       <c r="E164" s="2">
         <v>8356.1</v>
@@ -6302,7 +6302,7 @@
         <v>8.0</v>
       </c>
       <c r="D165" s="2">
-        <v>0.275</v>
+        <v>0.278971</v>
       </c>
       <c r="E165" s="2">
         <v>8386.4</v>
@@ -6332,7 +6332,7 @@
         <v>9.0</v>
       </c>
       <c r="D166" s="2">
-        <v>0.275</v>
+        <v>0.28176</v>
       </c>
       <c r="E166" s="2">
         <v>8416.7</v>
@@ -6362,7 +6362,7 @@
         <v>10.0</v>
       </c>
       <c r="D167" s="2">
-        <v>0.275</v>
+        <v>0.284578</v>
       </c>
       <c r="E167" s="2">
         <v>8460.2</v>
@@ -6392,7 +6392,7 @@
         <v>11.0</v>
       </c>
       <c r="D168" s="2">
-        <v>0.275</v>
+        <v>0.287424</v>
       </c>
       <c r="E168" s="2">
         <v>8483.0</v>
@@ -6422,7 +6422,7 @@
         <v>12.0</v>
       </c>
       <c r="D169" s="2">
-        <v>0.275</v>
+        <v>0.290298</v>
       </c>
       <c r="E169" s="2">
         <v>8517.0</v>
@@ -6452,7 +6452,7 @@
         <v>1.0</v>
       </c>
       <c r="D170" s="2">
-        <v>0.275</v>
+        <v>0.260201</v>
       </c>
       <c r="E170" s="2">
         <v>8545.5</v>
@@ -6482,7 +6482,7 @@
         <v>2.0</v>
       </c>
       <c r="D171" s="2">
-        <v>0.275</v>
+        <v>0.262803</v>
       </c>
       <c r="E171" s="2">
         <v>8593.4</v>
@@ -6512,7 +6512,7 @@
         <v>3.0</v>
       </c>
       <c r="D172" s="2">
-        <v>0.275</v>
+        <v>0.265431</v>
       </c>
       <c r="E172" s="2">
         <v>8642.0</v>
@@ -6542,7 +6542,7 @@
         <v>4.0</v>
       </c>
       <c r="D173" s="2">
-        <v>0.275</v>
+        <v>0.268085</v>
       </c>
       <c r="E173" s="2">
         <v>8707.1</v>
@@ -6572,7 +6572,7 @@
         <v>5.0</v>
       </c>
       <c r="D174" s="2">
-        <v>0.275</v>
+        <v>0.270766</v>
       </c>
       <c r="E174" s="2">
         <v>8795.5</v>
@@ -6602,7 +6602,7 @@
         <v>6.0</v>
       </c>
       <c r="D175" s="2">
-        <v>0.275</v>
+        <v>0.273474</v>
       </c>
       <c r="E175" s="2">
         <v>8820.7</v>
@@ -6632,7 +6632,7 @@
         <v>7.0</v>
       </c>
       <c r="D176" s="2">
-        <v>0.275</v>
+        <v>0.276209</v>
       </c>
       <c r="E176" s="2">
         <v>8853.3</v>
@@ -6662,7 +6662,7 @@
         <v>8.0</v>
       </c>
       <c r="D177" s="2">
-        <v>0.275</v>
+        <v>0.278971</v>
       </c>
       <c r="E177" s="2">
         <v>8977.3</v>
@@ -6692,7 +6692,7 @@
         <v>9.0</v>
       </c>
       <c r="D178" s="2">
-        <v>0.275</v>
+        <v>0.28176</v>
       </c>
       <c r="E178" s="2">
         <v>8984.9</v>
@@ -6722,7 +6722,7 @@
         <v>10.0</v>
       </c>
       <c r="D179" s="2">
-        <v>0.275</v>
+        <v>0.284578</v>
       </c>
       <c r="E179" s="2">
         <v>8995.0</v>
@@ -6752,7 +6752,7 @@
         <v>11.0</v>
       </c>
       <c r="D180" s="2">
-        <v>0.275</v>
+        <v>0.287424</v>
       </c>
       <c r="E180" s="2">
         <v>9035.4</v>
@@ -6782,7 +6782,7 @@
         <v>12.0</v>
       </c>
       <c r="D181" s="2">
-        <v>0.275</v>
+        <v>0.290298</v>
       </c>
       <c r="E181" s="2">
         <v>9048.0</v>
@@ -6812,7 +6812,7 @@
         <v>1.0</v>
       </c>
       <c r="D182" s="2">
-        <v>0.26666666666</v>
+        <v>0.252316</v>
       </c>
       <c r="E182" s="2">
         <v>9060.6</v>
@@ -6842,7 +6842,7 @@
         <v>2.0</v>
       </c>
       <c r="D183" s="2">
-        <v>0.26666666666</v>
+        <v>0.254839</v>
       </c>
       <c r="E183" s="2">
         <v>9118.7</v>
@@ -6872,7 +6872,7 @@
         <v>3.0</v>
       </c>
       <c r="D184" s="2">
-        <v>0.26666666666</v>
+        <v>0.257388</v>
       </c>
       <c r="E184" s="2">
         <v>9136.4</v>
@@ -6902,7 +6902,7 @@
         <v>4.0</v>
       </c>
       <c r="D185" s="2">
-        <v>0.26666666666</v>
+        <v>0.259962</v>
       </c>
       <c r="E185" s="2">
         <v>9207.1</v>
@@ -6932,7 +6932,7 @@
         <v>5.0</v>
       </c>
       <c r="D186" s="2">
-        <v>0.26666666666</v>
+        <v>0.262561</v>
       </c>
       <c r="E186" s="2">
         <v>9277.8</v>
@@ -6962,7 +6962,7 @@
         <v>6.0</v>
       </c>
       <c r="D187" s="2">
-        <v>0.26666666666</v>
+        <v>0.265187</v>
       </c>
       <c r="E187" s="2">
         <v>9330.0</v>
@@ -6992,7 +6992,7 @@
         <v>7.0</v>
       </c>
       <c r="D188" s="2">
-        <v>0.26666666666</v>
+        <v>0.267839</v>
       </c>
       <c r="E188" s="2">
         <v>9366.2</v>
@@ -7022,7 +7022,7 @@
         <v>8.0</v>
       </c>
       <c r="D189" s="2">
-        <v>0.26666666666</v>
+        <v>0.270517</v>
       </c>
       <c r="E189" s="2">
         <v>9419.2</v>
@@ -7052,7 +7052,7 @@
         <v>9.0</v>
       </c>
       <c r="D190" s="2">
-        <v>0.26666666666</v>
+        <v>0.273222</v>
       </c>
       <c r="E190" s="2">
         <v>9436.9</v>
@@ -7082,7 +7082,7 @@
         <v>10.0</v>
       </c>
       <c r="D191" s="2">
-        <v>0.26666666666</v>
+        <v>0.275954</v>
       </c>
       <c r="E191" s="2">
         <v>9472.2</v>
@@ -7112,7 +7112,7 @@
         <v>11.0</v>
       </c>
       <c r="D192" s="2">
-        <v>0.26666666666</v>
+        <v>0.278714</v>
       </c>
       <c r="E192" s="2">
         <v>9507.6</v>
@@ -7142,7 +7142,7 @@
         <v>12.0</v>
       </c>
       <c r="D193" s="2">
-        <v>0.26666666666</v>
+        <v>0.281501</v>
       </c>
       <c r="E193" s="2">
         <v>9596.0</v>
@@ -7172,7 +7172,7 @@
         <v>1.0</v>
       </c>
       <c r="D194" s="2">
-        <v>0.25833333333</v>
+        <v>0.244431</v>
       </c>
       <c r="E194" s="12">
         <v>8553.0</v>
@@ -7202,7 +7202,7 @@
         <v>2.0</v>
       </c>
       <c r="D195" s="2">
-        <v>0.25833333333</v>
+        <v>0.246876</v>
       </c>
       <c r="E195" s="12">
         <v>8570.7</v>
@@ -7232,7 +7232,7 @@
         <v>3.0</v>
       </c>
       <c r="D196" s="2">
-        <v>0.25833333333</v>
+        <v>0.249344</v>
       </c>
       <c r="E196" s="12">
         <v>10161.1</v>
@@ -7262,7 +7262,7 @@
         <v>4.0</v>
       </c>
       <c r="D197" s="2">
-        <v>0.25833333333</v>
+        <v>0.251838</v>
       </c>
       <c r="E197" s="12">
         <v>8623.7</v>
@@ -7292,7 +7292,7 @@
         <v>5.0</v>
       </c>
       <c r="D198" s="2">
-        <v>0.25833333333</v>
+        <v>0.254356</v>
       </c>
       <c r="E198" s="12">
         <v>8447.0</v>
@@ -7322,7 +7322,7 @@
         <v>6.0</v>
       </c>
       <c r="D199" s="2">
-        <v>0.25833333333</v>
+        <v>0.2569</v>
       </c>
       <c r="E199" s="12">
         <v>8588.4</v>
@@ -7352,7 +7352,7 @@
         <v>7.0</v>
       </c>
       <c r="D200" s="2">
-        <v>0.25833333333</v>
+        <v>0.259469</v>
       </c>
       <c r="E200" s="12">
         <v>9277.8</v>
@@ -7382,7 +7382,7 @@
         <v>8.0</v>
       </c>
       <c r="D201" s="2">
-        <v>0.25833333333</v>
+        <v>0.262063</v>
       </c>
       <c r="E201" s="12">
         <v>9101.0</v>
@@ -7412,7 +7412,7 @@
         <v>9.0</v>
       </c>
       <c r="D202" s="2">
-        <v>0.25833333333</v>
+        <v>0.264684</v>
       </c>
       <c r="E202" s="12">
         <v>9048.0</v>
@@ -7442,7 +7442,7 @@
         <v>10.0</v>
       </c>
       <c r="D203" s="2">
-        <v>0.25833333333</v>
+        <v>0.267331</v>
       </c>
       <c r="E203" s="12">
         <v>9330.0</v>
@@ -7472,7 +7472,7 @@
         <v>11.0</v>
       </c>
       <c r="D204" s="2">
-        <v>0.25833333333</v>
+        <v>0.270004</v>
       </c>
       <c r="E204" s="12">
         <v>9878.8</v>
@@ -7502,7 +7502,7 @@
         <v>12.0</v>
       </c>
       <c r="D205" s="2">
-        <v>0.25833333333</v>
+        <v>0.272704</v>
       </c>
       <c r="E205" s="12">
         <v>9684.3</v>
@@ -7532,7 +7532,7 @@
         <v>1.0</v>
       </c>
       <c r="D206" s="2">
-        <v>0.28333333333</v>
+        <v>0.268086</v>
       </c>
       <c r="E206" s="12">
         <v>10745.0</v>
@@ -7562,7 +7562,7 @@
         <v>2.0</v>
       </c>
       <c r="D207" s="2">
-        <v>0.28333333333</v>
+        <v>0.270767</v>
       </c>
       <c r="E207" s="12">
         <v>9083.3</v>
@@ -7592,7 +7592,7 @@
         <v>3.0</v>
       </c>
       <c r="D208" s="2">
-        <v>0.28333333333</v>
+        <v>0.273474</v>
       </c>
       <c r="E208" s="12">
         <v>9931.8</v>
@@ -7622,7 +7622,7 @@
         <v>4.0</v>
       </c>
       <c r="D209" s="2">
-        <v>0.28333333333</v>
+        <v>0.276209</v>
       </c>
       <c r="E209" s="12">
         <v>8800.5</v>
@@ -7652,7 +7652,7 @@
         <v>5.0</v>
       </c>
       <c r="D210" s="2">
-        <v>0.28333333333</v>
+        <v>0.278971</v>
       </c>
       <c r="E210" s="12">
         <v>9366.2</v>
@@ -7682,7 +7682,7 @@
         <v>6.0</v>
       </c>
       <c r="D211" s="2">
-        <v>0.28333333333</v>
+        <v>0.281761</v>
       </c>
       <c r="E211" s="12">
         <v>8995.0</v>
@@ -7712,7 +7712,7 @@
         <v>7.0</v>
       </c>
       <c r="D212" s="2">
-        <v>0.28333333333</v>
+        <v>0.284579</v>
       </c>
       <c r="E212" s="12">
         <v>9136.4</v>
@@ -7742,7 +7742,7 @@
         <v>8.0</v>
       </c>
       <c r="D213" s="2">
-        <v>0.28333333333</v>
+        <v>0.287424</v>
       </c>
       <c r="E213" s="12">
         <v>9984.9</v>
@@ -7772,7 +7772,7 @@
         <v>9.0</v>
       </c>
       <c r="D214" s="2">
-        <v>0.28333333333</v>
+        <v>0.290299</v>
       </c>
       <c r="E214" s="2">
         <v>9207.1</v>
@@ -7802,7 +7802,7 @@
         <v>10.0</v>
       </c>
       <c r="D215" s="2">
-        <v>0.28333333333</v>
+        <v>0.293202</v>
       </c>
       <c r="E215" s="2">
         <v>9507.6</v>
@@ -7832,7 +7832,7 @@
         <v>11.0</v>
       </c>
       <c r="D216" s="2">
-        <v>0.28333333333</v>
+        <v>0.296134</v>
       </c>
       <c r="E216" s="2">
         <v>9596.0</v>
@@ -7862,7 +7862,7 @@
         <v>12.0</v>
       </c>
       <c r="D217" s="2">
-        <v>0.28333333333</v>
+        <v>0.299095</v>
       </c>
       <c r="E217" s="2">
         <v>9790.4</v>
@@ -7892,7 +7892,7 @@
         <v>1.0</v>
       </c>
       <c r="D218" s="2">
-        <v>0.30833333333</v>
+        <v>0.291741</v>
       </c>
       <c r="E218" s="2">
         <v>9984.9</v>
@@ -7922,7 +7922,7 @@
         <v>2.0</v>
       </c>
       <c r="D219" s="2">
-        <v>0.30833333333</v>
+        <v>0.294658</v>
       </c>
       <c r="E219" s="2">
         <v>8977.3</v>
@@ -7952,7 +7952,7 @@
         <v>3.0</v>
       </c>
       <c r="D220" s="2">
-        <v>0.30833333333</v>
+        <v>0.297605</v>
       </c>
       <c r="E220" s="2">
         <v>9596.0</v>
@@ -7982,7 +7982,7 @@
         <v>4.0</v>
       </c>
       <c r="D221" s="2">
-        <v>0.30833333333</v>
+        <v>0.300581</v>
       </c>
       <c r="E221" s="2">
         <v>9684.3</v>
@@ -8012,7 +8012,7 @@
         <v>5.0</v>
       </c>
       <c r="D222" s="2">
-        <v>0.30833333333</v>
+        <v>0.303586</v>
       </c>
       <c r="E222" s="2">
         <v>10338.4</v>
@@ -8042,7 +8042,7 @@
         <v>6.0</v>
       </c>
       <c r="D223" s="2">
-        <v>0.30833333333</v>
+        <v>0.306622</v>
       </c>
       <c r="E223" s="2">
         <v>9118.7</v>
@@ -8072,7 +8072,7 @@
         <v>7.0</v>
       </c>
       <c r="D224" s="2">
-        <v>0.30833333333</v>
+        <v>0.309688</v>
       </c>
       <c r="E224" s="2">
         <v>9472.2</v>
@@ -8102,7 +8102,7 @@
         <v>8.0</v>
       </c>
       <c r="D225" s="2">
-        <v>0.30833333333</v>
+        <v>0.312785</v>
       </c>
       <c r="E225" s="2">
         <v>9436.9</v>
@@ -8132,7 +8132,7 @@
         <v>9.0</v>
       </c>
       <c r="D226" s="2">
-        <v>0.30833333333</v>
+        <v>0.315913</v>
       </c>
       <c r="E226" s="2">
         <v>9277.8</v>
@@ -8162,7 +8162,7 @@
         <v>10.0</v>
       </c>
       <c r="D227" s="2">
-        <v>0.30833333333</v>
+        <v>0.319072</v>
       </c>
       <c r="E227" s="2">
         <v>9419.2</v>
@@ -8192,7 +8192,7 @@
         <v>11.0</v>
       </c>
       <c r="D228" s="2">
-        <v>0.30833333333</v>
+        <v>0.322263</v>
       </c>
       <c r="E228" s="2">
         <v>9048.0</v>
@@ -8222,7 +8222,7 @@
         <v>12.0</v>
       </c>
       <c r="D229" s="2">
-        <v>0.30833333333</v>
+        <v>0.325486</v>
       </c>
       <c r="E229" s="2">
         <v>8995.0</v>
@@ -8252,7 +8252,7 @@
         <v>1.0</v>
       </c>
       <c r="D230" s="2">
-        <v>0.3</v>
+        <v>0.283856</v>
       </c>
       <c r="E230" s="2">
         <v>8853.3</v>
@@ -8282,7 +8282,7 @@
         <v>2.0</v>
       </c>
       <c r="D231" s="2">
-        <v>0.3</v>
+        <v>0.286694</v>
       </c>
       <c r="E231" s="2">
         <v>8447.0</v>
@@ -8312,7 +8312,7 @@
         <v>3.0</v>
       </c>
       <c r="D232" s="2">
-        <v>0.3</v>
+        <v>0.289561</v>
       </c>
       <c r="E232" s="2">
         <v>8623.7</v>
@@ -8342,7 +8342,7 @@
         <v>4.0</v>
       </c>
       <c r="D233" s="2">
-        <v>0.3</v>
+        <v>0.292457</v>
       </c>
       <c r="E233" s="2">
         <v>8287.9</v>
@@ -8372,7 +8372,7 @@
         <v>5.0</v>
       </c>
       <c r="D234" s="2">
-        <v>0.3</v>
+        <v>0.295381</v>
       </c>
       <c r="E234" s="2">
         <v>7952.0</v>
@@ -8402,7 +8402,7 @@
         <v>6.0</v>
       </c>
       <c r="D235" s="2">
-        <v>0.3</v>
+        <v>0.298335</v>
       </c>
       <c r="E235" s="2">
         <v>7722.2</v>
@@ -8432,7 +8432,7 @@
         <v>7.0</v>
       </c>
       <c r="D236" s="2">
-        <v>0.3</v>
+        <v>0.301318</v>
       </c>
       <c r="E236" s="2">
         <v>7545.4</v>
@@ -8462,7 +8462,7 @@
         <v>8.0</v>
       </c>
       <c r="D237" s="2">
-        <v>0.3</v>
+        <v>0.304332</v>
       </c>
       <c r="E237" s="2">
         <v>7121.2</v>
@@ -8492,7 +8492,7 @@
         <v>9.0</v>
       </c>
       <c r="D238" s="2">
-        <v>0.3</v>
+        <v>0.307375</v>
       </c>
       <c r="E238" s="2">
         <v>7510.1</v>
@@ -8522,7 +8522,7 @@
         <v>10.0</v>
       </c>
       <c r="D239" s="2">
-        <v>0.3</v>
+        <v>0.310449</v>
       </c>
       <c r="E239" s="2">
         <v>7298.0</v>
@@ -8552,7 +8552,7 @@
         <v>11.0</v>
       </c>
       <c r="D240" s="2">
-        <v>0.3</v>
+        <v>0.313553</v>
       </c>
       <c r="E240" s="2">
         <v>7191.9</v>
@@ -8582,7 +8582,7 @@
         <v>12.0</v>
       </c>
       <c r="D241" s="2">
-        <v>0.3</v>
+        <v>0.316689</v>
       </c>
       <c r="E241" s="2">
         <v>7244.9</v>
@@ -8612,7 +8612,7 @@
         <v>1.0</v>
       </c>
       <c r="D242" s="2">
-        <v>0.29166666666</v>
+        <v>0.275971</v>
       </c>
       <c r="E242" s="2">
         <v>7050.5</v>
@@ -8642,7 +8642,7 @@
         <v>2.0</v>
       </c>
       <c r="D243" s="2">
-        <v>0.29166666666</v>
+        <v>0.27873</v>
       </c>
       <c r="E243" s="2">
         <v>6042.9</v>
@@ -8672,7 +8672,7 @@
         <v>3.0</v>
       </c>
       <c r="D244" s="2">
-        <v>0.29166666666</v>
+        <v>0.281518</v>
       </c>
       <c r="E244" s="2">
         <v>5714.6</v>
@@ -8702,7 +8702,7 @@
         <v>4.0</v>
       </c>
       <c r="D245" s="2">
-        <v>0.29166666666</v>
+        <v>0.284333</v>
       </c>
       <c r="E245" s="2">
         <v>6295.4</v>
@@ -8732,7 +8732,7 @@
         <v>5.0</v>
       </c>
       <c r="D246" s="2">
-        <v>0.29166666666</v>
+        <v>0.287176</v>
       </c>
       <c r="E246" s="2">
         <v>6800.5</v>
@@ -8762,7 +8762,7 @@
         <v>6.0</v>
       </c>
       <c r="D247" s="2">
-        <v>0.29166666666</v>
+        <v>0.290048</v>
       </c>
       <c r="E247" s="2">
         <v>6824.8</v>
@@ -8792,7 +8792,7 @@
         <v>7.0</v>
       </c>
       <c r="D248" s="2">
-        <v>0.29166666666</v>
+        <v>0.292949</v>
       </c>
       <c r="E248" s="2">
         <v>6914.1</v>
@@ -8822,7 +8822,7 @@
         <v>8.0</v>
       </c>
       <c r="D249" s="2">
-        <v>0.29166666666</v>
+        <v>0.295878</v>
       </c>
       <c r="E249" s="2">
         <v>7318.2</v>
@@ -8852,7 +8852,7 @@
         <v>9.0</v>
       </c>
       <c r="D250" s="2">
-        <v>0.29166666666</v>
+        <v>0.298837</v>
       </c>
       <c r="E250" s="2">
         <v>7179.3</v>
@@ -8882,7 +8882,7 @@
         <v>10.0</v>
       </c>
       <c r="D251" s="2">
-        <v>0.29166666666</v>
+        <v>0.301825</v>
       </c>
       <c r="E251" s="2">
         <v>7255.1</v>
@@ -8912,7 +8912,7 @@
         <v>11.0</v>
       </c>
       <c r="D252" s="2">
-        <v>0.29166666666</v>
+        <v>0.304843</v>
       </c>
       <c r="E252" s="2">
         <v>8075.8</v>
@@ -8942,7 +8942,7 @@
         <v>12.0</v>
       </c>
       <c r="D253" s="2">
-        <v>0.29166666666</v>
+        <v>0.307892</v>
       </c>
       <c r="E253" s="2">
         <v>7646.5</v>
@@ -8972,7 +8972,7 @@
         <v>1.0</v>
       </c>
       <c r="D254" s="2">
-        <v>0.30833333333</v>
+        <v>0.291741</v>
       </c>
       <c r="E254" s="2">
         <v>7949.5</v>
@@ -9002,7 +9002,7 @@
         <v>2.0</v>
       </c>
       <c r="D255" s="2">
-        <v>0.30833333333</v>
+        <v>0.294658</v>
       </c>
       <c r="E255" s="2">
         <v>8820.7</v>
@@ -9032,7 +9032,7 @@
         <v>3.0</v>
       </c>
       <c r="D256" s="2">
-        <v>0.30833333333</v>
+        <v>0.297605</v>
       </c>
       <c r="E256" s="2">
         <v>8707.1</v>
@@ -9062,7 +9062,7 @@
         <v>4.0</v>
       </c>
       <c r="D257" s="2">
-        <v>0.30833333333</v>
+        <v>0.300581</v>
       </c>
       <c r="E257" s="2">
         <v>8416.7</v>
@@ -9092,7 +9092,7 @@
         <v>5.0</v>
       </c>
       <c r="D258" s="2">
-        <v>0.30833333333</v>
+        <v>0.303586</v>
       </c>
       <c r="E258" s="2">
         <v>7633.8</v>
@@ -9122,7 +9122,7 @@
         <v>6.0</v>
       </c>
       <c r="D259" s="2">
-        <v>0.30833333333</v>
+        <v>0.306622</v>
       </c>
       <c r="E259" s="2">
         <v>8075.8</v>
@@ -9152,7 +9152,7 @@
         <v>7.0</v>
       </c>
       <c r="D260" s="2">
-        <v>0.30833333333</v>
+        <v>0.309688</v>
       </c>
       <c r="E260" s="2">
         <v>8252.5</v>
@@ -9182,7 +9182,7 @@
         <v>8.0</v>
       </c>
       <c r="D261" s="2">
-        <v>0.30833333333</v>
+        <v>0.312785</v>
       </c>
       <c r="E261" s="2">
         <v>8378.8</v>
@@ -9212,7 +9212,7 @@
         <v>9.0</v>
       </c>
       <c r="D262" s="2">
-        <v>0.30833333333</v>
+        <v>0.315913</v>
       </c>
       <c r="E262" s="2">
         <v>9590.9</v>
@@ -9242,7 +9242,7 @@
         <v>10.0</v>
       </c>
       <c r="D263" s="2">
-        <v>0.30833333333</v>
+        <v>0.319072</v>
       </c>
       <c r="E263" s="2">
         <v>8795.5</v>
@@ -9272,7 +9272,7 @@
         <v>11.0</v>
       </c>
       <c r="D264" s="2">
-        <v>0.30833333333</v>
+        <v>0.322263</v>
       </c>
       <c r="E264" s="2">
         <v>8505.0</v>
@@ -9302,7 +9302,7 @@
         <v>12.0</v>
       </c>
       <c r="D265" s="2">
-        <v>0.30833333333</v>
+        <v>0.325486</v>
       </c>
       <c r="E265" s="2">
         <v>8593.4</v>
@@ -9332,7 +9332,7 @@
         <v>1.0</v>
       </c>
       <c r="D266" s="2">
-        <v>0.29166666666</v>
+        <v>0.275971</v>
       </c>
       <c r="E266" s="2">
         <v>9060.6</v>
@@ -9362,7 +9362,7 @@
         <v>2.0</v>
       </c>
       <c r="D267" s="2">
-        <v>0.29166666666</v>
+        <v>0.27873</v>
       </c>
       <c r="E267" s="2">
         <v>9035.4</v>
@@ -9392,7 +9392,7 @@
         <v>3.0</v>
       </c>
       <c r="D268" s="2">
-        <v>0.29166666666</v>
+        <v>0.281518</v>
       </c>
       <c r="E268" s="2">
         <v>9048.0</v>
@@ -9422,7 +9422,7 @@
         <v>4.0</v>
       </c>
       <c r="D269" s="2">
-        <v>0.29166666666</v>
+        <v>0.284333</v>
       </c>
       <c r="E269" s="2">
         <v>8820.7</v>
@@ -9452,7 +9452,7 @@
         <v>5.0</v>
       </c>
       <c r="D270" s="2">
-        <v>0.29166666666</v>
+        <v>0.287176</v>
       </c>
       <c r="E270" s="2">
         <v>8984.9</v>
@@ -9482,7 +9482,7 @@
         <v>6.0</v>
       </c>
       <c r="D271" s="2">
-        <v>0.29166666666</v>
+        <v>0.290048</v>
       </c>
       <c r="E271" s="2">
         <v>8366.2</v>
@@ -9512,7 +9512,7 @@
         <v>7.0</v>
       </c>
       <c r="D272" s="2">
-        <v>0.29166666666</v>
+        <v>0.292949</v>
       </c>
       <c r="E272" s="2">
         <v>8063.1</v>
@@ -9542,7 +9542,7 @@
         <v>8.0</v>
       </c>
       <c r="D273" s="2">
-        <v>0.29166666666</v>
+        <v>0.295878</v>
       </c>
       <c r="E273" s="2">
         <v>7936.9</v>
@@ -9572,7 +9572,7 @@
         <v>9.0</v>
       </c>
       <c r="D274" s="2">
-        <v>0.29166666666</v>
+        <v>0.298837</v>
       </c>
       <c r="E274" s="2">
         <v>8164.1</v>
@@ -9602,7 +9602,7 @@
         <v>10.0</v>
       </c>
       <c r="D275" s="2">
-        <v>0.29166666666</v>
+        <v>0.301825</v>
       </c>
       <c r="E275" s="2">
         <v>7962.1</v>
@@ -9632,7 +9632,7 @@
         <v>11.0</v>
       </c>
       <c r="D276" s="2">
-        <v>0.29166666666</v>
+        <v>0.304843</v>
       </c>
       <c r="E276" s="2">
         <v>8159.1</v>
@@ -9662,7 +9662,7 @@
         <v>12.0</v>
       </c>
       <c r="D277" s="2">
-        <v>0.29166666666</v>
+        <v>0.307892</v>
       </c>
       <c r="E277" s="2">
         <v>8075.8</v>
@@ -9692,7 +9692,7 @@
         <v>1.0</v>
       </c>
       <c r="D278" s="2">
-        <v>0.31666666666</v>
+        <v>0.299625</v>
       </c>
       <c r="E278" s="2">
         <v>8234.9</v>
@@ -9722,7 +9722,7 @@
         <v>2.0</v>
       </c>
       <c r="D279" s="2">
-        <v>0.31666666666</v>
+        <v>0.302622</v>
       </c>
       <c r="E279" s="2">
         <v>8356.1</v>
@@ -9752,7 +9752,7 @@
         <v>3.0</v>
       </c>
       <c r="D280" s="2">
-        <v>0.31666666666</v>
+        <v>0.305648</v>
       </c>
       <c r="E280" s="2">
         <v>8151.5</v>
@@ -9782,7 +9782,7 @@
         <v>4.0</v>
       </c>
       <c r="D281" s="2">
-        <v>0.31666666666</v>
+        <v>0.308704</v>
       </c>
       <c r="E281" s="2">
         <v>8272.7</v>
@@ -9812,7 +9812,7 @@
         <v>5.0</v>
       </c>
       <c r="D282" s="2">
-        <v>0.31666666666</v>
+        <v>0.311791</v>
       </c>
       <c r="E282" s="2">
         <v>7757.6</v>
@@ -9842,7 +9842,7 @@
         <v>6.0</v>
       </c>
       <c r="D283" s="2">
-        <v>0.31666666666</v>
+        <v>0.314909</v>
       </c>
       <c r="E283" s="2">
         <v>7992.4</v>
@@ -9872,7 +9872,7 @@
         <v>7.0</v>
       </c>
       <c r="D284" s="2">
-        <v>0.31666666666</v>
+        <v>0.318058</v>
       </c>
       <c r="E284" s="2">
         <v>8212.1</v>
@@ -9902,7 +9902,7 @@
         <v>8.0</v>
       </c>
       <c r="D285" s="2">
-        <v>0.31666666666</v>
+        <v>0.321239</v>
       </c>
       <c r="E285" s="2">
         <v>8386.4</v>
@@ -9932,7 +9932,7 @@
         <v>9.0</v>
       </c>
       <c r="D286" s="2">
-        <v>0.31666666666</v>
+        <v>0.324451</v>
       </c>
       <c r="E286" s="2">
         <v>8265.1</v>
@@ -9962,7 +9962,7 @@
         <v>10.0</v>
       </c>
       <c r="D287" s="2">
-        <v>0.31666666666</v>
+        <v>0.327696</v>
       </c>
       <c r="E287" s="2">
         <v>8075.8</v>
@@ -9992,7 +9992,7 @@
         <v>11.0</v>
       </c>
       <c r="D288" s="2">
-        <v>0.31666666666</v>
+        <v>0.330973</v>
       </c>
       <c r="E288" s="2">
         <v>7875.0</v>
@@ -10022,7 +10022,7 @@
         <v>12.0</v>
       </c>
       <c r="D289" s="2">
-        <v>0.31666666666</v>
+        <v>0.334283</v>
       </c>
       <c r="E289" s="2">
         <v>8181.8</v>
@@ -10052,7 +10052,7 @@
         <v>1.0</v>
       </c>
       <c r="D290" s="2">
-        <v>0.3</v>
+        <v>0.283856</v>
       </c>
       <c r="E290" s="2">
         <v>8136.4</v>
@@ -10082,7 +10082,7 @@
         <v>2.0</v>
       </c>
       <c r="D291" s="2">
-        <v>0.3</v>
+        <v>0.286694</v>
       </c>
       <c r="E291" s="2">
         <v>8096.6</v>
@@ -10112,7 +10112,7 @@
         <v>3.0</v>
       </c>
       <c r="D292" s="2">
-        <v>0.3</v>
+        <v>0.289561</v>
       </c>
       <c r="E292" s="2">
         <v>8187.5</v>
@@ -10142,7 +10142,7 @@
         <v>4.0</v>
       </c>
       <c r="D293" s="2">
-        <v>0.3</v>
+        <v>0.292457</v>
       </c>
       <c r="E293" s="2">
         <v>8460.2</v>
@@ -10172,7 +10172,7 @@
         <v>5.0</v>
       </c>
       <c r="D294" s="2">
-        <v>0.3</v>
+        <v>0.295381</v>
       </c>
       <c r="E294" s="2">
         <v>8517.0</v>
@@ -10202,7 +10202,7 @@
         <v>6.0</v>
       </c>
       <c r="D295" s="2">
-        <v>0.3</v>
+        <v>0.298335</v>
       </c>
       <c r="E295" s="2">
         <v>8483.0</v>
@@ -10232,7 +10232,7 @@
         <v>7.0</v>
       </c>
       <c r="D296" s="2">
-        <v>0.3</v>
+        <v>0.301318</v>
       </c>
       <c r="E296" s="2">
         <v>8295.5</v>
@@ -10262,7 +10262,7 @@
         <v>8.0</v>
       </c>
       <c r="D297" s="2">
-        <v>0.3</v>
+        <v>0.304332</v>
       </c>
       <c r="E297" s="2">
         <v>8193.2</v>
@@ -10292,7 +10292,7 @@
         <v>9.0</v>
       </c>
       <c r="D298" s="2">
-        <v>0.3</v>
+        <v>0.307375</v>
       </c>
       <c r="E298" s="2">
         <v>8136.4</v>
@@ -10322,7 +10322,7 @@
         <v>10.0</v>
       </c>
       <c r="D299" s="2">
-        <v>0.3</v>
+        <v>0.310449</v>
       </c>
       <c r="E299" s="2">
         <v>8238.6</v>
@@ -10352,7 +10352,7 @@
         <v>11.0</v>
       </c>
       <c r="D300" s="2">
-        <v>0.3</v>
+        <v>0.313553</v>
       </c>
       <c r="E300" s="2">
         <v>8642.0</v>
@@ -10382,7 +10382,7 @@
         <v>12.0</v>
       </c>
       <c r="D301" s="2">
-        <v>0.3</v>
+        <v>0.316689</v>
       </c>
       <c r="E301" s="2">
         <v>8545.5</v>
@@ -10412,7 +10412,7 @@
         <v>1.0</v>
       </c>
       <c r="D302" s="2">
-        <v>0.30833333333</v>
+        <v>0.291741</v>
       </c>
       <c r="E302" s="2">
         <v>7846.6</v>
@@ -10442,7 +10442,7 @@
         <v>2.0</v>
       </c>
       <c r="D303" s="2">
-        <v>0.30833333333</v>
+        <v>0.294658</v>
       </c>
       <c r="E303" s="2">
         <v>8113.6</v>
@@ -10472,7 +10472,7 @@
         <v>3.0</v>
       </c>
       <c r="D304" s="2">
-        <v>0.30833333333</v>
+        <v>0.297605</v>
       </c>
       <c r="E304" s="2">
         <v>7738.6</v>
@@ -10502,7 +10502,7 @@
         <v>4.0</v>
       </c>
       <c r="D305" s="2">
-        <v>0.30833333333</v>
+        <v>0.300581</v>
       </c>
       <c r="E305" s="2">
         <v>7318.2</v>
@@ -10532,7 +10532,7 @@
         <v>5.0</v>
       </c>
       <c r="D306" s="2">
-        <v>0.30833333333</v>
+        <v>0.303586</v>
       </c>
       <c r="E306" s="2">
         <v>6982.9</v>
@@ -10562,7 +10562,7 @@
         <v>6.0</v>
       </c>
       <c r="D307" s="2">
-        <v>0.30833333333</v>
+        <v>0.306622</v>
       </c>
       <c r="E307" s="2">
         <v>7335.2</v>
@@ -10592,7 +10592,7 @@
         <v>7.0</v>
       </c>
       <c r="D308" s="2">
-        <v>0.30833333333</v>
+        <v>0.309688</v>
       </c>
       <c r="E308" s="2">
         <v>7343.4</v>
@@ -10622,7 +10622,7 @@
         <v>8.0</v>
       </c>
       <c r="D309" s="2">
-        <v>0.30833333333</v>
+        <v>0.312785</v>
       </c>
       <c r="E309" s="2">
         <v>7299.2</v>
@@ -10652,7 +10652,7 @@
         <v>9.0</v>
       </c>
       <c r="D310" s="2">
-        <v>0.30833333333</v>
+        <v>0.315913</v>
       </c>
       <c r="E310" s="2">
         <v>7078.3</v>
@@ -10682,7 +10682,7 @@
         <v>10.0</v>
       </c>
       <c r="D311" s="2">
-        <v>0.30833333333</v>
+        <v>0.319072</v>
       </c>
       <c r="E311" s="2">
         <v>6928.0</v>
@@ -10712,7 +10712,7 @@
         <v>11.0</v>
       </c>
       <c r="D312" s="2">
-        <v>0.30833333333</v>
+        <v>0.322263</v>
       </c>
       <c r="E312" s="2">
         <v>6751.3</v>
@@ -10741,7 +10741,7 @@
         <v>12.0</v>
       </c>
       <c r="D313" s="2">
-        <v>0.30833333333</v>
+        <v>0.325486</v>
       </c>
       <c r="E313" s="2">
         <v>6300.5</v>

--- a/historical_xlpe_demand.xlsx
+++ b/historical_xlpe_demand.xlsx
@@ -13,11 +13,11 @@
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision">
   <authors>
-    <author>tc={40fe6a31-1f31-419e-bfa6-8900449ed13e}</author>
-    <author>tc={8dd46b68-e860-41a0-97fc-755da7cbce17}</author>
+    <author>tc={6f272649-a21e-46e6-aaae-c88b1a61ae0e}</author>
+    <author>tc={75094427-b850-404c-afc3-cffa37dacd13}</author>
   </authors>
   <commentList>
-    <comment authorId="0" xr:uid="{40fe6a31-1f31-419e-bfa6-8900449ed13e}" ref="G1">
+    <comment authorId="0" xr:uid="{6f272649-a21e-46e6-aaae-c88b1a61ae0e}" ref="G1">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -26,7 +26,7 @@
 </t>
       </text>
     </comment>
-    <comment authorId="1" xr:uid="{8dd46b68-e860-41a0-97fc-755da7cbce17}" ref="G1">
+    <comment authorId="1" xr:uid="{75094427-b850-404c-afc3-cffa37dacd13}" ref="G1">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -1075,7 +1075,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1103,10 +1103,7 @@
     <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="2" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="2" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -1145,7 +1142,7 @@
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments">
-  <x18tc:person displayName="Salma Waleed El Marakby" id="{57e9841c-36df-4301-b20c-55843a971ac9}" providerId="google-sheets"/>
+  <x18tc:person displayName="Salma Waleed El Marakby" id="{0d570789-4e96-443f-ae67-0506174a6525}" providerId="google-sheets"/>
 </x18tc:personList>
 </file>
 
@@ -1345,10 +1342,10 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <x18tc:ThreadedComments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:xltc2="http://schemas.microsoft.com/office/spreadsheetml/2020/threadedcomments2" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <x18tc:threadedComment ref="G1" dT="2026-01-14T03:16:27.00" personId="{57e9841c-36df-4301-b20c-55843a971ac9}" id="{8dd46b68-e860-41a0-97fc-755da7cbce17}" done="0">
+  <x18tc:threadedComment ref="G1" dT="2026-01-14T03:16:27.00" personId="{0d570789-4e96-443f-ae67-0506174a6525}" id="{6f272649-a21e-46e6-aaae-c88b1a61ae0e}" done="0">
     <x18tc:text xml:space="preserve">Middle East, North Africa, Afghanistan &amp; Pakistan</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="G1" dT="2026-01-14T03:16:06.00" personId="{57e9841c-36df-4301-b20c-55843a971ac9}" id="{40fe6a31-1f31-419e-bfa6-8900449ed13e}" done="1">
+  <x18tc:threadedComment ref="G1" dT="2026-01-14T03:16:06.00" personId="{0d570789-4e96-443f-ae67-0506174a6525}" id="{75094427-b850-404c-afc3-cffa37dacd13}" done="1">
     <x18tc:text xml:space="preserve">Middle East, North Africa, Afghanistan &amp; Pakistan</x18tc:text>
   </x18tc:threadedComment>
 </x18tc:ThreadedComments>
@@ -1361,7 +1358,7 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
-    <col customWidth="1" min="4" max="4" width="15.5"/>
+    <col customWidth="1" min="4" max="4" width="20.38"/>
     <col customWidth="1" min="5" max="5" width="16.63"/>
     <col customWidth="1" min="6" max="6" width="25.25"/>
     <col customWidth="1" min="7" max="7" width="14.25"/>
@@ -1424,7 +1421,7 @@
         <v>6.365211</v>
       </c>
       <c r="H2" s="2">
-        <v>429785.0</v>
+        <v>429544.0</v>
       </c>
       <c r="I2" s="2">
         <v>0.0</v>
@@ -1454,7 +1451,7 @@
         <v>8.401323</v>
       </c>
       <c r="H3" s="2">
-        <v>437410.0</v>
+        <v>432504.0</v>
       </c>
       <c r="I3" s="2">
         <v>1.77</v>
@@ -1484,7 +1481,7 @@
         <v>9.974024</v>
       </c>
       <c r="H4" s="2">
-        <v>437410.0</v>
+        <v>438775.0</v>
       </c>
       <c r="I4" s="8">
         <v>0.0</v>
@@ -1514,7 +1511,7 @@
         <v>11.3226</v>
       </c>
       <c r="H5" s="2">
-        <v>437410.0</v>
+        <v>439566.0</v>
       </c>
       <c r="I5" s="8">
         <v>0.0</v>
@@ -1544,7 +1541,7 @@
         <v>12.3222</v>
       </c>
       <c r="H6" s="2">
-        <v>437410.0</v>
+        <v>439764.0</v>
       </c>
       <c r="I6" s="8">
         <v>0.0</v>
@@ -1574,7 +1571,7 @@
         <v>13.06246</v>
       </c>
       <c r="H7" s="2">
-        <v>437410.0</v>
+        <v>439556.0</v>
       </c>
       <c r="I7" s="8">
         <v>0.0</v>
@@ -1604,7 +1601,7 @@
         <v>13.51761</v>
       </c>
       <c r="H8" s="2">
-        <v>437410.0</v>
+        <v>439283.0</v>
       </c>
       <c r="I8" s="8">
         <v>0.0</v>
@@ -1634,7 +1631,7 @@
         <v>13.74097</v>
       </c>
       <c r="H9" s="2">
-        <v>437410.0</v>
+        <v>437907.0</v>
       </c>
       <c r="I9" s="8">
         <v>0.0</v>
@@ -1664,7 +1661,7 @@
         <v>13.73669</v>
       </c>
       <c r="H10" s="2">
-        <v>440639.0</v>
+        <v>441345.0</v>
       </c>
       <c r="I10" s="8">
         <v>0.74</v>
@@ -1694,7 +1691,7 @@
         <v>13.53805</v>
       </c>
       <c r="H11" s="2">
-        <v>450328.0</v>
+        <v>452604.0</v>
       </c>
       <c r="I11" s="8">
         <v>2.2</v>
@@ -1724,7 +1721,7 @@
         <v>13.15478</v>
       </c>
       <c r="H12" s="2">
-        <v>453557.0</v>
+        <v>449081.0</v>
       </c>
       <c r="I12" s="8">
         <v>0.72</v>
@@ -1754,7 +1751,7 @@
         <v>12.6336</v>
       </c>
       <c r="H13" s="2">
-        <v>456786.0</v>
+        <v>453130.0</v>
       </c>
       <c r="I13" s="8">
         <v>0.71</v>
@@ -1783,8 +1780,8 @@
       <c r="G14" s="8">
         <v>11.96275</v>
       </c>
-      <c r="H14" s="9">
-        <v>457470.0</v>
+      <c r="H14" s="2">
+        <v>462380.0</v>
       </c>
       <c r="I14" s="8">
         <v>0.15</v>
@@ -1814,9 +1811,9 @@
         <v>11.18081</v>
       </c>
       <c r="H15" s="2">
-        <v>460016.0</v>
-      </c>
-      <c r="I15" s="10">
+        <v>463539.0</v>
+      </c>
+      <c r="I15" s="9">
         <v>0.56</v>
       </c>
       <c r="K15" s="6"/>
@@ -1844,7 +1841,7 @@
         <v>10.39868</v>
       </c>
       <c r="H16" s="2">
-        <v>460016.0</v>
+        <v>459628.0</v>
       </c>
       <c r="I16" s="8">
         <v>0.0</v>
@@ -1874,7 +1871,7 @@
         <v>9.470513</v>
       </c>
       <c r="H17" s="2">
-        <v>463245.0</v>
+        <v>468806.0</v>
       </c>
       <c r="I17" s="8">
         <v>0.7</v>
@@ -1904,7 +1901,7 @@
         <v>8.531533</v>
       </c>
       <c r="H18" s="2">
-        <v>472934.0</v>
+        <v>473326.0</v>
       </c>
       <c r="I18" s="8">
         <v>2.09</v>
@@ -1934,7 +1931,7 @@
         <v>7.542122</v>
       </c>
       <c r="H19" s="2">
-        <v>472934.0</v>
+        <v>475571.0</v>
       </c>
       <c r="I19" s="8">
         <v>0.0</v>
@@ -1964,7 +1961,7 @@
         <v>6.588111</v>
       </c>
       <c r="H20" s="2">
-        <v>472934.0</v>
+        <v>475453.0</v>
       </c>
       <c r="I20" s="8">
         <v>0.0</v>
@@ -1994,7 +1991,7 @@
         <v>5.628882</v>
       </c>
       <c r="H21" s="2">
-        <v>472934.0</v>
+        <v>472191.0</v>
       </c>
       <c r="I21" s="8">
         <v>0.0</v>
@@ -2024,7 +2021,7 @@
         <v>4.72003</v>
       </c>
       <c r="H22" s="2">
-        <v>476163.0</v>
+        <v>481075.0</v>
       </c>
       <c r="I22" s="8">
         <v>0.68</v>
@@ -2054,7 +2051,7 @@
         <v>3.910702</v>
       </c>
       <c r="H23" s="2">
-        <v>482622.0</v>
+        <v>484979.0</v>
       </c>
       <c r="I23" s="8">
         <v>1.36</v>
@@ -2084,7 +2081,7 @@
         <v>3.169925</v>
       </c>
       <c r="H24" s="2">
-        <v>485851.0</v>
+        <v>485621.0</v>
       </c>
       <c r="I24" s="8">
         <v>0.67</v>
@@ -2114,7 +2111,7 @@
         <v>2.567489</v>
       </c>
       <c r="H25" s="2">
-        <v>489081.0</v>
+        <v>486935.0</v>
       </c>
       <c r="I25" s="8">
         <v>0.66</v>
@@ -2144,7 +2141,7 @@
         <v>2.086215</v>
       </c>
       <c r="H26" s="2">
-        <v>487890.0</v>
+        <v>487665.0</v>
       </c>
       <c r="I26" s="8">
         <v>-0.24</v>
@@ -2174,7 +2171,7 @@
         <v>1.765333</v>
       </c>
       <c r="H27" s="2">
-        <v>495539.0</v>
+        <v>495295.0</v>
       </c>
       <c r="I27" s="8">
         <v>1.57</v>
@@ -2204,7 +2201,7 @@
         <v>1.606051</v>
       </c>
       <c r="H28" s="2">
-        <v>498769.0</v>
+        <v>498271.0</v>
       </c>
       <c r="I28" s="8">
         <v>0.65</v>
@@ -2234,7 +2231,7 @@
         <v>1.55993</v>
       </c>
       <c r="H29" s="2">
-        <v>501998.0</v>
+        <v>501207.0</v>
       </c>
       <c r="I29" s="8">
         <v>0.65</v>
@@ -2264,7 +2261,7 @@
         <v>1.631439</v>
       </c>
       <c r="H30" s="2">
-        <v>505228.0</v>
+        <v>509921.0</v>
       </c>
       <c r="I30" s="8">
         <v>0.64</v>
@@ -2294,7 +2291,7 @@
         <v>1.810226</v>
       </c>
       <c r="H31" s="2">
-        <v>511687.0</v>
+        <v>514178.0</v>
       </c>
       <c r="I31" s="8">
         <v>1.28</v>
@@ -2324,7 +2321,7 @@
         <v>2.070282</v>
       </c>
       <c r="H32" s="2">
-        <v>514916.0</v>
+        <v>514740.0</v>
       </c>
       <c r="I32" s="8">
         <v>0.63</v>
@@ -2354,7 +2351,7 @@
         <v>2.413825</v>
       </c>
       <c r="H33" s="2">
-        <v>514916.0</v>
+        <v>516759.0</v>
       </c>
       <c r="I33" s="8">
         <v>0.0</v>
@@ -2384,7 +2381,7 @@
         <v>2.818044</v>
       </c>
       <c r="H34" s="2">
-        <v>514916.0</v>
+        <v>518275.0</v>
       </c>
       <c r="I34" s="8">
         <v>0.0</v>
@@ -2414,7 +2411,7 @@
         <v>3.252362</v>
       </c>
       <c r="H35" s="2">
-        <v>514916.0</v>
+        <v>519773.0</v>
       </c>
       <c r="I35" s="8">
         <v>0.0</v>
@@ -2444,7 +2441,7 @@
         <v>3.730615</v>
       </c>
       <c r="H36" s="2">
-        <v>514916.0</v>
+        <v>515195.0</v>
       </c>
       <c r="I36" s="8">
         <v>0.0</v>
@@ -2474,7 +2471,7 @@
         <v>4.207473</v>
       </c>
       <c r="H37" s="2">
-        <v>514916.0</v>
+        <v>517904.0</v>
       </c>
       <c r="I37" s="8">
         <v>0.0</v>
@@ -2504,7 +2501,7 @@
         <v>4.699607</v>
       </c>
       <c r="H38" s="2">
-        <v>516128.0</v>
+        <v>512741.0</v>
       </c>
       <c r="I38" s="8">
         <v>0.24</v>
@@ -2534,7 +2531,7 @@
         <v>5.177487</v>
       </c>
       <c r="H39" s="2">
-        <v>521375.0</v>
+        <v>522585.0</v>
       </c>
       <c r="I39" s="8">
         <v>1.02</v>
@@ -2564,7 +2561,7 @@
         <v>5.591148</v>
       </c>
       <c r="H40" s="2">
-        <v>524604.0</v>
+        <v>521299.0</v>
       </c>
       <c r="I40" s="8">
         <v>0.62</v>
@@ -2594,7 +2591,7 @@
         <v>6.024557</v>
       </c>
       <c r="H41" s="2">
-        <v>527834.0</v>
+        <v>529548.0</v>
       </c>
       <c r="I41" s="8">
         <v>0.62</v>
@@ -2624,7 +2621,7 @@
         <v>6.414776</v>
       </c>
       <c r="H42" s="2">
-        <v>527834.0</v>
+        <v>532538.0</v>
       </c>
       <c r="I42" s="8">
         <v>0.0</v>
@@ -2654,7 +2651,7 @@
         <v>6.782878</v>
       </c>
       <c r="H43" s="2">
-        <v>531063.0</v>
+        <v>532003.0</v>
       </c>
       <c r="I43" s="8">
         <v>0.61</v>
@@ -2684,7 +2681,7 @@
         <v>7.100386</v>
       </c>
       <c r="H44" s="2">
-        <v>531063.0</v>
+        <v>534607.0</v>
       </c>
       <c r="I44" s="8">
         <v>0.0</v>
@@ -2714,7 +2711,7 @@
         <v>7.383527</v>
       </c>
       <c r="H45" s="2">
-        <v>534292.0</v>
+        <v>533616.0</v>
       </c>
       <c r="I45" s="8">
         <v>0.61</v>
@@ -2744,7 +2741,7 @@
         <v>7.61596</v>
       </c>
       <c r="H46" s="2">
-        <v>537522.0</v>
+        <v>535780.0</v>
       </c>
       <c r="I46" s="8">
         <v>0.6</v>
@@ -2774,7 +2771,7 @@
         <v>7.787833</v>
       </c>
       <c r="H47" s="2">
-        <v>540751.0</v>
+        <v>541954.0</v>
       </c>
       <c r="I47" s="8">
         <v>0.6</v>
@@ -2804,7 +2801,7 @@
         <v>7.905665</v>
       </c>
       <c r="H48" s="2">
-        <v>543981.0</v>
+        <v>547662.0</v>
       </c>
       <c r="I48" s="8">
         <v>0.6</v>
@@ -2834,7 +2831,7 @@
         <v>7.957125</v>
       </c>
       <c r="H49" s="2">
-        <v>543981.0</v>
+        <v>541448.0</v>
       </c>
       <c r="I49" s="8">
         <v>0.0</v>
@@ -2864,7 +2861,7 @@
         <v>7.940703</v>
       </c>
       <c r="H50" s="2">
-        <v>550412.0</v>
+        <v>543218.0</v>
       </c>
       <c r="I50" s="8">
         <v>1.18</v>
@@ -2894,7 +2891,7 @@
         <v>7.851349</v>
       </c>
       <c r="H51" s="2">
-        <v>550439.0</v>
+        <v>549849.0</v>
       </c>
       <c r="I51" s="8">
         <v>0.0</v>
@@ -2924,7 +2921,7 @@
         <v>7.709699</v>
       </c>
       <c r="H52" s="2">
-        <v>560128.0</v>
+        <v>556720.0</v>
       </c>
       <c r="I52" s="8">
         <v>1.76</v>
@@ -2954,7 +2951,7 @@
         <v>7.507468</v>
       </c>
       <c r="H53" s="2">
-        <v>563357.0</v>
+        <v>557744.0</v>
       </c>
       <c r="I53" s="8">
         <v>0.58</v>
@@ -2984,7 +2981,7 @@
         <v>7.272713</v>
       </c>
       <c r="H54" s="2">
-        <v>566587.0</v>
+        <v>569643.0</v>
       </c>
       <c r="I54" s="8">
         <v>0.57</v>
@@ -3014,7 +3011,7 @@
         <v>7.00135</v>
       </c>
       <c r="H55" s="2">
-        <v>573045.0</v>
+        <v>567661.0</v>
       </c>
       <c r="I55" s="8">
         <v>1.14</v>
@@ -3044,7 +3041,7 @@
         <v>6.721956</v>
       </c>
       <c r="H56" s="2">
-        <v>569816.0</v>
+        <v>569960.0</v>
       </c>
       <c r="I56" s="8">
         <v>-0.56</v>
@@ -3074,7 +3071,7 @@
         <v>6.427466</v>
       </c>
       <c r="H57" s="2">
-        <v>579504.0</v>
+        <v>577455.0</v>
       </c>
       <c r="I57" s="8">
         <v>1.7</v>
@@ -3104,7 +3101,7 @@
         <v>6.138855</v>
       </c>
       <c r="H58" s="2">
-        <v>582734.0</v>
+        <v>576189.0</v>
       </c>
       <c r="I58" s="8">
         <v>0.56</v>
@@ -3134,7 +3131,7 @@
         <v>5.876341</v>
       </c>
       <c r="H59" s="2">
-        <v>582734.0</v>
+        <v>587320.0</v>
       </c>
       <c r="I59" s="8">
         <v>0.0</v>
@@ -3164,7 +3161,7 @@
         <v>5.633988</v>
       </c>
       <c r="H60" s="2">
-        <v>589192.0</v>
+        <v>589224.0</v>
       </c>
       <c r="I60" s="8">
         <v>1.11</v>
@@ -3194,7 +3191,7 @@
         <v>5.4385</v>
       </c>
       <c r="H61" s="2">
-        <v>592422.0</v>
+        <v>587556.0</v>
       </c>
       <c r="I61" s="8">
         <v>0.55</v>
@@ -3224,7 +3221,7 @@
         <v>5.288409</v>
       </c>
       <c r="H62" s="2">
-        <v>596564.0</v>
+        <v>597887.0</v>
       </c>
       <c r="I62" s="8">
         <v>0.7</v>
@@ -3254,7 +3251,7 @@
         <v>5.19941</v>
       </c>
       <c r="H63" s="2">
-        <v>598881.0</v>
+        <v>599617.0</v>
       </c>
       <c r="I63" s="8">
         <v>0.39</v>
@@ -3284,7 +3281,7 @@
         <v>5.167257</v>
       </c>
       <c r="H64" s="2">
-        <v>602110.0</v>
+        <v>604139.0</v>
       </c>
       <c r="I64" s="8">
         <v>0.54</v>
@@ -3314,7 +3311,7 @@
         <v>5.177065</v>
       </c>
       <c r="H65" s="2">
-        <v>602110.0</v>
+        <v>607905.0</v>
       </c>
       <c r="I65" s="8">
         <v>0.0</v>
@@ -3344,7 +3341,7 @@
         <v>5.224079</v>
       </c>
       <c r="H66" s="2">
-        <v>608569.0</v>
+        <v>604662.0</v>
       </c>
       <c r="I66" s="8">
         <v>1.07</v>
@@ -3374,7 +3371,7 @@
         <v>5.302983</v>
       </c>
       <c r="H67" s="2">
-        <v>618257.0</v>
+        <v>621432.0</v>
       </c>
       <c r="I67" s="8">
         <v>1.59</v>
@@ -3404,7 +3401,7 @@
         <v>5.400599</v>
       </c>
       <c r="H68" s="2">
-        <v>621487.0</v>
+        <v>619146.0</v>
       </c>
       <c r="I68" s="8">
         <v>0.52</v>
@@ -3434,7 +3431,7 @@
         <v>5.514984</v>
       </c>
       <c r="H69" s="2">
-        <v>621487.0</v>
+        <v>617437.0</v>
       </c>
       <c r="I69" s="8">
         <v>0.0</v>
@@ -3464,7 +3461,7 @@
         <v>5.634518</v>
       </c>
       <c r="H70" s="2">
-        <v>624716.0</v>
+        <v>628658.0</v>
       </c>
       <c r="I70" s="8">
         <v>0.52</v>
@@ -3494,7 +3491,7 @@
         <v>5.746923</v>
       </c>
       <c r="H71" s="2">
-        <v>631175.0</v>
+        <v>632061.0</v>
       </c>
       <c r="I71" s="8">
         <v>1.03</v>
@@ -3524,7 +3521,7 @@
         <v>5.851243</v>
       </c>
       <c r="H72" s="2">
-        <v>634404.0</v>
+        <v>632516.0</v>
       </c>
       <c r="I72" s="8">
         <v>0.51</v>
@@ -3554,7 +3551,7 @@
         <v>5.932659</v>
       </c>
       <c r="H73" s="2">
-        <v>640863.0</v>
+        <v>644047.0</v>
       </c>
       <c r="I73" s="8">
         <v>1.02</v>
@@ -3584,7 +3581,7 @@
         <v>5.98815</v>
       </c>
       <c r="H74" s="2">
-        <v>639223.0</v>
+        <v>643366.0</v>
       </c>
       <c r="I74" s="8">
         <v>-0.26</v>
@@ -3614,7 +3611,7 @@
         <v>6.008255</v>
       </c>
       <c r="H75" s="2">
-        <v>640863.0</v>
+        <v>634174.0</v>
       </c>
       <c r="I75" s="8">
         <v>0.26</v>
@@ -3644,7 +3641,7 @@
         <v>5.998322</v>
       </c>
       <c r="H76" s="2">
-        <v>640863.0</v>
+        <v>640860.0</v>
       </c>
       <c r="I76" s="8">
         <v>0.0</v>
@@ -3674,7 +3671,7 @@
         <v>5.960994</v>
       </c>
       <c r="H77" s="2">
-        <v>640863.0</v>
+        <v>646321.0</v>
       </c>
       <c r="I77" s="8">
         <v>0.0</v>
@@ -3704,7 +3701,7 @@
         <v>5.903246</v>
       </c>
       <c r="H78" s="2">
-        <v>640863.0</v>
+        <v>639500.0</v>
       </c>
       <c r="I78" s="8">
         <v>0.0</v>
@@ -3734,7 +3731,7 @@
         <v>5.82627</v>
       </c>
       <c r="H79" s="2">
-        <v>644093.0</v>
+        <v>641026.0</v>
       </c>
       <c r="I79" s="8">
         <v>0.5</v>
@@ -3764,7 +3761,7 @@
         <v>5.739858</v>
       </c>
       <c r="H80" s="2">
-        <v>650551.0</v>
+        <v>652209.0</v>
       </c>
       <c r="I80" s="8">
         <v>1.0</v>
@@ -3794,7 +3791,7 @@
         <v>5.643291</v>
       </c>
       <c r="H81" s="2">
-        <v>650551.0</v>
+        <v>651092.0</v>
       </c>
       <c r="I81" s="8">
         <v>0.0</v>
@@ -3824,7 +3821,7 @@
         <v>5.544457</v>
       </c>
       <c r="H82" s="2">
-        <v>653781.0</v>
+        <v>652248.0</v>
       </c>
       <c r="I82" s="8">
         <v>0.5</v>
@@ -3854,7 +3851,7 @@
         <v>5.451531</v>
       </c>
       <c r="H83" s="2">
-        <v>660240.0</v>
+        <v>656734.0</v>
       </c>
       <c r="I83" s="8">
         <v>0.99</v>
@@ -3884,7 +3881,7 @@
         <v>5.36336</v>
       </c>
       <c r="H84" s="2">
-        <v>663469.0</v>
+        <v>661001.0</v>
       </c>
       <c r="I84" s="8">
         <v>0.49</v>
@@ -3914,7 +3911,7 @@
         <v>5.290459</v>
       </c>
       <c r="H85" s="2">
-        <v>669928.0</v>
+        <v>668350.0</v>
       </c>
       <c r="I85" s="8">
         <v>0.97</v>
@@ -3944,7 +3941,7 @@
         <v>5.233011</v>
       </c>
       <c r="H86" s="2">
-        <v>679305.0</v>
+        <v>681329.0</v>
       </c>
       <c r="I86" s="8">
         <v>1.4</v>
@@ -3974,7 +3971,7 @@
         <v>5.196823</v>
       </c>
       <c r="H87" s="2">
-        <v>679616.0</v>
+        <v>675000.0</v>
       </c>
       <c r="I87" s="8">
         <v>0.05</v>
@@ -4004,7 +4001,7 @@
         <v>5.178286</v>
       </c>
       <c r="H88" s="2">
-        <v>686075.0</v>
+        <v>681216.0</v>
       </c>
       <c r="I88" s="8">
         <v>0.95</v>
@@ -4034,7 +4031,7 @@
         <v>5.166923</v>
       </c>
       <c r="H89" s="2">
-        <v>692534.0</v>
+        <v>684392.0</v>
       </c>
       <c r="I89" s="8">
         <v>0.94</v>
@@ -4064,7 +4061,7 @@
         <v>5.158653</v>
       </c>
       <c r="H90" s="2">
-        <v>692534.0</v>
+        <v>702469.0</v>
       </c>
       <c r="I90" s="8">
         <v>0.0</v>
@@ -4094,7 +4091,7 @@
         <v>5.146048</v>
       </c>
       <c r="H91" s="2">
-        <v>702222.0</v>
+        <v>703967.0</v>
       </c>
       <c r="I91" s="8">
         <v>1.4</v>
@@ -4124,7 +4121,7 @@
         <v>5.123338</v>
       </c>
       <c r="H92" s="2">
-        <v>715140.0</v>
+        <v>706337.0</v>
       </c>
       <c r="I92" s="8">
         <v>1.84</v>
@@ -4154,7 +4151,7 @@
         <v>5.082132</v>
       </c>
       <c r="H93" s="2">
-        <v>715140.0</v>
+        <v>718019.0</v>
       </c>
       <c r="I93" s="8">
         <v>0.0</v>
@@ -4184,7 +4181,7 @@
         <v>5.015908</v>
       </c>
       <c r="H94" s="2">
-        <v>721599.0</v>
+        <v>715984.0</v>
       </c>
       <c r="I94" s="8">
         <v>0.9</v>
@@ -4214,7 +4211,7 @@
         <v>4.921343</v>
       </c>
       <c r="H95" s="2">
-        <v>721599.0</v>
+        <v>718465.0</v>
       </c>
       <c r="I95" s="8">
         <v>0.0</v>
@@ -4244,7 +4241,7 @@
         <v>4.785257</v>
       </c>
       <c r="H96" s="2">
-        <v>724828.0</v>
+        <v>726523.0</v>
       </c>
       <c r="I96" s="8">
         <v>0.45</v>
@@ -4274,7 +4271,7 @@
         <v>4.609846</v>
       </c>
       <c r="H97" s="2">
-        <v>731287.0</v>
+        <v>729054.0</v>
       </c>
       <c r="I97" s="8">
         <v>0.89</v>
@@ -4304,7 +4301,7 @@
         <v>4.376541</v>
       </c>
       <c r="H98" s="2">
-        <v>722179.0</v>
+        <v>735636.0</v>
       </c>
       <c r="I98" s="8">
         <v>-1.25</v>
@@ -4334,7 +4331,7 @@
         <v>4.086958</v>
       </c>
       <c r="H99" s="2">
-        <v>737746.0</v>
+        <v>729366.0</v>
       </c>
       <c r="I99" s="8">
         <v>2.16</v>
@@ -4364,7 +4361,7 @@
         <v>3.774789</v>
       </c>
       <c r="H100" s="2">
-        <v>737746.0</v>
+        <v>738335.0</v>
       </c>
       <c r="I100" s="8">
         <v>0.0</v>
@@ -4394,7 +4391,7 @@
         <v>3.410821</v>
       </c>
       <c r="H101" s="2">
-        <v>740975.0</v>
+        <v>741084.0</v>
       </c>
       <c r="I101" s="8">
         <v>0.44</v>
@@ -4424,7 +4421,7 @@
         <v>3.042281</v>
       </c>
       <c r="H102" s="2">
-        <v>744204.0</v>
+        <v>746243.0</v>
       </c>
       <c r="I102" s="8">
         <v>0.44</v>
@@ -4454,7 +4451,7 @@
         <v>2.658831</v>
       </c>
       <c r="H103" s="2">
-        <v>744204.0</v>
+        <v>749265.0</v>
       </c>
       <c r="I103" s="8">
         <v>0.0</v>
@@ -4484,7 +4481,7 @@
         <v>2.298829</v>
       </c>
       <c r="H104" s="2">
-        <v>750663.0</v>
+        <v>754904.0</v>
       </c>
       <c r="I104" s="8">
         <v>0.87</v>
@@ -4514,7 +4511,7 @@
         <v>1.952505</v>
       </c>
       <c r="H105" s="2">
-        <v>757122.0</v>
+        <v>761986.0</v>
       </c>
       <c r="I105" s="8">
         <v>0.86</v>
@@ -4544,7 +4541,7 @@
         <v>1.646742</v>
       </c>
       <c r="H106" s="2">
-        <v>757122.0</v>
+        <v>751045.0</v>
       </c>
       <c r="I106" s="8">
         <v>0.0</v>
@@ -4574,7 +4571,7 @@
         <v>1.403233</v>
       </c>
       <c r="H107" s="2">
-        <v>757122.0</v>
+        <v>764315.0</v>
       </c>
       <c r="I107" s="8">
         <v>0.0</v>
@@ -4604,7 +4601,7 @@
         <v>1.219974</v>
       </c>
       <c r="H108" s="2">
-        <v>760351.0</v>
+        <v>765946.0</v>
       </c>
       <c r="I108" s="8">
         <v>0.43</v>
@@ -4634,7 +4631,7 @@
         <v>1.122407</v>
       </c>
       <c r="H109" s="2">
-        <v>757689.0</v>
+        <v>758049.0</v>
       </c>
       <c r="I109" s="8">
         <v>-0.35</v>
@@ -4664,7 +4661,7 @@
         <v>1.118258</v>
       </c>
       <c r="H110" s="2">
-        <v>760351.0</v>
+        <v>767633.0</v>
       </c>
       <c r="I110" s="8">
         <v>0.35</v>
@@ -4694,7 +4691,7 @@
         <v>1.221506</v>
       </c>
       <c r="H111" s="2">
-        <v>766810.0</v>
+        <v>775220.0</v>
       </c>
       <c r="I111" s="8">
         <v>0.85</v>
@@ -4724,7 +4721,7 @@
         <v>1.397252</v>
       </c>
       <c r="H112" s="2">
-        <v>776499.0</v>
+        <v>768861.0</v>
       </c>
       <c r="I112" s="8">
         <v>1.26</v>
@@ -4754,7 +4751,7 @@
         <v>1.667218</v>
       </c>
       <c r="H113" s="2">
-        <v>779728.0</v>
+        <v>788414.0</v>
       </c>
       <c r="I113" s="8">
         <v>0.42</v>
@@ -4784,7 +4781,7 @@
         <v>1.988139</v>
       </c>
       <c r="H114" s="2">
-        <v>786187.0</v>
+        <v>791162.0</v>
       </c>
       <c r="I114" s="8">
         <v>0.83</v>
@@ -4814,7 +4811,7 @@
         <v>2.364568</v>
       </c>
       <c r="H115" s="2">
-        <v>789416.0</v>
+        <v>793897.0</v>
       </c>
       <c r="I115" s="8">
         <v>0.41</v>
@@ -4844,7 +4841,7 @@
         <v>2.756095</v>
       </c>
       <c r="H116" s="2">
-        <v>795875.0</v>
+        <v>798282.0</v>
       </c>
       <c r="I116" s="8">
         <v>0.82</v>
@@ -4874,7 +4871,7 @@
         <v>3.171982</v>
       </c>
       <c r="H117" s="2">
-        <v>808793.0</v>
+        <v>814248.0</v>
       </c>
       <c r="I117" s="8">
         <v>1.62</v>
@@ -4904,7 +4901,7 @@
         <v>3.582242</v>
       </c>
       <c r="H118" s="2">
-        <v>818481.0</v>
+        <v>820584.0</v>
       </c>
       <c r="I118" s="8">
         <v>1.2</v>
@@ -4934,7 +4931,7 @@
         <v>3.957611</v>
       </c>
       <c r="H119" s="2">
-        <v>818481.0</v>
+        <v>827141.0</v>
       </c>
       <c r="I119" s="8">
         <v>0.0</v>
@@ -4964,7 +4961,7 @@
         <v>4.306272</v>
       </c>
       <c r="H120" s="2">
-        <v>821710.0</v>
+        <v>822117.0</v>
       </c>
       <c r="I120" s="8">
         <v>0.39</v>
@@ -4994,7 +4991,7 @@
         <v>4.589608</v>
       </c>
       <c r="H121" s="2">
-        <v>829422.0</v>
+        <v>831304.0</v>
       </c>
       <c r="I121" s="8">
         <v>0.94</v>
@@ -5024,7 +5021,7 @@
         <v>4.809665</v>
       </c>
       <c r="H122" s="2">
-        <v>831399.0</v>
+        <v>834530.0</v>
       </c>
       <c r="I122" s="8">
         <v>0.24</v>
@@ -5054,7 +5051,7 @@
         <v>4.943565</v>
       </c>
       <c r="H123" s="2">
-        <v>834628.0</v>
+        <v>830223.0</v>
       </c>
       <c r="I123" s="8">
         <v>0.39</v>
@@ -5084,7 +5081,7 @@
         <v>4.996209</v>
       </c>
       <c r="H124" s="2">
-        <v>841087.0</v>
+        <v>842448.0</v>
       </c>
       <c r="I124" s="8">
         <v>0.77</v>
@@ -5114,7 +5111,7 @@
         <v>4.989893</v>
       </c>
       <c r="H125" s="2">
-        <v>844316.0</v>
+        <v>841165.0</v>
       </c>
       <c r="I125" s="8">
         <v>0.38</v>
@@ -5144,7 +5141,7 @@
         <v>4.930041</v>
       </c>
       <c r="H126" s="2">
-        <v>847546.0</v>
+        <v>849960.0</v>
       </c>
       <c r="I126" s="8">
         <v>0.38</v>
@@ -5174,7 +5171,7 @@
         <v>4.824306</v>
       </c>
       <c r="H127" s="2">
-        <v>850775.0</v>
+        <v>843992.0</v>
       </c>
       <c r="I127" s="8">
         <v>0.38</v>
@@ -5204,7 +5201,7 @@
         <v>4.690651</v>
       </c>
       <c r="H128" s="2">
-        <v>854005.0</v>
+        <v>863376.0</v>
       </c>
       <c r="I128" s="8">
         <v>0.38</v>
@@ -5234,7 +5231,7 @@
         <v>4.531806</v>
       </c>
       <c r="H129" s="2">
-        <v>866922.0</v>
+        <v>867415.0</v>
       </c>
       <c r="I129" s="8">
         <v>1.51</v>
@@ -5264,7 +5261,7 @@
         <v>4.363719</v>
       </c>
       <c r="H130" s="2">
-        <v>866922.0</v>
+        <v>858717.0</v>
       </c>
       <c r="I130" s="8">
         <v>0.0</v>
@@ -5294,7 +5291,7 @@
         <v>4.20352</v>
       </c>
       <c r="H131" s="2">
-        <v>866922.0</v>
+        <v>864402.0</v>
       </c>
       <c r="I131" s="8">
         <v>0.0</v>
@@ -5324,7 +5321,7 @@
         <v>4.052168</v>
       </c>
       <c r="H132" s="2">
-        <v>870152.0</v>
+        <v>866813.0</v>
       </c>
       <c r="I132" s="8">
         <v>0.37</v>
@@ -5354,7 +5351,7 @@
         <v>3.930571</v>
       </c>
       <c r="H133" s="2">
-        <v>858752.0</v>
+        <v>865024.0</v>
       </c>
       <c r="I133" s="8">
         <v>-1.31</v>
@@ -5384,7 +5381,7 @@
         <v>3.842264</v>
       </c>
       <c r="H134" s="2">
-        <v>879840.0</v>
+        <v>881112.0</v>
       </c>
       <c r="I134" s="8">
         <v>2.46</v>
@@ -5414,7 +5411,7 @@
         <v>3.800357</v>
       </c>
       <c r="H135" s="2">
-        <v>889528.0</v>
+        <v>891466.0</v>
       </c>
       <c r="I135" s="8">
         <v>1.1</v>
@@ -5444,7 +5441,7 @@
         <v>3.798342</v>
       </c>
       <c r="H136" s="2">
-        <v>892758.0</v>
+        <v>885274.0</v>
       </c>
       <c r="I136" s="8">
         <v>0.36</v>
@@ -5474,7 +5471,7 @@
         <v>3.828086</v>
       </c>
       <c r="H137" s="2">
-        <v>892758.0</v>
+        <v>887412.0</v>
       </c>
       <c r="I137" s="8">
         <v>0.0</v>
@@ -5504,7 +5501,7 @@
         <v>3.881245</v>
       </c>
       <c r="H138" s="2">
-        <v>899216.0</v>
+        <v>906789.0</v>
       </c>
       <c r="I138" s="8">
         <v>0.72</v>
@@ -5534,7 +5531,7 @@
         <v>3.953222</v>
       </c>
       <c r="H139" s="2">
-        <v>905675.0</v>
+        <v>911094.0</v>
       </c>
       <c r="I139" s="8">
         <v>0.72</v>
@@ -5564,7 +5561,7 @@
         <v>4.031583</v>
       </c>
       <c r="H140" s="2">
-        <v>905675.0</v>
+        <v>906546.0</v>
       </c>
       <c r="I140" s="8">
         <v>0.0</v>
@@ -5594,7 +5591,7 @@
         <v>4.113413</v>
       </c>
       <c r="H141" s="2">
-        <v>908905.0</v>
+        <v>910162.0</v>
       </c>
       <c r="I141" s="8">
         <v>0.36</v>
@@ -5624,7 +5621,7 @@
         <v>4.187843</v>
       </c>
       <c r="H142" s="2">
-        <v>908905.0</v>
+        <v>903473.0</v>
       </c>
       <c r="I142" s="8">
         <v>0.0</v>
@@ -5654,7 +5651,7 @@
         <v>4.244948</v>
       </c>
       <c r="H143" s="2">
-        <v>912134.0</v>
+        <v>911162.0</v>
       </c>
       <c r="I143" s="8">
         <v>0.36</v>
@@ -5684,7 +5681,7 @@
         <v>4.280396</v>
       </c>
       <c r="H144" s="2">
-        <v>918593.0</v>
+        <v>921770.0</v>
       </c>
       <c r="I144" s="8">
         <v>0.71</v>
@@ -5714,7 +5711,7 @@
         <v>4.28411</v>
       </c>
       <c r="H145" s="2">
-        <v>916630.0</v>
+        <v>918289.0</v>
       </c>
       <c r="I145" s="8">
         <v>-0.21</v>
@@ -5744,7 +5741,7 @@
         <v>4.248199</v>
       </c>
       <c r="H146" s="2">
-        <v>918593.0</v>
+        <v>923158.0</v>
       </c>
       <c r="I146" s="8">
         <v>0.21</v>
@@ -5774,7 +5771,7 @@
         <v>4.166379</v>
       </c>
       <c r="H147" s="2">
-        <v>925052.0</v>
+        <v>926694.0</v>
       </c>
       <c r="I147" s="8">
         <v>0.7</v>
@@ -5804,7 +5801,7 @@
         <v>4.05306</v>
       </c>
       <c r="H148" s="2">
-        <v>931511.0</v>
+        <v>927933.0</v>
       </c>
       <c r="I148" s="8">
         <v>0.7</v>
@@ -5834,7 +5831,7 @@
         <v>3.9004</v>
       </c>
       <c r="H149" s="2">
-        <v>937969.0</v>
+        <v>944227.0</v>
       </c>
       <c r="I149" s="8">
         <v>0.69</v>
@@ -5864,7 +5861,7 @@
         <v>3.729228</v>
       </c>
       <c r="H150" s="2">
-        <v>941199.0</v>
+        <v>945778.0</v>
       </c>
       <c r="I150" s="8">
         <v>0.34</v>
@@ -5894,7 +5891,7 @@
         <v>3.536137</v>
       </c>
       <c r="H151" s="2">
-        <v>944428.0</v>
+        <v>937210.0</v>
       </c>
       <c r="I151" s="8">
         <v>0.34</v>
@@ -5924,7 +5921,7 @@
         <v>3.341248</v>
       </c>
       <c r="H152" s="2">
-        <v>950887.0</v>
+        <v>957526.0</v>
       </c>
       <c r="I152" s="8">
         <v>0.68</v>
@@ -5954,7 +5951,7 @@
         <v>3.139575</v>
       </c>
       <c r="H153" s="2">
-        <v>957346.0</v>
+        <v>953830.0</v>
       </c>
       <c r="I153" s="8">
         <v>0.68</v>
@@ -5984,7 +5981,7 @@
         <v>2.945747</v>
       </c>
       <c r="H154" s="2">
-        <v>960575.0</v>
+        <v>959312.0</v>
       </c>
       <c r="I154" s="8">
         <v>0.34</v>
@@ -6014,7 +6011,7 @@
         <v>2.773387</v>
       </c>
       <c r="H155" s="2">
-        <v>967034.0</v>
+        <v>957879.0</v>
       </c>
       <c r="I155" s="8">
         <v>0.67</v>
@@ -6044,7 +6041,7 @@
         <v>2.619012</v>
       </c>
       <c r="H156" s="2">
-        <v>973493.0</v>
+        <v>970551.0</v>
       </c>
       <c r="I156" s="8">
         <v>0.67</v>
@@ -6074,7 +6071,7 @@
         <v>2.500245</v>
       </c>
       <c r="H157" s="2">
-        <v>956041.0</v>
+        <v>965019.0</v>
       </c>
       <c r="I157" s="8">
         <v>-1.79</v>
@@ -6104,7 +6101,7 @@
         <v>2.417173</v>
       </c>
       <c r="H158" s="2">
-        <v>976722.0</v>
+        <v>964505.0</v>
       </c>
       <c r="I158" s="8">
         <v>2.16</v>
@@ -6134,7 +6131,7 @@
         <v>2.379982</v>
       </c>
       <c r="H159" s="2">
-        <v>979952.0</v>
+        <v>978340.0</v>
       </c>
       <c r="I159" s="8">
         <v>0.33</v>
@@ -6164,7 +6161,7 @@
         <v>2.382083</v>
       </c>
       <c r="H160" s="2">
-        <v>983181.0</v>
+        <v>991082.0</v>
       </c>
       <c r="I160" s="8">
         <v>0.33</v>
@@ -6194,7 +6191,7 @@
         <v>2.417346</v>
       </c>
       <c r="H161" s="2">
-        <v>989640.0</v>
+        <v>988279.0</v>
       </c>
       <c r="I161" s="8">
         <v>0.66</v>
@@ -6224,7 +6221,7 @@
         <v>2.477918</v>
       </c>
       <c r="H162" s="2">
-        <v>989640.0</v>
+        <v>991648.0</v>
       </c>
       <c r="I162" s="8">
         <v>0.0</v>
@@ -6254,7 +6251,7 @@
         <v>2.56088</v>
       </c>
       <c r="H163" s="2">
-        <v>992869.0</v>
+        <v>994404.0</v>
       </c>
       <c r="I163" s="8">
         <v>0.33</v>
@@ -6284,7 +6281,7 @@
         <v>2.654224</v>
       </c>
       <c r="H164" s="2">
-        <v>999328.0</v>
+        <v>991260.0</v>
       </c>
       <c r="I164" s="8">
         <v>0.65</v>
@@ -6314,7 +6311,7 @@
         <v>2.757218</v>
       </c>
       <c r="H165" s="2">
-        <v>1009016.0</v>
+        <v>1015548.0</v>
       </c>
       <c r="I165" s="8">
         <v>0.97</v>
@@ -6344,7 +6341,7 @@
         <v>2.85979</v>
       </c>
       <c r="H166" s="2">
-        <v>1012246.0</v>
+        <v>1018852.0</v>
       </c>
       <c r="I166" s="8">
         <v>0.32</v>
@@ -6374,7 +6371,7 @@
         <v>2.951921</v>
       </c>
       <c r="H167" s="2">
-        <v>1015475.0</v>
+        <v>1023288.0</v>
       </c>
       <c r="I167" s="8">
         <v>0.32</v>
@@ -6404,7 +6401,7 @@
         <v>3.032798</v>
       </c>
       <c r="H168" s="2">
-        <v>1021934.0</v>
+        <v>1012242.0</v>
       </c>
       <c r="I168" s="8">
         <v>0.64</v>
@@ -6434,7 +6431,7 @@
         <v>3.090548</v>
       </c>
       <c r="H169" s="2">
-        <v>1024427.0</v>
+        <v>1032785.0</v>
       </c>
       <c r="I169" s="8">
         <v>0.24</v>
@@ -6464,7 +6461,7 @@
         <v>3.122064</v>
       </c>
       <c r="H170" s="2">
-        <v>1034852.0</v>
+        <v>1038740.0</v>
       </c>
       <c r="I170" s="8">
         <v>1.02</v>
@@ -6494,7 +6491,7 @@
         <v>3.120277</v>
       </c>
       <c r="H171" s="2">
-        <v>1041311.0</v>
+        <v>1048656.0</v>
       </c>
       <c r="I171" s="8">
         <v>0.62</v>
@@ -6524,7 +6521,7 @@
         <v>3.093941</v>
       </c>
       <c r="H172" s="2">
-        <v>1047769.0</v>
+        <v>1038749.0</v>
       </c>
       <c r="I172" s="8">
         <v>0.62</v>
@@ -6554,7 +6551,7 @@
         <v>3.044003</v>
       </c>
       <c r="H173" s="2">
-        <v>1047769.0</v>
+        <v>1042317.0</v>
       </c>
       <c r="I173" s="8">
         <v>0.0</v>
@@ -6584,7 +6581,7 @@
         <v>2.981404</v>
       </c>
       <c r="H174" s="2">
-        <v>1050999.0</v>
+        <v>1051449.0</v>
       </c>
       <c r="I174" s="8">
         <v>0.31</v>
@@ -6614,7 +6611,7 @@
         <v>2.908937</v>
       </c>
       <c r="H175" s="2">
-        <v>1054228.0</v>
+        <v>1052980.0</v>
       </c>
       <c r="I175" s="8">
         <v>0.31</v>
@@ -6644,7 +6641,7 @@
         <v>2.837944</v>
       </c>
       <c r="H176" s="2">
-        <v>1054228.0</v>
+        <v>1047821.0</v>
       </c>
       <c r="I176" s="8">
         <v>0.0</v>
@@ -6674,7 +6671,7 @@
         <v>2.770658</v>
       </c>
       <c r="H177" s="2">
-        <v>1063917.0</v>
+        <v>1061896.0</v>
       </c>
       <c r="I177" s="8">
         <v>0.92</v>
@@ -6704,7 +6701,7 @@
         <v>2.716623</v>
       </c>
       <c r="H178" s="2">
-        <v>1073605.0</v>
+        <v>1080974.0</v>
       </c>
       <c r="I178" s="8">
         <v>0.91</v>
@@ -6734,7 +6731,7 @@
         <v>2.683688</v>
       </c>
       <c r="H179" s="2">
-        <v>1076834.0</v>
+        <v>1066625.0</v>
       </c>
       <c r="I179" s="8">
         <v>0.3</v>
@@ -6764,7 +6761,7 @@
         <v>2.676623</v>
       </c>
       <c r="H180" s="2">
-        <v>1076834.0</v>
+        <v>1069614.0</v>
       </c>
       <c r="I180" s="8">
         <v>0.0</v>
@@ -6794,7 +6791,7 @@
         <v>2.702551</v>
       </c>
       <c r="H181" s="2">
-        <v>1071364.0</v>
+        <v>1076827.0</v>
       </c>
       <c r="I181" s="8">
         <v>-0.51</v>
@@ -6824,7 +6821,7 @@
         <v>2.770166</v>
       </c>
       <c r="H182" s="2">
-        <v>1080064.0</v>
+        <v>1082787.0</v>
       </c>
       <c r="I182" s="8">
         <v>0.81</v>
@@ -6854,7 +6851,7 @@
         <v>2.8835</v>
       </c>
       <c r="H183" s="2">
-        <v>1086522.0</v>
+        <v>1084571.0</v>
       </c>
       <c r="I183" s="8">
         <v>0.6</v>
@@ -6884,7 +6881,7 @@
         <v>3.019339</v>
       </c>
       <c r="H184" s="2">
-        <v>1092981.0</v>
+        <v>1095614.0</v>
       </c>
       <c r="I184" s="8">
         <v>0.59</v>
@@ -6914,7 +6911,7 @@
         <v>3.197629</v>
       </c>
       <c r="H185" s="2">
-        <v>1092981.0</v>
+        <v>1093598.0</v>
       </c>
       <c r="I185" s="8">
         <v>0.0</v>
@@ -6944,7 +6941,7 @@
         <v>3.389016</v>
       </c>
       <c r="H186" s="2">
-        <v>1092981.0</v>
+        <v>1083496.0</v>
       </c>
       <c r="I186" s="8">
         <v>0.0</v>
@@ -6974,7 +6971,7 @@
         <v>3.596575</v>
       </c>
       <c r="H187" s="2">
-        <v>1096211.0</v>
+        <v>1088138.0</v>
       </c>
       <c r="I187" s="8">
         <v>0.3</v>
@@ -7004,7 +7001,7 @@
         <v>3.797648</v>
       </c>
       <c r="H188" s="2">
-        <v>1102670.0</v>
+        <v>1109703.0</v>
       </c>
       <c r="I188" s="8">
         <v>0.59</v>
@@ -7034,7 +7031,7 @@
         <v>3.995957</v>
       </c>
       <c r="H189" s="2">
-        <v>1109128.0</v>
+        <v>1116239.0</v>
       </c>
       <c r="I189" s="8">
         <v>0.59</v>
@@ -7064,7 +7061,7 @@
         <v>4.174802</v>
       </c>
       <c r="H190" s="2">
-        <v>1109128.0</v>
+        <v>1119979.0</v>
       </c>
       <c r="I190" s="8">
         <v>0.0</v>
@@ -7094,7 +7091,7 @@
         <v>4.319976</v>
       </c>
       <c r="H191" s="2">
-        <v>1109128.0</v>
+        <v>1116900.0</v>
       </c>
       <c r="I191" s="8">
         <v>0.0</v>
@@ -7124,7 +7121,7 @@
         <v>4.431474</v>
       </c>
       <c r="H192" s="2">
-        <v>1109128.0</v>
+        <v>1101643.0</v>
       </c>
       <c r="I192" s="8">
         <v>0.0</v>
@@ -7154,7 +7151,7 @@
         <v>4.492835</v>
       </c>
       <c r="H193" s="2">
-        <v>1109611.0</v>
+        <v>1113286.0</v>
       </c>
       <c r="I193" s="8">
         <v>0.04</v>
@@ -7162,7 +7159,7 @@
       <c r="K193" s="6"/>
     </row>
     <row r="194">
-      <c r="A194" s="11" t="s">
+      <c r="A194" s="10" t="s">
         <v>201</v>
       </c>
       <c r="B194" s="7">
@@ -7174,7 +7171,7 @@
       <c r="D194" s="2">
         <v>0.244431</v>
       </c>
-      <c r="E194" s="12">
+      <c r="E194" s="11">
         <v>8553.0</v>
       </c>
       <c r="F194" s="2">
@@ -7184,7 +7181,7 @@
         <v>4.498467</v>
       </c>
       <c r="H194" s="2">
-        <v>1112358.0</v>
+        <v>1124099.0</v>
       </c>
       <c r="I194" s="8">
         <v>0.25</v>
@@ -7192,7 +7189,7 @@
       <c r="K194" s="6"/>
     </row>
     <row r="195">
-      <c r="A195" s="11" t="s">
+      <c r="A195" s="10" t="s">
         <v>202</v>
       </c>
       <c r="B195" s="7">
@@ -7204,7 +7201,7 @@
       <c r="D195" s="2">
         <v>0.246876</v>
       </c>
-      <c r="E195" s="12">
+      <c r="E195" s="11">
         <v>8570.7</v>
       </c>
       <c r="F195" s="2">
@@ -7214,7 +7211,7 @@
         <v>4.438819</v>
       </c>
       <c r="H195" s="2">
-        <v>1122046.0</v>
+        <v>1114595.0</v>
       </c>
       <c r="I195" s="8">
         <v>0.87</v>
@@ -7222,7 +7219,7 @@
       <c r="K195" s="6"/>
     </row>
     <row r="196">
-      <c r="A196" s="11" t="s">
+      <c r="A196" s="10" t="s">
         <v>203</v>
       </c>
       <c r="B196" s="7">
@@ -7234,7 +7231,7 @@
       <c r="D196" s="2">
         <v>0.249344</v>
       </c>
-      <c r="E196" s="12">
+      <c r="E196" s="11">
         <v>10161.1</v>
       </c>
       <c r="F196" s="2">
@@ -7244,7 +7241,7 @@
         <v>4.329588</v>
       </c>
       <c r="H196" s="2">
-        <v>1125275.0</v>
+        <v>1123276.0</v>
       </c>
       <c r="I196" s="8">
         <v>0.29</v>
@@ -7252,7 +7249,7 @@
       <c r="K196" s="6"/>
     </row>
     <row r="197">
-      <c r="A197" s="11" t="s">
+      <c r="A197" s="10" t="s">
         <v>204</v>
       </c>
       <c r="B197" s="7">
@@ -7264,7 +7261,7 @@
       <c r="D197" s="2">
         <v>0.251838</v>
       </c>
-      <c r="E197" s="12">
+      <c r="E197" s="11">
         <v>8623.7</v>
       </c>
       <c r="F197" s="2">
@@ -7274,7 +7271,7 @@
         <v>4.164945</v>
       </c>
       <c r="H197" s="2">
-        <v>1131734.0</v>
+        <v>1127152.0</v>
       </c>
       <c r="I197" s="8">
         <v>0.57</v>
@@ -7282,7 +7279,7 @@
       <c r="K197" s="6"/>
     </row>
     <row r="198">
-      <c r="A198" s="11" t="s">
+      <c r="A198" s="10" t="s">
         <v>205</v>
       </c>
       <c r="B198" s="7">
@@ -7294,7 +7291,7 @@
       <c r="D198" s="2">
         <v>0.254356</v>
       </c>
-      <c r="E198" s="12">
+      <c r="E198" s="11">
         <v>8447.0</v>
       </c>
       <c r="F198" s="2">
@@ -7304,7 +7301,7 @@
         <v>3.967493</v>
       </c>
       <c r="H198" s="2">
-        <v>1134964.0</v>
+        <v>1129385.0</v>
       </c>
       <c r="I198" s="8">
         <v>0.29</v>
@@ -7312,7 +7309,7 @@
       <c r="K198" s="6"/>
     </row>
     <row r="199">
-      <c r="A199" s="11" t="s">
+      <c r="A199" s="10" t="s">
         <v>206</v>
       </c>
       <c r="B199" s="7">
@@ -7324,7 +7321,7 @@
       <c r="D199" s="2">
         <v>0.2569</v>
       </c>
-      <c r="E199" s="12">
+      <c r="E199" s="11">
         <v>8588.4</v>
       </c>
       <c r="F199" s="2">
@@ -7334,7 +7331,7 @@
         <v>3.733562</v>
       </c>
       <c r="H199" s="2">
-        <v>1144652.0</v>
+        <v>1144613.0</v>
       </c>
       <c r="I199" s="8">
         <v>0.85</v>
@@ -7342,7 +7339,7 @@
       <c r="K199" s="6"/>
     </row>
     <row r="200">
-      <c r="A200" s="11" t="s">
+      <c r="A200" s="10" t="s">
         <v>207</v>
       </c>
       <c r="B200" s="7">
@@ -7354,7 +7351,7 @@
       <c r="D200" s="2">
         <v>0.259469</v>
       </c>
-      <c r="E200" s="12">
+      <c r="E200" s="11">
         <v>9277.8</v>
       </c>
       <c r="F200" s="2">
@@ -7364,7 +7361,7 @@
         <v>3.487332</v>
       </c>
       <c r="H200" s="2">
-        <v>1151111.0</v>
+        <v>1148693.0</v>
       </c>
       <c r="I200" s="8">
         <v>0.56</v>
@@ -7372,7 +7369,7 @@
       <c r="K200" s="6"/>
     </row>
     <row r="201">
-      <c r="A201" s="11" t="s">
+      <c r="A201" s="10" t="s">
         <v>208</v>
       </c>
       <c r="B201" s="7">
@@ -7384,7 +7381,7 @@
       <c r="D201" s="2">
         <v>0.262063</v>
       </c>
-      <c r="E201" s="12">
+      <c r="E201" s="11">
         <v>9101.0</v>
       </c>
       <c r="F201" s="2">
@@ -7394,7 +7391,7 @@
         <v>3.22188</v>
       </c>
       <c r="H201" s="2">
-        <v>1151111.0</v>
+        <v>1149981.0</v>
       </c>
       <c r="I201" s="8">
         <v>0.0</v>
@@ -7402,7 +7399,7 @@
       <c r="K201" s="6"/>
     </row>
     <row r="202">
-      <c r="A202" s="11" t="s">
+      <c r="A202" s="10" t="s">
         <v>209</v>
       </c>
       <c r="B202" s="7">
@@ -7414,7 +7411,7 @@
       <c r="D202" s="2">
         <v>0.264684</v>
       </c>
-      <c r="E202" s="12">
+      <c r="E202" s="11">
         <v>9048.0</v>
       </c>
       <c r="F202" s="2">
@@ -7424,7 +7421,7 @@
         <v>2.954882</v>
       </c>
       <c r="H202" s="2">
-        <v>1160799.0</v>
+        <v>1161176.0</v>
       </c>
       <c r="I202" s="8">
         <v>0.84</v>
@@ -7432,7 +7429,7 @@
       <c r="K202" s="6"/>
     </row>
     <row r="203">
-      <c r="A203" s="11" t="s">
+      <c r="A203" s="10" t="s">
         <v>210</v>
       </c>
       <c r="B203" s="7">
@@ -7444,7 +7441,7 @@
       <c r="D203" s="2">
         <v>0.267331</v>
       </c>
-      <c r="E203" s="12">
+      <c r="E203" s="11">
         <v>9330.0</v>
       </c>
       <c r="F203" s="2">
@@ -7454,7 +7451,7 @@
         <v>2.704212</v>
       </c>
       <c r="H203" s="2">
-        <v>1164028.0</v>
+        <v>1158247.0</v>
       </c>
       <c r="I203" s="8">
         <v>0.28</v>
@@ -7462,7 +7459,7 @@
       <c r="K203" s="6"/>
     </row>
     <row r="204">
-      <c r="A204" s="11" t="s">
+      <c r="A204" s="10" t="s">
         <v>211</v>
       </c>
       <c r="B204" s="7">
@@ -7474,7 +7471,7 @@
       <c r="D204" s="2">
         <v>0.270004</v>
       </c>
-      <c r="E204" s="12">
+      <c r="E204" s="11">
         <v>9878.8</v>
       </c>
       <c r="F204" s="2">
@@ -7484,7 +7481,7 @@
         <v>2.462652</v>
       </c>
       <c r="H204" s="2">
-        <v>1167258.0</v>
+        <v>1172314.0</v>
       </c>
       <c r="I204" s="8">
         <v>0.28</v>
@@ -7492,7 +7489,7 @@
       <c r="K204" s="6"/>
     </row>
     <row r="205">
-      <c r="A205" s="11" t="s">
+      <c r="A205" s="10" t="s">
         <v>212</v>
       </c>
       <c r="B205" s="7">
@@ -7504,7 +7501,7 @@
       <c r="D205" s="2">
         <v>0.272704</v>
       </c>
-      <c r="E205" s="12">
+      <c r="E205" s="11">
         <v>9684.3</v>
       </c>
       <c r="F205" s="2">
@@ -7514,7 +7511,7 @@
         <v>2.254874</v>
       </c>
       <c r="H205" s="2">
-        <v>1165294.0</v>
+        <v>1168387.0</v>
       </c>
       <c r="I205" s="8">
         <v>-0.17</v>
@@ -7522,7 +7519,7 @@
       <c r="K205" s="6"/>
     </row>
     <row r="206">
-      <c r="A206" s="11" t="s">
+      <c r="A206" s="10" t="s">
         <v>213</v>
       </c>
       <c r="B206" s="7">
@@ -7534,7 +7531,7 @@
       <c r="D206" s="2">
         <v>0.268086</v>
       </c>
-      <c r="E206" s="12">
+      <c r="E206" s="11">
         <v>10745.0</v>
       </c>
       <c r="F206" s="2">
@@ -7544,7 +7541,7 @@
         <v>2.076518</v>
       </c>
       <c r="H206" s="2">
-        <v>1170487.0</v>
+        <v>1181504.0</v>
       </c>
       <c r="I206" s="8">
         <v>0.45</v>
@@ -7552,7 +7549,7 @@
       <c r="K206" s="6"/>
     </row>
     <row r="207">
-      <c r="A207" s="11" t="s">
+      <c r="A207" s="10" t="s">
         <v>214</v>
       </c>
       <c r="B207" s="7">
@@ -7564,7 +7561,7 @@
       <c r="D207" s="2">
         <v>0.270767</v>
       </c>
-      <c r="E207" s="12">
+      <c r="E207" s="11">
         <v>9083.3</v>
       </c>
       <c r="F207" s="2">
@@ -7574,7 +7571,7 @@
         <v>1.942481</v>
       </c>
       <c r="H207" s="2">
-        <v>1173717.0</v>
+        <v>1176012.0</v>
       </c>
       <c r="I207" s="8">
         <v>0.28</v>
@@ -7582,7 +7579,7 @@
       <c r="K207" s="6"/>
     </row>
     <row r="208">
-      <c r="A208" s="11" t="s">
+      <c r="A208" s="10" t="s">
         <v>215</v>
       </c>
       <c r="B208" s="7">
@@ -7594,7 +7591,7 @@
       <c r="D208" s="2">
         <v>0.273474</v>
       </c>
-      <c r="E208" s="12">
+      <c r="E208" s="11">
         <v>9931.8</v>
       </c>
       <c r="F208" s="2">
@@ -7604,7 +7601,7 @@
         <v>1.858218</v>
       </c>
       <c r="H208" s="2">
-        <v>1173717.0</v>
+        <v>1167033.0</v>
       </c>
       <c r="I208" s="8">
         <v>0.0</v>
@@ -7612,7 +7609,7 @@
       <c r="K208" s="6"/>
     </row>
     <row r="209">
-      <c r="A209" s="11" t="s">
+      <c r="A209" s="10" t="s">
         <v>216</v>
       </c>
       <c r="B209" s="7">
@@ -7624,7 +7621,7 @@
       <c r="D209" s="2">
         <v>0.276209</v>
       </c>
-      <c r="E209" s="12">
+      <c r="E209" s="11">
         <v>8800.5</v>
       </c>
       <c r="F209" s="2">
@@ -7634,7 +7631,7 @@
         <v>1.802079</v>
       </c>
       <c r="H209" s="2">
-        <v>1180175.0</v>
+        <v>1171833.0</v>
       </c>
       <c r="I209" s="8">
         <v>0.55</v>
@@ -7642,7 +7639,7 @@
       <c r="K209" s="6"/>
     </row>
     <row r="210">
-      <c r="A210" s="11" t="s">
+      <c r="A210" s="10" t="s">
         <v>217</v>
       </c>
       <c r="B210" s="7">
@@ -7654,7 +7651,7 @@
       <c r="D210" s="2">
         <v>0.278971</v>
       </c>
-      <c r="E210" s="12">
+      <c r="E210" s="11">
         <v>9366.2</v>
       </c>
       <c r="F210" s="2">
@@ -7664,7 +7661,7 @@
         <v>1.78137</v>
       </c>
       <c r="H210" s="2">
-        <v>1183405.0</v>
+        <v>1174552.0</v>
       </c>
       <c r="I210" s="8">
         <v>0.27</v>
@@ -7672,7 +7669,7 @@
       <c r="K210" s="6"/>
     </row>
     <row r="211">
-      <c r="A211" s="11" t="s">
+      <c r="A211" s="10" t="s">
         <v>218</v>
       </c>
       <c r="B211" s="7">
@@ -7684,7 +7681,7 @@
       <c r="D211" s="2">
         <v>0.281761</v>
       </c>
-      <c r="E211" s="12">
+      <c r="E211" s="11">
         <v>8995.0</v>
       </c>
       <c r="F211" s="2">
@@ -7694,7 +7691,7 @@
         <v>1.790912</v>
       </c>
       <c r="H211" s="2">
-        <v>1189864.0</v>
+        <v>1200978.0</v>
       </c>
       <c r="I211" s="8">
         <v>0.55</v>
@@ -7702,7 +7699,7 @@
       <c r="K211" s="6"/>
     </row>
     <row r="212">
-      <c r="A212" s="11" t="s">
+      <c r="A212" s="10" t="s">
         <v>219</v>
       </c>
       <c r="B212" s="7">
@@ -7714,7 +7711,7 @@
       <c r="D212" s="2">
         <v>0.284579</v>
       </c>
-      <c r="E212" s="12">
+      <c r="E212" s="11">
         <v>9136.4</v>
       </c>
       <c r="F212" s="2">
@@ -7724,7 +7721,7 @@
         <v>1.826454</v>
       </c>
       <c r="H212" s="2">
-        <v>1196323.0</v>
+        <v>1206231.0</v>
       </c>
       <c r="I212" s="8">
         <v>0.54</v>
@@ -7732,7 +7729,7 @@
       <c r="K212" s="6"/>
     </row>
     <row r="213">
-      <c r="A213" s="11" t="s">
+      <c r="A213" s="10" t="s">
         <v>220</v>
       </c>
       <c r="B213" s="7">
@@ -7744,7 +7741,7 @@
       <c r="D213" s="2">
         <v>0.287424</v>
       </c>
-      <c r="E213" s="12">
+      <c r="E213" s="11">
         <v>9984.9</v>
       </c>
       <c r="F213" s="2">
@@ -7754,7 +7751,7 @@
         <v>1.88657</v>
       </c>
       <c r="H213" s="2">
-        <v>1202781.0</v>
+        <v>1203512.0</v>
       </c>
       <c r="I213" s="8">
         <v>0.54</v>
@@ -7762,7 +7759,7 @@
       <c r="K213" s="6"/>
     </row>
     <row r="214">
-      <c r="A214" s="11" t="s">
+      <c r="A214" s="10" t="s">
         <v>221</v>
       </c>
       <c r="B214" s="7">
@@ -7784,7 +7781,7 @@
         <v>1.966597</v>
       </c>
       <c r="H214" s="2">
-        <v>1209240.0</v>
+        <v>1214447.0</v>
       </c>
       <c r="I214" s="8">
         <v>0.54</v>
@@ -7792,7 +7789,7 @@
       <c r="K214" s="6"/>
     </row>
     <row r="215">
-      <c r="A215" s="11" t="s">
+      <c r="A215" s="10" t="s">
         <v>222</v>
       </c>
       <c r="B215" s="7">
@@ -7814,7 +7811,7 @@
         <v>2.059326</v>
       </c>
       <c r="H215" s="2">
-        <v>1212470.0</v>
+        <v>1212273.0</v>
       </c>
       <c r="I215" s="8">
         <v>0.27</v>
@@ -7822,7 +7819,7 @@
       <c r="K215" s="6"/>
     </row>
     <row r="216">
-      <c r="A216" s="11" t="s">
+      <c r="A216" s="10" t="s">
         <v>223</v>
       </c>
       <c r="B216" s="7">
@@ -7844,7 +7841,7 @@
         <v>2.167142</v>
       </c>
       <c r="H216" s="2">
-        <v>1196066.0</v>
+        <v>1196305.0</v>
       </c>
       <c r="I216" s="8">
         <v>-1.35</v>
@@ -7852,7 +7849,7 @@
       <c r="K216" s="6"/>
     </row>
     <row r="217">
-      <c r="A217" s="11" t="s">
+      <c r="A217" s="10" t="s">
         <v>224</v>
       </c>
       <c r="B217" s="7">
@@ -7874,7 +7871,7 @@
         <v>2.279454</v>
       </c>
       <c r="H217" s="2">
-        <v>1215699.0</v>
+        <v>1219823.0</v>
       </c>
       <c r="I217" s="8">
         <v>1.64</v>
@@ -7882,7 +7879,7 @@
       <c r="K217" s="6"/>
     </row>
     <row r="218">
-      <c r="A218" s="11" t="s">
+      <c r="A218" s="10" t="s">
         <v>225</v>
       </c>
       <c r="B218" s="7">
@@ -7904,7 +7901,7 @@
         <v>2.399952</v>
       </c>
       <c r="H218" s="2">
-        <v>1218928.0</v>
+        <v>1217843.0</v>
       </c>
       <c r="I218" s="8">
         <v>0.27</v>
@@ -7912,7 +7909,7 @@
       <c r="K218" s="6"/>
     </row>
     <row r="219">
-      <c r="A219" s="11" t="s">
+      <c r="A219" s="10" t="s">
         <v>226</v>
       </c>
       <c r="B219" s="7">
@@ -7934,7 +7931,7 @@
         <v>2.520357</v>
       </c>
       <c r="H219" s="2">
-        <v>1222158.0</v>
+        <v>1226787.0</v>
       </c>
       <c r="I219" s="8">
         <v>0.26</v>
@@ -7942,7 +7939,7 @@
       <c r="K219" s="6"/>
     </row>
     <row r="220">
-      <c r="A220" s="11" t="s">
+      <c r="A220" s="10" t="s">
         <v>227</v>
       </c>
       <c r="B220" s="7">
@@ -7964,7 +7961,7 @@
         <v>2.622688</v>
       </c>
       <c r="H220" s="2">
-        <v>1228617.0</v>
+        <v>1229615.0</v>
       </c>
       <c r="I220" s="8">
         <v>0.53</v>
@@ -7972,7 +7969,7 @@
       <c r="K220" s="6"/>
     </row>
     <row r="221">
-      <c r="A221" s="11" t="s">
+      <c r="A221" s="10" t="s">
         <v>228</v>
       </c>
       <c r="B221" s="7">
@@ -7994,7 +7991,7 @@
         <v>2.721142</v>
       </c>
       <c r="H221" s="2">
-        <v>1231846.0</v>
+        <v>1232745.0</v>
       </c>
       <c r="I221" s="8">
         <v>0.26</v>
@@ -8002,7 +7999,7 @@
       <c r="K221" s="6"/>
     </row>
     <row r="222">
-      <c r="A222" s="11" t="s">
+      <c r="A222" s="10" t="s">
         <v>229</v>
       </c>
       <c r="B222" s="7">
@@ -8024,7 +8021,7 @@
         <v>2.79392</v>
       </c>
       <c r="H222" s="2">
-        <v>1238305.0</v>
+        <v>1242862.0</v>
       </c>
       <c r="I222" s="8">
         <v>0.52</v>
@@ -8032,7 +8029,7 @@
       <c r="K222" s="6"/>
     </row>
     <row r="223">
-      <c r="A223" s="11" t="s">
+      <c r="A223" s="10" t="s">
         <v>230</v>
       </c>
       <c r="B223" s="7">
@@ -8054,7 +8051,7 @@
         <v>2.8377</v>
       </c>
       <c r="H223" s="2">
-        <v>1241534.0</v>
+        <v>1244327.0</v>
       </c>
       <c r="I223" s="8">
         <v>0.26</v>
@@ -8062,7 +8059,7 @@
       <c r="K223" s="6"/>
     </row>
     <row r="224">
-      <c r="A224" s="11" t="s">
+      <c r="A224" s="10" t="s">
         <v>231</v>
       </c>
       <c r="B224" s="7">
@@ -8084,7 +8081,7 @@
         <v>2.841835</v>
       </c>
       <c r="H224" s="2">
-        <v>1241534.0</v>
+        <v>1233534.0</v>
       </c>
       <c r="I224" s="8">
         <v>0.0</v>
@@ -8092,7 +8089,7 @@
       <c r="K224" s="6"/>
     </row>
     <row r="225">
-      <c r="A225" s="11" t="s">
+      <c r="A225" s="10" t="s">
         <v>232</v>
       </c>
       <c r="B225" s="7">
@@ -8114,7 +8111,7 @@
         <v>2.798429</v>
       </c>
       <c r="H225" s="2">
-        <v>1241534.0</v>
+        <v>1235093.0</v>
       </c>
       <c r="I225" s="8">
         <v>0.0</v>
@@ -8122,7 +8119,7 @@
       <c r="K225" s="6"/>
     </row>
     <row r="226">
-      <c r="A226" s="11" t="s">
+      <c r="A226" s="10" t="s">
         <v>233</v>
       </c>
       <c r="B226" s="7">
@@ -8144,7 +8141,7 @@
         <v>2.698256</v>
       </c>
       <c r="H226" s="2">
-        <v>1241534.0</v>
+        <v>1244370.0</v>
       </c>
       <c r="I226" s="8">
         <v>0.0</v>
@@ -8152,7 +8149,7 @@
       <c r="K226" s="6"/>
     </row>
     <row r="227">
-      <c r="A227" s="11" t="s">
+      <c r="A227" s="10" t="s">
         <v>234</v>
       </c>
       <c r="B227" s="7">
@@ -8174,7 +8171,7 @@
         <v>2.539354</v>
       </c>
       <c r="H227" s="2">
-        <v>1247993.0</v>
+        <v>1250583.0</v>
       </c>
       <c r="I227" s="8">
         <v>0.52</v>
@@ -8182,7 +8179,7 @@
       <c r="K227" s="6"/>
     </row>
     <row r="228">
-      <c r="A228" s="11" t="s">
+      <c r="A228" s="10" t="s">
         <v>235</v>
       </c>
       <c r="B228" s="7">
@@ -8204,7 +8201,7 @@
         <v>2.30296</v>
       </c>
       <c r="H228" s="2">
-        <v>1240210.0</v>
+        <v>1252801.0</v>
       </c>
       <c r="I228" s="8">
         <v>-0.62</v>
@@ -8212,7 +8209,7 @@
       <c r="K228" s="6"/>
     </row>
     <row r="229">
-      <c r="A229" s="11" t="s">
+      <c r="A229" s="10" t="s">
         <v>236</v>
       </c>
       <c r="B229" s="7">
@@ -8234,7 +8231,7 @@
         <v>1.9965</v>
       </c>
       <c r="H229" s="2">
-        <v>1251223.0</v>
+        <v>1261663.0</v>
       </c>
       <c r="I229" s="8">
         <v>0.89</v>
@@ -8242,7 +8239,7 @@
       <c r="K229" s="6"/>
     </row>
     <row r="230">
-      <c r="A230" s="11" t="s">
+      <c r="A230" s="10" t="s">
         <v>237</v>
       </c>
       <c r="B230" s="7">
@@ -8264,7 +8261,7 @@
         <v>1.591372</v>
       </c>
       <c r="H230" s="2">
-        <v>1257681.0</v>
+        <v>1247770.0</v>
       </c>
       <c r="I230" s="8">
         <v>0.52</v>
@@ -8272,7 +8269,7 @@
       <c r="K230" s="6"/>
     </row>
     <row r="231">
-      <c r="A231" s="11" t="s">
+      <c r="A231" s="10" t="s">
         <v>238</v>
       </c>
       <c r="B231" s="7">
@@ -8294,7 +8291,7 @@
         <v>1.093699</v>
       </c>
       <c r="H231" s="2">
-        <v>1260911.0</v>
+        <v>1266386.0</v>
       </c>
       <c r="I231" s="8">
         <v>0.26</v>
@@ -8302,7 +8299,7 @@
       <c r="K231" s="6"/>
     </row>
     <row r="232">
-      <c r="A232" s="11" t="s">
+      <c r="A232" s="10" t="s">
         <v>239</v>
       </c>
       <c r="B232" s="7">
@@ -8324,7 +8321,7 @@
         <v>0.581065</v>
       </c>
       <c r="H232" s="2">
-        <v>1260911.0</v>
+        <v>1250084.0</v>
       </c>
       <c r="I232" s="8">
         <v>0.0</v>
@@ -8332,7 +8329,7 @@
       <c r="K232" s="6"/>
     </row>
     <row r="233">
-      <c r="A233" s="11" t="s">
+      <c r="A233" s="10" t="s">
         <v>240</v>
       </c>
       <c r="B233" s="7">
@@ -8354,7 +8351,7 @@
         <v>-0.03281</v>
       </c>
       <c r="H233" s="2">
-        <v>1264140.0</v>
+        <v>1252847.0</v>
       </c>
       <c r="I233" s="8">
         <v>0.26</v>
@@ -8362,7 +8359,7 @@
       <c r="K233" s="6"/>
     </row>
     <row r="234">
-      <c r="A234" s="11" t="s">
+      <c r="A234" s="10" t="s">
         <v>241</v>
       </c>
       <c r="B234" s="7">
@@ -8384,7 +8381,7 @@
         <v>-0.64991</v>
       </c>
       <c r="H234" s="2">
-        <v>1270599.0</v>
+        <v>1268054.0</v>
       </c>
       <c r="I234" s="8">
         <v>0.51</v>
@@ -8392,7 +8389,7 @@
       <c r="K234" s="6"/>
     </row>
     <row r="235">
-      <c r="A235" s="11" t="s">
+      <c r="A235" s="10" t="s">
         <v>242</v>
       </c>
       <c r="B235" s="7">
@@ -8414,7 +8411,7 @@
         <v>-1.28645</v>
       </c>
       <c r="H235" s="2">
-        <v>1270599.0</v>
+        <v>1365391.0</v>
       </c>
       <c r="I235" s="8">
         <v>0.0</v>
@@ -8422,7 +8419,7 @@
       <c r="K235" s="6"/>
     </row>
     <row r="236">
-      <c r="A236" s="11" t="s">
+      <c r="A236" s="10" t="s">
         <v>243</v>
       </c>
       <c r="B236" s="7">
@@ -8444,7 +8441,7 @@
         <v>-1.87753</v>
       </c>
       <c r="H236" s="2">
-        <v>1574164.0</v>
+        <v>1381284.0</v>
       </c>
       <c r="I236" s="8">
         <v>23.89</v>
@@ -8452,7 +8449,7 @@
       <c r="K236" s="6"/>
     </row>
     <row r="237">
-      <c r="A237" s="11" t="s">
+      <c r="A237" s="10" t="s">
         <v>244</v>
       </c>
       <c r="B237" s="7">
@@ -8474,7 +8471,7 @@
         <v>-2.43763</v>
       </c>
       <c r="H237" s="2">
-        <v>1270599.0</v>
+        <v>1358975.0</v>
       </c>
       <c r="I237" s="8">
         <v>-19.28</v>
@@ -8482,7 +8479,7 @@
       <c r="K237" s="6"/>
     </row>
     <row r="238">
-      <c r="A238" s="11" t="s">
+      <c r="A238" s="10" t="s">
         <v>245</v>
       </c>
       <c r="B238" s="7">
@@ -8504,7 +8501,7 @@
         <v>-2.92092</v>
       </c>
       <c r="H238" s="2">
-        <v>1270599.0</v>
+        <v>1281770.0</v>
       </c>
       <c r="I238" s="8">
         <v>0.0</v>
@@ -8512,7 +8509,7 @@
       <c r="K238" s="6"/>
     </row>
     <row r="239">
-      <c r="A239" s="11" t="s">
+      <c r="A239" s="10" t="s">
         <v>246</v>
       </c>
       <c r="B239" s="7">
@@ -8534,7 +8531,7 @@
         <v>-3.29136</v>
       </c>
       <c r="H239" s="2">
-        <v>1270599.0</v>
+        <v>1384050.0</v>
       </c>
       <c r="I239" s="8">
         <v>0.0</v>
@@ -8542,7 +8539,7 @@
       <c r="K239" s="6"/>
     </row>
     <row r="240">
-      <c r="A240" s="11" t="s">
+      <c r="A240" s="10" t="s">
         <v>247</v>
       </c>
       <c r="B240" s="7">
@@ -8564,7 +8561,7 @@
         <v>-3.54874</v>
       </c>
       <c r="H240" s="2">
-        <v>1583852.0</v>
+        <v>1362643.0</v>
       </c>
       <c r="I240" s="8">
         <v>24.65</v>
@@ -8572,7 +8569,7 @@
       <c r="K240" s="6"/>
     </row>
     <row r="241">
-      <c r="A241" s="11" t="s">
+      <c r="A241" s="10" t="s">
         <v>248</v>
       </c>
       <c r="B241" s="7">
@@ -8594,7 +8591,7 @@
         <v>-3.65262</v>
       </c>
       <c r="H241" s="2">
-        <v>1267370.0</v>
+        <v>1368648.0</v>
       </c>
       <c r="I241" s="8">
         <v>-19.98</v>
@@ -8602,7 +8599,7 @@
       <c r="K241" s="6"/>
     </row>
     <row r="242">
-      <c r="A242" s="11" t="s">
+      <c r="A242" s="10" t="s">
         <v>249</v>
       </c>
       <c r="B242" s="7">
@@ -8624,7 +8621,7 @@
         <v>-3.585</v>
       </c>
       <c r="H242" s="2">
-        <v>1256873.0</v>
+        <v>1258489.0</v>
       </c>
       <c r="I242" s="8">
         <v>-0.83</v>
@@ -8632,7 +8629,7 @@
       <c r="K242" s="6"/>
     </row>
     <row r="243">
-      <c r="A243" s="11" t="s">
+      <c r="A243" s="10" t="s">
         <v>250</v>
       </c>
       <c r="B243" s="7">
@@ -8654,7 +8651,7 @@
         <v>-3.32305</v>
       </c>
       <c r="H243" s="2">
-        <v>1267370.0</v>
+        <v>1273601.0</v>
       </c>
       <c r="I243" s="8">
         <v>0.84</v>
@@ -8662,7 +8659,7 @@
       <c r="K243" s="6"/>
     </row>
     <row r="244">
-      <c r="A244" s="11" t="s">
+      <c r="A244" s="10" t="s">
         <v>251</v>
       </c>
       <c r="B244" s="7">
@@ -8684,7 +8681,7 @@
         <v>-2.91826</v>
       </c>
       <c r="H244" s="2">
-        <v>1273829.0</v>
+        <v>1284231.0</v>
       </c>
       <c r="I244" s="8">
         <v>0.51</v>
@@ -8692,7 +8689,7 @@
       <c r="K244" s="6"/>
     </row>
     <row r="245">
-      <c r="A245" s="11" t="s">
+      <c r="A245" s="10" t="s">
         <v>252</v>
       </c>
       <c r="B245" s="7">
@@ -8714,7 +8711,7 @@
         <v>-2.34064</v>
       </c>
       <c r="H245" s="2">
-        <v>1280287.0</v>
+        <v>1284019.0</v>
       </c>
       <c r="I245" s="8">
         <v>0.51</v>
@@ -8722,7 +8719,7 @@
       <c r="K245" s="6"/>
     </row>
     <row r="246">
-      <c r="A246" s="11" t="s">
+      <c r="A246" s="10" t="s">
         <v>253</v>
       </c>
       <c r="B246" s="7">
@@ -8744,7 +8741,7 @@
         <v>-1.66422</v>
       </c>
       <c r="H246" s="2">
-        <v>1286746.0</v>
+        <v>1288275.0</v>
       </c>
       <c r="I246" s="8">
         <v>0.5</v>
@@ -8752,7 +8749,7 @@
       <c r="K246" s="6"/>
     </row>
     <row r="247">
-      <c r="A247" s="11" t="s">
+      <c r="A247" s="10" t="s">
         <v>254</v>
       </c>
       <c r="B247" s="7">
@@ -8774,7 +8771,7 @@
         <v>-0.87046</v>
       </c>
       <c r="H247" s="2">
-        <v>1302893.0</v>
+        <v>1294797.0</v>
       </c>
       <c r="I247" s="8">
         <v>1.25</v>
@@ -8782,7 +8779,7 @@
       <c r="K247" s="6"/>
     </row>
     <row r="248">
-      <c r="A248" s="11" t="s">
+      <c r="A248" s="10" t="s">
         <v>255</v>
       </c>
       <c r="B248" s="7">
@@ -8804,7 +8801,7 @@
         <v>-0.03599</v>
       </c>
       <c r="H248" s="2">
-        <v>1306123.0</v>
+        <v>1301033.0</v>
       </c>
       <c r="I248" s="8">
         <v>0.25</v>
@@ -8812,7 +8809,7 @@
       <c r="K248" s="6"/>
     </row>
     <row r="249">
-      <c r="A249" s="11" t="s">
+      <c r="A249" s="10" t="s">
         <v>256</v>
       </c>
       <c r="B249" s="7">
@@ -8834,7 +8831,7 @@
         <v>0.868259</v>
       </c>
       <c r="H249" s="2">
-        <v>1309352.0</v>
+        <v>1304026.0</v>
       </c>
       <c r="I249" s="8">
         <v>0.25</v>
@@ -8842,7 +8839,7 @@
       <c r="K249" s="6"/>
     </row>
     <row r="250">
-      <c r="A250" s="11" t="s">
+      <c r="A250" s="10" t="s">
         <v>257</v>
       </c>
       <c r="B250" s="7">
@@ -8864,7 +8861,7 @@
         <v>1.788175</v>
       </c>
       <c r="H250" s="2">
-        <v>1315811.0</v>
+        <v>1317698.0</v>
       </c>
       <c r="I250" s="8">
         <v>0.49</v>
@@ -8872,7 +8869,7 @@
       <c r="K250" s="6"/>
     </row>
     <row r="251">
-      <c r="A251" s="11" t="s">
+      <c r="A251" s="10" t="s">
         <v>258</v>
       </c>
       <c r="B251" s="7">
@@ -8894,7 +8891,7 @@
         <v>2.667629</v>
       </c>
       <c r="H251" s="2">
-        <v>1319040.0</v>
+        <v>1320618.0</v>
       </c>
       <c r="I251" s="8">
         <v>0.25</v>
@@ -8902,7 +8899,7 @@
       <c r="K251" s="6"/>
     </row>
     <row r="252">
-      <c r="A252" s="11" t="s">
+      <c r="A252" s="10" t="s">
         <v>259</v>
       </c>
       <c r="B252" s="7">
@@ -8924,7 +8921,7 @@
         <v>3.538694</v>
       </c>
       <c r="H252" s="2">
-        <v>1322270.0</v>
+        <v>1309281.0</v>
       </c>
       <c r="I252" s="8">
         <v>0.24</v>
@@ -8932,7 +8929,7 @@
       <c r="K252" s="6"/>
     </row>
     <row r="253">
-      <c r="A253" s="11" t="s">
+      <c r="A253" s="10" t="s">
         <v>260</v>
       </c>
       <c r="B253" s="7">
@@ -8954,7 +8951,7 @@
         <v>4.319751</v>
       </c>
       <c r="H253" s="2">
-        <v>1325499.0</v>
+        <v>1320176.0</v>
       </c>
       <c r="I253" s="8">
         <v>0.24</v>
@@ -8962,7 +8959,7 @@
       <c r="K253" s="6"/>
     </row>
     <row r="254">
-      <c r="A254" s="11" t="s">
+      <c r="A254" s="10" t="s">
         <v>261</v>
       </c>
       <c r="B254" s="7">
@@ -8984,7 +8981,7 @@
         <v>5.036314</v>
       </c>
       <c r="H254" s="2">
-        <v>1303389.0</v>
+        <v>1334483.0</v>
       </c>
       <c r="I254" s="8">
         <v>-1.67</v>
@@ -8992,7 +8989,7 @@
       <c r="K254" s="6"/>
     </row>
     <row r="255">
-      <c r="A255" s="11" t="s">
+      <c r="A255" s="10" t="s">
         <v>262</v>
       </c>
       <c r="B255" s="7">
@@ -9014,7 +9011,7 @@
         <v>5.639562</v>
       </c>
       <c r="H255" s="2">
-        <v>1335187.0</v>
+        <v>1315720.0</v>
       </c>
       <c r="I255" s="8">
         <v>2.44</v>
@@ -9022,7 +9019,7 @@
       <c r="K255" s="6"/>
     </row>
     <row r="256">
-      <c r="A256" s="11" t="s">
+      <c r="A256" s="10" t="s">
         <v>263</v>
       </c>
       <c r="B256" s="7">
@@ -9044,7 +9041,7 @@
         <v>6.087859</v>
       </c>
       <c r="H256" s="2">
-        <v>1338417.0</v>
+        <v>1350273.0</v>
       </c>
       <c r="I256" s="8">
         <v>0.24</v>
@@ -9052,7 +9049,7 @@
       <c r="K256" s="6"/>
     </row>
     <row r="257">
-      <c r="A257" s="11" t="s">
+      <c r="A257" s="10" t="s">
         <v>264</v>
       </c>
       <c r="B257" s="7">
@@ -9074,7 +9071,7 @@
         <v>6.483596</v>
       </c>
       <c r="H257" s="2">
-        <v>1344876.0</v>
+        <v>1341336.0</v>
       </c>
       <c r="I257" s="8">
         <v>0.48</v>
@@ -9082,7 +9079,7 @@
       <c r="K257" s="6"/>
     </row>
     <row r="258">
-      <c r="A258" s="11" t="s">
+      <c r="A258" s="10" t="s">
         <v>265</v>
       </c>
       <c r="B258" s="7">
@@ -9104,7 +9101,7 @@
         <v>6.772181</v>
       </c>
       <c r="H258" s="2">
-        <v>1348105.0</v>
+        <v>1342871.0</v>
       </c>
       <c r="I258" s="8">
         <v>0.24</v>
@@ -9112,7 +9109,7 @@
       <c r="K258" s="6"/>
     </row>
     <row r="259">
-      <c r="A259" s="11" t="s">
+      <c r="A259" s="10" t="s">
         <v>266</v>
       </c>
       <c r="B259" s="7">
@@ -9134,7 +9131,7 @@
         <v>6.979542</v>
       </c>
       <c r="H259" s="2">
-        <v>1351335.0</v>
+        <v>1356289.0</v>
       </c>
       <c r="I259" s="8">
         <v>0.24</v>
@@ -9142,7 +9139,7 @@
       <c r="K259" s="6"/>
     </row>
     <row r="260">
-      <c r="A260" s="11" t="s">
+      <c r="A260" s="10" t="s">
         <v>267</v>
       </c>
       <c r="B260" s="7">
@@ -9164,7 +9161,7 @@
         <v>7.098702</v>
       </c>
       <c r="H260" s="2">
-        <v>1357793.0</v>
+        <v>1405995.0</v>
       </c>
       <c r="I260" s="8">
         <v>0.48</v>
@@ -9172,7 +9169,7 @@
       <c r="K260" s="6"/>
     </row>
     <row r="261">
-      <c r="A261" s="11" t="s">
+      <c r="A261" s="10" t="s">
         <v>268</v>
       </c>
       <c r="B261" s="7">
@@ -9194,7 +9191,7 @@
         <v>7.144293</v>
       </c>
       <c r="H261" s="2">
-        <v>1467593.0</v>
+        <v>1395126.0</v>
       </c>
       <c r="I261" s="8">
         <v>8.09</v>
@@ -9202,7 +9199,7 @@
       <c r="K261" s="6"/>
     </row>
     <row r="262">
-      <c r="A262" s="11" t="s">
+      <c r="A262" s="10" t="s">
         <v>269</v>
       </c>
       <c r="B262" s="7">
@@ -9224,7 +9221,7 @@
         <v>7.11787</v>
       </c>
       <c r="H262" s="2">
-        <v>1367482.0</v>
+        <v>1407517.0</v>
       </c>
       <c r="I262" s="8">
         <v>-6.82</v>
@@ -9232,7 +9229,7 @@
       <c r="K262" s="6"/>
     </row>
     <row r="263">
-      <c r="A263" s="11" t="s">
+      <c r="A263" s="10" t="s">
         <v>270</v>
       </c>
       <c r="B263" s="7">
@@ -9254,7 +9251,7 @@
         <v>7.030204</v>
       </c>
       <c r="H263" s="2">
-        <v>1373940.0</v>
+        <v>1372240.0</v>
       </c>
       <c r="I263" s="8">
         <v>0.47</v>
@@ -9262,7 +9259,7 @@
       <c r="K263" s="6"/>
     </row>
     <row r="264">
-      <c r="A264" s="11" t="s">
+      <c r="A264" s="10" t="s">
         <v>271</v>
       </c>
       <c r="B264" s="7">
@@ -9284,7 +9281,7 @@
         <v>6.882139</v>
       </c>
       <c r="H264" s="2">
-        <v>1377170.0</v>
+        <v>1386393.0</v>
       </c>
       <c r="I264" s="8">
         <v>0.24</v>
@@ -9292,7 +9289,7 @@
       <c r="K264" s="6"/>
     </row>
     <row r="265">
-      <c r="A265" s="11" t="s">
+      <c r="A265" s="10" t="s">
         <v>272</v>
       </c>
       <c r="B265" s="7">
@@ -9314,7 +9311,7 @@
         <v>6.689629</v>
       </c>
       <c r="H265" s="2">
-        <v>1380399.0</v>
+        <v>1361636.0</v>
       </c>
       <c r="I265" s="8">
         <v>0.23</v>
@@ -9322,7 +9319,7 @@
       <c r="K265" s="6"/>
     </row>
     <row r="266">
-      <c r="A266" s="11" t="s">
+      <c r="A266" s="10" t="s">
         <v>273</v>
       </c>
       <c r="B266" s="7">
@@ -9344,7 +9341,7 @@
         <v>6.446529</v>
       </c>
       <c r="H266" s="2">
-        <v>1349210.0</v>
+        <v>1366449.0</v>
       </c>
       <c r="I266" s="8">
         <v>-2.26</v>
@@ -9352,7 +9349,7 @@
       <c r="K266" s="6"/>
     </row>
     <row r="267">
-      <c r="A267" s="11" t="s">
+      <c r="A267" s="10" t="s">
         <v>274</v>
       </c>
       <c r="B267" s="7">
@@ -9374,7 +9371,7 @@
         <v>6.165135</v>
       </c>
       <c r="H267" s="2">
-        <v>1399776.0</v>
+        <v>1373270.0</v>
       </c>
       <c r="I267" s="8">
         <v>3.75</v>
@@ -9382,7 +9379,7 @@
       <c r="K267" s="6"/>
     </row>
     <row r="268">
-      <c r="A268" s="11" t="s">
+      <c r="A268" s="10" t="s">
         <v>275</v>
       </c>
       <c r="B268" s="7">
@@ -9404,7 +9401,7 @@
         <v>5.882975</v>
       </c>
       <c r="H268" s="2">
-        <v>1403005.0</v>
+        <v>1414898.0</v>
       </c>
       <c r="I268" s="8">
         <v>0.23</v>
@@ -9412,7 +9409,7 @@
       <c r="K268" s="6"/>
     </row>
     <row r="269">
-      <c r="A269" s="11" t="s">
+      <c r="A269" s="10" t="s">
         <v>276</v>
       </c>
       <c r="B269" s="7">
@@ -9434,7 +9431,7 @@
         <v>5.544847</v>
       </c>
       <c r="H269" s="2">
-        <v>1412693.0</v>
+        <v>1408875.0</v>
       </c>
       <c r="I269" s="8">
         <v>0.69</v>
@@ -9442,7 +9439,7 @@
       <c r="K269" s="6"/>
     </row>
     <row r="270">
-      <c r="A270" s="11" t="s">
+      <c r="A270" s="10" t="s">
         <v>277</v>
       </c>
       <c r="B270" s="7">
@@ -9464,7 +9461,7 @@
         <v>5.197078</v>
       </c>
       <c r="H270" s="2">
-        <v>1415923.0</v>
+        <v>1413994.0</v>
       </c>
       <c r="I270" s="8">
         <v>0.23</v>
@@ -9472,7 +9469,7 @@
       <c r="K270" s="6"/>
     </row>
     <row r="271">
-      <c r="A271" s="11" t="s">
+      <c r="A271" s="10" t="s">
         <v>278</v>
       </c>
       <c r="B271" s="7">
@@ -9494,7 +9491,7 @@
         <v>4.822043</v>
       </c>
       <c r="H271" s="2">
-        <v>1425611.0</v>
+        <v>1428735.0</v>
       </c>
       <c r="I271" s="8">
         <v>0.68</v>
@@ -9502,7 +9499,7 @@
       <c r="K271" s="6"/>
     </row>
     <row r="272">
-      <c r="A272" s="11" t="s">
+      <c r="A272" s="10" t="s">
         <v>279</v>
       </c>
       <c r="B272" s="7">
@@ -9524,7 +9521,7 @@
         <v>4.449258</v>
       </c>
       <c r="H272" s="2">
-        <v>1428840.0</v>
+        <v>1420209.0</v>
       </c>
       <c r="I272" s="8">
         <v>0.23</v>
@@ -9532,7 +9529,7 @@
       <c r="K272" s="6"/>
     </row>
     <row r="273">
-      <c r="A273" s="11" t="s">
+      <c r="A273" s="10" t="s">
         <v>280</v>
       </c>
       <c r="B273" s="7">
@@ -9554,7 +9551,7 @@
         <v>4.059431</v>
       </c>
       <c r="H273" s="2">
-        <v>1415923.0</v>
+        <v>1448334.0</v>
       </c>
       <c r="I273" s="8">
         <v>-0.9</v>
@@ -9562,7 +9559,7 @@
       <c r="K273" s="6"/>
     </row>
     <row r="274">
-      <c r="A274" s="11" t="s">
+      <c r="A274" s="10" t="s">
         <v>281</v>
       </c>
       <c r="B274" s="7">
@@ -9584,7 +9581,7 @@
         <v>3.670561</v>
       </c>
       <c r="H274" s="2">
-        <v>1477282.0</v>
+        <v>1456878.0</v>
       </c>
       <c r="I274" s="8">
         <v>4.33</v>
@@ -9592,7 +9589,7 @@
       <c r="K274" s="6"/>
     </row>
     <row r="275">
-      <c r="A275" s="11" t="s">
+      <c r="A275" s="10" t="s">
         <v>282</v>
       </c>
       <c r="B275" s="7">
@@ -9614,7 +9611,7 @@
         <v>3.300526</v>
       </c>
       <c r="H275" s="2">
-        <v>1483741.0</v>
+        <v>1491665.0</v>
       </c>
       <c r="I275" s="8">
         <v>0.44</v>
@@ -9622,7 +9619,7 @@
       <c r="K275" s="6"/>
     </row>
     <row r="276">
-      <c r="A276" s="11" t="s">
+      <c r="A276" s="10" t="s">
         <v>283</v>
       </c>
       <c r="B276" s="7">
@@ -9644,7 +9641,7 @@
         <v>2.930216</v>
       </c>
       <c r="H276" s="2">
-        <v>1490199.0</v>
+        <v>1486621.0</v>
       </c>
       <c r="I276" s="8">
         <v>0.44</v>
@@ -9652,7 +9649,7 @@
       <c r="K276" s="6"/>
     </row>
     <row r="277">
-      <c r="A277" s="11" t="s">
+      <c r="A277" s="10" t="s">
         <v>284</v>
       </c>
       <c r="B277" s="7">
@@ -9674,7 +9671,7 @@
         <v>2.588843</v>
       </c>
       <c r="H277" s="2">
-        <v>1491378.0</v>
+        <v>1468570.0</v>
       </c>
       <c r="I277" s="8">
         <v>0.08</v>
@@ -9682,7 +9679,7 @@
       <c r="K277" s="6"/>
     </row>
     <row r="278">
-      <c r="A278" s="11" t="s">
+      <c r="A278" s="10" t="s">
         <v>285</v>
       </c>
       <c r="B278" s="7">
@@ -9704,7 +9701,7 @@
         <v>2.259207</v>
       </c>
       <c r="H278" s="2">
-        <v>1425653.0</v>
+        <v>1446464.0</v>
       </c>
       <c r="I278" s="8">
         <v>-4.41</v>
@@ -9712,7 +9709,7 @@
       <c r="K278" s="6"/>
     </row>
     <row r="279">
-      <c r="A279" s="11" t="s">
+      <c r="A279" s="10" t="s">
         <v>286</v>
       </c>
       <c r="B279" s="7">
@@ -9734,7 +9731,7 @@
         <v>1.958716</v>
       </c>
       <c r="H279" s="2">
-        <v>1431327.0</v>
+        <v>1439779.0</v>
       </c>
       <c r="I279" s="8">
         <v>0.4</v>
@@ -9742,7 +9739,7 @@
       <c r="K279" s="6"/>
     </row>
     <row r="280">
-      <c r="A280" s="11" t="s">
+      <c r="A280" s="10" t="s">
         <v>287</v>
       </c>
       <c r="B280" s="7">
@@ -9764,7 +9761,7 @@
         <v>1.717107</v>
       </c>
       <c r="H280" s="2">
-        <v>1436985.0</v>
+        <v>1452472.0</v>
       </c>
       <c r="I280" s="8">
         <v>0.4</v>
@@ -9772,7 +9769,7 @@
       <c r="K280" s="6"/>
     </row>
     <row r="281">
-      <c r="A281" s="11" t="s">
+      <c r="A281" s="10" t="s">
         <v>288</v>
       </c>
       <c r="B281" s="7">
@@ -9794,7 +9791,7 @@
         <v>1.487864</v>
       </c>
       <c r="H281" s="2">
-        <v>1453185.0</v>
+        <v>1469921.0</v>
       </c>
       <c r="I281" s="8">
         <v>1.13</v>
@@ -9802,7 +9799,7 @@
       <c r="K281" s="6"/>
     </row>
     <row r="282">
-      <c r="A282" s="11" t="s">
+      <c r="A282" s="10" t="s">
         <v>289</v>
       </c>
       <c r="B282" s="7">
@@ -9824,7 +9821,7 @@
         <v>1.309496</v>
       </c>
       <c r="H282" s="2">
-        <v>1483247.0</v>
+        <v>1464664.0</v>
       </c>
       <c r="I282" s="8">
         <v>2.07</v>
@@ -9832,7 +9829,7 @@
       <c r="K282" s="6"/>
     </row>
     <row r="283">
-      <c r="A283" s="11" t="s">
+      <c r="A283" s="10" t="s">
         <v>290</v>
       </c>
       <c r="B283" s="7">
@@ -9854,7 +9851,7 @@
         <v>1.175669</v>
       </c>
       <c r="H283" s="2">
-        <v>1486505.0</v>
+        <v>1472782.0</v>
       </c>
       <c r="I283" s="8">
         <v>0.22</v>
@@ -9862,7 +9859,7 @@
       <c r="K283" s="6"/>
     </row>
     <row r="284">
-      <c r="A284" s="11" t="s">
+      <c r="A284" s="10" t="s">
         <v>291</v>
       </c>
       <c r="B284" s="7">
@@ -9884,7 +9881,7 @@
         <v>1.100338</v>
       </c>
       <c r="H284" s="2">
-        <v>1492670.0</v>
+        <v>1487100.0</v>
       </c>
       <c r="I284" s="8">
         <v>0.41</v>
@@ -9892,7 +9889,7 @@
       <c r="K284" s="6"/>
     </row>
     <row r="285">
-      <c r="A285" s="11" t="s">
+      <c r="A285" s="10" t="s">
         <v>292</v>
       </c>
       <c r="B285" s="7">
@@ -9914,7 +9911,7 @@
         <v>1.08404</v>
       </c>
       <c r="H285" s="2">
-        <v>1496960.0</v>
+        <v>1497529.0</v>
       </c>
       <c r="I285" s="8">
         <v>0.29</v>
@@ -9922,7 +9919,7 @@
       <c r="K285" s="6"/>
     </row>
     <row r="286">
-      <c r="A286" s="11" t="s">
+      <c r="A286" s="10" t="s">
         <v>293</v>
       </c>
       <c r="B286" s="7">
@@ -9944,7 +9941,7 @@
         <v>1.135945</v>
       </c>
       <c r="H286" s="2">
-        <v>1544553.0</v>
+        <v>1540277.0</v>
       </c>
       <c r="I286" s="8">
         <v>3.18</v>
@@ -9952,7 +9949,7 @@
       <c r="K286" s="6"/>
     </row>
     <row r="287">
-      <c r="A287" s="11" t="s">
+      <c r="A287" s="10" t="s">
         <v>294</v>
       </c>
       <c r="B287" s="7">
@@ -9974,7 +9971,7 @@
         <v>1.256493</v>
       </c>
       <c r="H287" s="2">
-        <v>1547712.0</v>
+        <v>1545636.0</v>
       </c>
       <c r="I287" s="8">
         <v>0.2</v>
@@ -9982,7 +9979,7 @@
       <c r="K287" s="6"/>
     </row>
     <row r="288">
-      <c r="A288" s="11" t="s">
+      <c r="A288" s="10" t="s">
         <v>295</v>
       </c>
       <c r="B288" s="7">
@@ -10004,7 +10001,7 @@
         <v>1.45928</v>
       </c>
       <c r="H288" s="2">
-        <v>1556346.0</v>
+        <v>1551187.0</v>
       </c>
       <c r="I288" s="8">
         <v>0.56</v>
@@ -10012,7 +10009,7 @@
       <c r="K288" s="6"/>
     </row>
     <row r="289">
-      <c r="A289" s="11" t="s">
+      <c r="A289" s="10" t="s">
         <v>296</v>
       </c>
       <c r="B289" s="7">
@@ -10034,7 +10031,7 @@
         <v>1.736543</v>
       </c>
       <c r="H289" s="2">
-        <v>1559811.0</v>
+        <v>1569913.0</v>
       </c>
       <c r="I289" s="8">
         <v>0.22</v>
@@ -10042,7 +10039,7 @@
       <c r="K289" s="6"/>
     </row>
     <row r="290">
-      <c r="A290" s="11" t="s">
+      <c r="A290" s="10" t="s">
         <v>297</v>
       </c>
       <c r="B290" s="7">
@@ -10064,15 +10061,15 @@
         <v>2.112325</v>
       </c>
       <c r="H290" s="2">
-        <v>1569181.0</v>
+        <v>1572659.0</v>
       </c>
       <c r="I290" s="8">
         <v>0.6</v>
       </c>
-      <c r="K290" s="13"/>
+      <c r="K290" s="12"/>
     </row>
     <row r="291">
-      <c r="A291" s="11" t="s">
+      <c r="A291" s="10" t="s">
         <v>298</v>
       </c>
       <c r="B291" s="7">
@@ -10094,15 +10091,15 @@
         <v>2.110046</v>
       </c>
       <c r="H291" s="2">
-        <v>1574896.0</v>
+        <v>1567108.0</v>
       </c>
       <c r="I291" s="8">
         <v>0.36</v>
       </c>
-      <c r="K291" s="13"/>
+      <c r="K291" s="12"/>
     </row>
     <row r="292">
-      <c r="A292" s="11" t="s">
+      <c r="A292" s="10" t="s">
         <v>299</v>
       </c>
       <c r="B292" s="7">
@@ -10124,15 +10121,15 @@
         <v>2.096658</v>
       </c>
       <c r="H292" s="2">
-        <v>1580175.0</v>
+        <v>1571526.0</v>
       </c>
       <c r="I292" s="8">
         <v>0.34</v>
       </c>
-      <c r="K292" s="13"/>
+      <c r="K292" s="12"/>
     </row>
     <row r="293">
-      <c r="A293" s="11" t="s">
+      <c r="A293" s="10" t="s">
         <v>300</v>
       </c>
       <c r="B293" s="7">
@@ -10154,15 +10151,15 @@
         <v>2.087755</v>
       </c>
       <c r="H293" s="2">
-        <v>1596218.0</v>
+        <v>1589047.0</v>
       </c>
       <c r="I293" s="8">
         <v>1.02</v>
       </c>
-      <c r="K293" s="13"/>
+      <c r="K293" s="12"/>
     </row>
     <row r="294">
-      <c r="A294" s="11" t="s">
+      <c r="A294" s="10" t="s">
         <v>301</v>
       </c>
       <c r="B294" s="7">
@@ -10184,15 +10181,15 @@
         <v>2.065196</v>
       </c>
       <c r="H294" s="2">
-        <v>1625601.0</v>
+        <v>1626798.0</v>
       </c>
       <c r="I294" s="8">
         <v>1.84</v>
       </c>
-      <c r="K294" s="13"/>
+      <c r="K294" s="12"/>
     </row>
     <row r="295">
-      <c r="A295" s="11" t="s">
+      <c r="A295" s="10" t="s">
         <v>302</v>
       </c>
       <c r="B295" s="7">
@@ -10214,15 +10211,15 @@
         <v>2.068871</v>
       </c>
       <c r="H295" s="2">
-        <v>1628871.0</v>
+        <v>1631935.0</v>
       </c>
       <c r="I295" s="8">
         <v>0.2</v>
       </c>
-      <c r="K295" s="13"/>
+      <c r="K295" s="12"/>
     </row>
     <row r="296">
-      <c r="A296" s="11" t="s">
+      <c r="A296" s="10" t="s">
         <v>303</v>
       </c>
       <c r="B296" s="7">
@@ -10244,15 +10241,15 @@
         <v>2.045001</v>
       </c>
       <c r="H296" s="2">
-        <v>1634922.0</v>
+        <v>1641683.0</v>
       </c>
       <c r="I296" s="8">
         <v>0.37</v>
       </c>
-      <c r="K296" s="13"/>
+      <c r="K296" s="12"/>
     </row>
     <row r="297">
-      <c r="A297" s="11" t="s">
+      <c r="A297" s="10" t="s">
         <v>304</v>
       </c>
       <c r="B297" s="7">
@@ -10274,15 +10271,15 @@
         <v>2.030954</v>
       </c>
       <c r="H297" s="2">
-        <v>1639195.0</v>
+        <v>1642335.0</v>
       </c>
       <c r="I297" s="8">
         <v>0.26</v>
       </c>
-      <c r="K297" s="13"/>
+      <c r="K297" s="12"/>
     </row>
     <row r="298">
-      <c r="A298" s="11" t="s">
+      <c r="A298" s="10" t="s">
         <v>305</v>
       </c>
       <c r="B298" s="7">
@@ -10304,15 +10301,15 @@
         <v>2.025186</v>
       </c>
       <c r="H298" s="2">
-        <v>1685630.0</v>
+        <v>1672831.0</v>
       </c>
       <c r="I298" s="8">
         <v>2.83</v>
       </c>
-      <c r="K298" s="13"/>
+      <c r="K298" s="12"/>
     </row>
     <row r="299">
-      <c r="A299" s="11" t="s">
+      <c r="A299" s="10" t="s">
         <v>306</v>
       </c>
       <c r="B299" s="7">
@@ -10334,15 +10331,15 @@
         <v>1.999087</v>
       </c>
       <c r="H299" s="2">
-        <v>1688762.0</v>
+        <v>1694303.0</v>
       </c>
       <c r="I299" s="8">
         <v>0.19</v>
       </c>
-      <c r="K299" s="13"/>
+      <c r="K299" s="12"/>
     </row>
     <row r="300">
-      <c r="A300" s="11" t="s">
+      <c r="A300" s="10" t="s">
         <v>307</v>
       </c>
       <c r="B300" s="7">
@@ -10364,15 +10361,15 @@
         <v>1.998318</v>
       </c>
       <c r="H300" s="2">
-        <v>1696985.0</v>
+        <v>1704780.0</v>
       </c>
       <c r="I300" s="8">
         <v>0.49</v>
       </c>
-      <c r="K300" s="13"/>
+      <c r="K300" s="12"/>
     </row>
     <row r="301">
-      <c r="A301" s="11" t="s">
+      <c r="A301" s="10" t="s">
         <v>308</v>
       </c>
       <c r="B301" s="7">
@@ -10394,15 +10391,15 @@
         <v>1.99152</v>
       </c>
       <c r="H301" s="2">
-        <v>1700542.0</v>
+        <v>1687971.0</v>
       </c>
       <c r="I301" s="8">
         <v>0.21</v>
       </c>
-      <c r="K301" s="13"/>
+      <c r="K301" s="12"/>
     </row>
     <row r="302">
-      <c r="A302" s="11" t="s">
+      <c r="A302" s="10" t="s">
         <v>309</v>
       </c>
       <c r="B302" s="7">
@@ -10424,15 +10421,15 @@
         <v>1.977934</v>
       </c>
       <c r="H302" s="2">
-        <v>1709787.0</v>
+        <v>1715952.0</v>
       </c>
       <c r="I302" s="8">
         <v>0.54</v>
       </c>
-      <c r="K302" s="13"/>
+      <c r="K302" s="12"/>
     </row>
     <row r="303">
-      <c r="A303" s="11" t="s">
+      <c r="A303" s="10" t="s">
         <v>310</v>
       </c>
       <c r="B303" s="7">
@@ -10454,15 +10451,15 @@
         <v>1.958997</v>
       </c>
       <c r="H303" s="2">
-        <v>1715503.0</v>
+        <v>1700145.0</v>
       </c>
       <c r="I303" s="8">
         <v>0.33</v>
       </c>
-      <c r="K303" s="13"/>
+      <c r="K303" s="12"/>
     </row>
     <row r="304">
-      <c r="A304" s="11" t="s">
+      <c r="A304" s="10" t="s">
         <v>311</v>
       </c>
       <c r="B304" s="7">
@@ -10484,15 +10481,15 @@
         <v>1.950984</v>
       </c>
       <c r="H304" s="2">
-        <v>1720635.0</v>
+        <v>1709792.0</v>
       </c>
       <c r="I304" s="8">
         <v>0.3</v>
       </c>
-      <c r="K304" s="13"/>
+      <c r="K304" s="12"/>
     </row>
     <row r="305">
-      <c r="A305" s="11" t="s">
+      <c r="A305" s="10" t="s">
         <v>312</v>
       </c>
       <c r="B305" s="7">
@@ -10514,15 +10511,15 @@
         <v>1.920248</v>
       </c>
       <c r="H305" s="2">
-        <v>1736617.0</v>
+        <v>1729530.0</v>
       </c>
       <c r="I305" s="8">
         <v>0.93</v>
       </c>
-      <c r="K305" s="13"/>
+      <c r="K305" s="12"/>
     </row>
     <row r="306">
-      <c r="A306" s="11" t="s">
+      <c r="A306" s="10" t="s">
         <v>313</v>
       </c>
       <c r="B306" s="7">
@@ -10544,15 +10541,15 @@
         <v>1.902859</v>
       </c>
       <c r="H306" s="2">
-        <v>1765736.0</v>
+        <v>1772773.0</v>
       </c>
       <c r="I306" s="8">
         <v>1.68</v>
       </c>
-      <c r="K306" s="13"/>
+      <c r="K306" s="12"/>
     </row>
     <row r="307">
-      <c r="A307" s="11" t="s">
+      <c r="A307" s="10" t="s">
         <v>314</v>
       </c>
       <c r="B307" s="7">
@@ -10574,15 +10571,15 @@
         <v>1.89307</v>
       </c>
       <c r="H307" s="2">
-        <v>1769010.0</v>
+        <v>1775180.0</v>
       </c>
       <c r="I307" s="8">
         <v>0.19</v>
       </c>
-      <c r="K307" s="13"/>
+      <c r="K307" s="12"/>
     </row>
     <row r="308">
-      <c r="A308" s="11" t="s">
+      <c r="A308" s="10" t="s">
         <v>315</v>
       </c>
       <c r="B308" s="7">
@@ -10604,15 +10601,15 @@
         <v>1.883218</v>
       </c>
       <c r="H308" s="2">
-        <v>1775017.0</v>
+        <v>1780559.0</v>
       </c>
       <c r="I308" s="8">
         <v>0.34</v>
       </c>
-      <c r="K308" s="13"/>
+      <c r="K308" s="12"/>
     </row>
     <row r="309">
-      <c r="A309" s="11" t="s">
+      <c r="A309" s="10" t="s">
         <v>316</v>
       </c>
       <c r="B309" s="7">
@@ -10634,15 +10631,15 @@
         <v>1.880286</v>
       </c>
       <c r="H309" s="2">
-        <v>1779283.0</v>
+        <v>1788331.0</v>
       </c>
       <c r="I309" s="8">
         <v>0.24</v>
       </c>
-      <c r="K309" s="13"/>
+      <c r="K309" s="12"/>
     </row>
     <row r="310">
-      <c r="A310" s="11" t="s">
+      <c r="A310" s="10" t="s">
         <v>317</v>
       </c>
       <c r="B310" s="7">
@@ -10664,15 +10661,15 @@
         <v>1.856767</v>
       </c>
       <c r="H310" s="2">
-        <v>1825267.0</v>
+        <v>1821760.0</v>
       </c>
       <c r="I310" s="8">
         <v>2.58</v>
       </c>
-      <c r="K310" s="13"/>
+      <c r="K310" s="12"/>
     </row>
     <row r="311">
-      <c r="A311" s="11" t="s">
+      <c r="A311" s="10" t="s">
         <v>318</v>
       </c>
       <c r="B311" s="7">
@@ -10694,15 +10691,15 @@
         <v>1.834012</v>
       </c>
       <c r="H311" s="2">
-        <v>1828389.0</v>
+        <v>1827854.0</v>
       </c>
       <c r="I311" s="8">
         <v>0.17</v>
       </c>
-      <c r="K311" s="13"/>
+      <c r="K311" s="12"/>
     </row>
     <row r="312">
-      <c r="A312" s="11" t="s">
+      <c r="A312" s="10" t="s">
         <v>319</v>
       </c>
       <c r="B312" s="7">
@@ -10724,14 +10721,14 @@
         <v>1.81764</v>
       </c>
       <c r="H312" s="2">
-        <v>1836452.0</v>
+        <v>1834068.0</v>
       </c>
       <c r="I312" s="8">
         <v>0.44</v>
       </c>
     </row>
     <row r="313">
-      <c r="A313" s="11" t="s">
+      <c r="A313" s="10" t="s">
         <v>320</v>
       </c>
       <c r="B313" s="7">
@@ -10753,7 +10750,7 @@
         <v>1.805976</v>
       </c>
       <c r="H313" s="2">
-        <v>1840044.0</v>
+        <v>1826995.0</v>
       </c>
       <c r="I313" s="8">
         <v>0.2</v>
@@ -10762,12 +10759,12 @@
     <row r="314">
       <c r="A314" s="5"/>
       <c r="C314" s="7"/>
-      <c r="G314" s="14"/>
+      <c r="G314" s="13"/>
     </row>
     <row r="315">
       <c r="A315" s="5"/>
       <c r="C315" s="7"/>
-      <c r="G315" s="14"/>
+      <c r="G315" s="13"/>
     </row>
     <row r="316">
       <c r="A316" s="5"/>
@@ -10782,626 +10779,626 @@
       <c r="C318" s="7"/>
     </row>
     <row r="319">
-      <c r="A319" s="15"/>
+      <c r="A319" s="14"/>
       <c r="C319" s="7"/>
     </row>
     <row r="320">
-      <c r="A320" s="15"/>
+      <c r="A320" s="14"/>
       <c r="C320" s="7"/>
     </row>
     <row r="321">
-      <c r="A321" s="15"/>
+      <c r="A321" s="14"/>
       <c r="C321" s="7"/>
     </row>
     <row r="322">
-      <c r="A322" s="15"/>
+      <c r="A322" s="14"/>
       <c r="C322" s="7"/>
     </row>
     <row r="323">
-      <c r="A323" s="15"/>
+      <c r="A323" s="14"/>
       <c r="C323" s="7"/>
     </row>
     <row r="324">
-      <c r="A324" s="15"/>
+      <c r="A324" s="14"/>
       <c r="C324" s="7"/>
     </row>
     <row r="325">
-      <c r="A325" s="15"/>
+      <c r="A325" s="14"/>
       <c r="C325" s="7"/>
     </row>
     <row r="326">
-      <c r="A326" s="15"/>
+      <c r="A326" s="14"/>
       <c r="C326" s="7"/>
     </row>
     <row r="327">
-      <c r="A327" s="15"/>
+      <c r="A327" s="14"/>
       <c r="C327" s="7"/>
     </row>
     <row r="328">
-      <c r="A328" s="15"/>
+      <c r="A328" s="14"/>
       <c r="C328" s="7"/>
     </row>
     <row r="329">
-      <c r="A329" s="16"/>
+      <c r="A329" s="15"/>
       <c r="C329" s="7"/>
     </row>
     <row r="330">
-      <c r="A330" s="16"/>
+      <c r="A330" s="15"/>
       <c r="C330" s="7"/>
     </row>
     <row r="331">
-      <c r="A331" s="16"/>
+      <c r="A331" s="15"/>
       <c r="C331" s="7"/>
     </row>
     <row r="332">
-      <c r="A332" s="15"/>
+      <c r="A332" s="14"/>
       <c r="C332" s="7"/>
     </row>
     <row r="333">
-      <c r="A333" s="15"/>
+      <c r="A333" s="14"/>
       <c r="C333" s="7"/>
     </row>
     <row r="334">
-      <c r="A334" s="15"/>
+      <c r="A334" s="14"/>
       <c r="C334" s="7"/>
     </row>
     <row r="335">
-      <c r="A335" s="15"/>
+      <c r="A335" s="14"/>
       <c r="C335" s="7"/>
     </row>
     <row r="336">
-      <c r="A336" s="15"/>
+      <c r="A336" s="14"/>
       <c r="C336" s="7"/>
     </row>
     <row r="337">
-      <c r="A337" s="15"/>
+      <c r="A337" s="14"/>
       <c r="C337" s="7"/>
     </row>
     <row r="338">
-      <c r="A338" s="15"/>
+      <c r="A338" s="14"/>
       <c r="C338" s="7"/>
     </row>
     <row r="339">
-      <c r="A339" s="15"/>
+      <c r="A339" s="14"/>
       <c r="C339" s="7"/>
     </row>
     <row r="340">
-      <c r="A340" s="15"/>
+      <c r="A340" s="14"/>
       <c r="C340" s="7"/>
     </row>
     <row r="341">
-      <c r="A341" s="16"/>
+      <c r="A341" s="15"/>
       <c r="C341" s="7"/>
     </row>
     <row r="342">
-      <c r="A342" s="16"/>
+      <c r="A342" s="15"/>
       <c r="C342" s="7"/>
     </row>
     <row r="343">
-      <c r="A343" s="16"/>
+      <c r="A343" s="15"/>
       <c r="C343" s="7"/>
     </row>
     <row r="344">
-      <c r="A344" s="15"/>
+      <c r="A344" s="14"/>
       <c r="C344" s="7"/>
     </row>
     <row r="345">
-      <c r="A345" s="15"/>
+      <c r="A345" s="14"/>
       <c r="C345" s="7"/>
     </row>
     <row r="346">
-      <c r="A346" s="15"/>
+      <c r="A346" s="14"/>
       <c r="C346" s="7"/>
     </row>
     <row r="347">
-      <c r="A347" s="15"/>
+      <c r="A347" s="14"/>
       <c r="C347" s="7"/>
     </row>
     <row r="348">
-      <c r="A348" s="15"/>
+      <c r="A348" s="14"/>
       <c r="C348" s="7"/>
     </row>
     <row r="349">
-      <c r="A349" s="15"/>
+      <c r="A349" s="14"/>
       <c r="C349" s="7"/>
     </row>
     <row r="350">
-      <c r="A350" s="15"/>
+      <c r="A350" s="14"/>
       <c r="C350" s="7"/>
     </row>
     <row r="351">
-      <c r="A351" s="15"/>
+      <c r="A351" s="14"/>
       <c r="C351" s="7"/>
     </row>
     <row r="352">
-      <c r="A352" s="15"/>
+      <c r="A352" s="14"/>
       <c r="C352" s="7"/>
     </row>
     <row r="353">
-      <c r="A353" s="16"/>
+      <c r="A353" s="15"/>
       <c r="C353" s="7"/>
     </row>
     <row r="354">
-      <c r="A354" s="16"/>
+      <c r="A354" s="15"/>
       <c r="C354" s="7"/>
     </row>
     <row r="355">
-      <c r="A355" s="16"/>
+      <c r="A355" s="15"/>
       <c r="C355" s="7"/>
     </row>
     <row r="356">
-      <c r="A356" s="15"/>
+      <c r="A356" s="14"/>
       <c r="C356" s="7"/>
     </row>
     <row r="357">
-      <c r="A357" s="15"/>
+      <c r="A357" s="14"/>
       <c r="C357" s="7"/>
     </row>
     <row r="358">
-      <c r="A358" s="15"/>
+      <c r="A358" s="14"/>
       <c r="C358" s="7"/>
     </row>
     <row r="359">
-      <c r="A359" s="15"/>
+      <c r="A359" s="14"/>
       <c r="C359" s="7"/>
     </row>
     <row r="360">
-      <c r="A360" s="15"/>
+      <c r="A360" s="14"/>
       <c r="C360" s="7"/>
     </row>
     <row r="361">
-      <c r="A361" s="15"/>
+      <c r="A361" s="14"/>
       <c r="C361" s="7"/>
     </row>
     <row r="362">
-      <c r="A362" s="15"/>
+      <c r="A362" s="14"/>
     </row>
     <row r="363">
-      <c r="A363" s="15"/>
+      <c r="A363" s="14"/>
     </row>
     <row r="364">
-      <c r="A364" s="15"/>
+      <c r="A364" s="14"/>
     </row>
     <row r="365">
-      <c r="A365" s="16"/>
+      <c r="A365" s="15"/>
     </row>
     <row r="366">
-      <c r="A366" s="16"/>
+      <c r="A366" s="15"/>
     </row>
     <row r="367">
-      <c r="A367" s="16"/>
+      <c r="A367" s="15"/>
     </row>
     <row r="368">
-      <c r="A368" s="15"/>
+      <c r="A368" s="14"/>
     </row>
     <row r="369">
-      <c r="A369" s="15"/>
+      <c r="A369" s="14"/>
     </row>
     <row r="370">
-      <c r="A370" s="15"/>
+      <c r="A370" s="14"/>
     </row>
     <row r="371">
-      <c r="A371" s="15"/>
+      <c r="A371" s="14"/>
     </row>
     <row r="372">
-      <c r="A372" s="15"/>
+      <c r="A372" s="14"/>
     </row>
     <row r="373">
-      <c r="A373" s="15"/>
+      <c r="A373" s="14"/>
     </row>
     <row r="374">
-      <c r="A374" s="15"/>
+      <c r="A374" s="14"/>
     </row>
     <row r="375">
-      <c r="A375" s="15"/>
+      <c r="A375" s="14"/>
     </row>
     <row r="376">
-      <c r="A376" s="15"/>
+      <c r="A376" s="14"/>
     </row>
     <row r="377">
-      <c r="A377" s="16"/>
+      <c r="A377" s="15"/>
     </row>
     <row r="378">
-      <c r="A378" s="16"/>
+      <c r="A378" s="15"/>
     </row>
     <row r="379">
-      <c r="A379" s="16"/>
+      <c r="A379" s="15"/>
     </row>
     <row r="380">
-      <c r="A380" s="15"/>
+      <c r="A380" s="14"/>
     </row>
     <row r="381">
-      <c r="A381" s="15"/>
+      <c r="A381" s="14"/>
     </row>
     <row r="382">
-      <c r="A382" s="15"/>
+      <c r="A382" s="14"/>
     </row>
     <row r="383">
-      <c r="A383" s="15"/>
+      <c r="A383" s="14"/>
     </row>
     <row r="384">
-      <c r="A384" s="15"/>
+      <c r="A384" s="14"/>
     </row>
     <row r="385">
-      <c r="A385" s="15"/>
+      <c r="A385" s="14"/>
     </row>
     <row r="386">
-      <c r="A386" s="15"/>
+      <c r="A386" s="14"/>
     </row>
     <row r="387">
-      <c r="A387" s="15"/>
+      <c r="A387" s="14"/>
     </row>
     <row r="388">
-      <c r="A388" s="15"/>
+      <c r="A388" s="14"/>
     </row>
     <row r="389">
-      <c r="A389" s="16"/>
+      <c r="A389" s="15"/>
     </row>
     <row r="390">
-      <c r="A390" s="16"/>
+      <c r="A390" s="15"/>
     </row>
     <row r="391">
-      <c r="A391" s="16"/>
+      <c r="A391" s="15"/>
     </row>
     <row r="392">
-      <c r="A392" s="15"/>
+      <c r="A392" s="14"/>
     </row>
     <row r="393">
-      <c r="A393" s="15"/>
+      <c r="A393" s="14"/>
     </row>
     <row r="394">
-      <c r="A394" s="15"/>
+      <c r="A394" s="14"/>
     </row>
     <row r="395">
-      <c r="A395" s="15"/>
+      <c r="A395" s="14"/>
     </row>
     <row r="396">
-      <c r="A396" s="15"/>
+      <c r="A396" s="14"/>
     </row>
     <row r="397">
-      <c r="A397" s="15"/>
+      <c r="A397" s="14"/>
     </row>
     <row r="398">
-      <c r="A398" s="15"/>
+      <c r="A398" s="14"/>
     </row>
     <row r="399">
-      <c r="A399" s="15"/>
+      <c r="A399" s="14"/>
     </row>
     <row r="400">
-      <c r="A400" s="15"/>
+      <c r="A400" s="14"/>
     </row>
     <row r="401">
-      <c r="A401" s="16"/>
+      <c r="A401" s="15"/>
     </row>
     <row r="402">
-      <c r="A402" s="16"/>
+      <c r="A402" s="15"/>
     </row>
     <row r="403">
-      <c r="A403" s="16"/>
+      <c r="A403" s="15"/>
     </row>
     <row r="404">
-      <c r="A404" s="15"/>
+      <c r="A404" s="14"/>
     </row>
     <row r="405">
-      <c r="A405" s="15"/>
+      <c r="A405" s="14"/>
     </row>
     <row r="406">
-      <c r="A406" s="15"/>
+      <c r="A406" s="14"/>
     </row>
     <row r="407">
-      <c r="A407" s="15"/>
+      <c r="A407" s="14"/>
     </row>
     <row r="408">
-      <c r="A408" s="15"/>
+      <c r="A408" s="14"/>
     </row>
     <row r="409">
-      <c r="A409" s="15"/>
+      <c r="A409" s="14"/>
     </row>
     <row r="410">
-      <c r="A410" s="15"/>
+      <c r="A410" s="14"/>
     </row>
     <row r="411">
-      <c r="A411" s="15"/>
+      <c r="A411" s="14"/>
     </row>
     <row r="412">
-      <c r="A412" s="15"/>
+      <c r="A412" s="14"/>
     </row>
     <row r="413">
-      <c r="A413" s="16"/>
+      <c r="A413" s="15"/>
     </row>
     <row r="414">
-      <c r="A414" s="16"/>
+      <c r="A414" s="15"/>
     </row>
     <row r="415">
-      <c r="A415" s="16"/>
+      <c r="A415" s="15"/>
     </row>
     <row r="416">
-      <c r="A416" s="15"/>
+      <c r="A416" s="14"/>
     </row>
     <row r="417">
-      <c r="A417" s="15"/>
+      <c r="A417" s="14"/>
     </row>
     <row r="418">
-      <c r="A418" s="15"/>
+      <c r="A418" s="14"/>
     </row>
     <row r="419">
-      <c r="A419" s="15"/>
+      <c r="A419" s="14"/>
     </row>
     <row r="420">
-      <c r="A420" s="15"/>
+      <c r="A420" s="14"/>
     </row>
     <row r="421">
-      <c r="A421" s="15"/>
+      <c r="A421" s="14"/>
     </row>
     <row r="422">
-      <c r="A422" s="15"/>
+      <c r="A422" s="14"/>
     </row>
     <row r="423">
-      <c r="A423" s="15"/>
+      <c r="A423" s="14"/>
     </row>
     <row r="424">
-      <c r="A424" s="15"/>
+      <c r="A424" s="14"/>
     </row>
     <row r="425">
-      <c r="A425" s="16"/>
+      <c r="A425" s="15"/>
     </row>
     <row r="426">
-      <c r="A426" s="16"/>
+      <c r="A426" s="15"/>
     </row>
     <row r="427">
-      <c r="A427" s="16"/>
+      <c r="A427" s="15"/>
     </row>
     <row r="428">
-      <c r="A428" s="15"/>
+      <c r="A428" s="14"/>
     </row>
     <row r="429">
-      <c r="A429" s="15"/>
+      <c r="A429" s="14"/>
     </row>
     <row r="430">
-      <c r="A430" s="15"/>
+      <c r="A430" s="14"/>
     </row>
     <row r="431">
-      <c r="A431" s="15"/>
+      <c r="A431" s="14"/>
     </row>
     <row r="432">
-      <c r="A432" s="15"/>
+      <c r="A432" s="14"/>
     </row>
     <row r="433">
-      <c r="A433" s="15"/>
+      <c r="A433" s="14"/>
     </row>
     <row r="434">
-      <c r="A434" s="15"/>
+      <c r="A434" s="14"/>
     </row>
     <row r="435">
-      <c r="A435" s="15"/>
+      <c r="A435" s="14"/>
     </row>
     <row r="436">
-      <c r="A436" s="15"/>
+      <c r="A436" s="14"/>
     </row>
     <row r="437">
-      <c r="A437" s="16"/>
+      <c r="A437" s="15"/>
     </row>
     <row r="438">
-      <c r="A438" s="16"/>
+      <c r="A438" s="15"/>
     </row>
     <row r="439">
-      <c r="A439" s="16"/>
+      <c r="A439" s="15"/>
     </row>
     <row r="440">
-      <c r="A440" s="15"/>
+      <c r="A440" s="14"/>
     </row>
     <row r="441">
-      <c r="A441" s="15"/>
+      <c r="A441" s="14"/>
     </row>
     <row r="442">
-      <c r="A442" s="15"/>
+      <c r="A442" s="14"/>
     </row>
     <row r="443">
-      <c r="A443" s="15"/>
+      <c r="A443" s="14"/>
     </row>
     <row r="444">
-      <c r="A444" s="15"/>
+      <c r="A444" s="14"/>
     </row>
     <row r="445">
-      <c r="A445" s="15"/>
+      <c r="A445" s="14"/>
     </row>
     <row r="446">
-      <c r="A446" s="15"/>
+      <c r="A446" s="14"/>
     </row>
     <row r="447">
-      <c r="A447" s="15"/>
+      <c r="A447" s="14"/>
     </row>
     <row r="448">
-      <c r="A448" s="15"/>
+      <c r="A448" s="14"/>
     </row>
     <row r="449">
-      <c r="A449" s="16"/>
+      <c r="A449" s="15"/>
     </row>
     <row r="450">
-      <c r="A450" s="16"/>
+      <c r="A450" s="15"/>
     </row>
     <row r="451">
-      <c r="A451" s="16"/>
+      <c r="A451" s="15"/>
     </row>
     <row r="452">
-      <c r="A452" s="15"/>
+      <c r="A452" s="14"/>
     </row>
     <row r="453">
-      <c r="A453" s="15"/>
+      <c r="A453" s="14"/>
     </row>
     <row r="454">
-      <c r="A454" s="15"/>
+      <c r="A454" s="14"/>
     </row>
     <row r="455">
-      <c r="A455" s="15"/>
+      <c r="A455" s="14"/>
     </row>
     <row r="456">
-      <c r="A456" s="15"/>
+      <c r="A456" s="14"/>
     </row>
     <row r="457">
-      <c r="A457" s="15"/>
+      <c r="A457" s="14"/>
     </row>
     <row r="458">
-      <c r="A458" s="15"/>
+      <c r="A458" s="14"/>
     </row>
     <row r="459">
-      <c r="A459" s="15"/>
+      <c r="A459" s="14"/>
     </row>
     <row r="460">
-      <c r="A460" s="15"/>
+      <c r="A460" s="14"/>
     </row>
     <row r="461">
-      <c r="A461" s="16"/>
+      <c r="A461" s="15"/>
     </row>
     <row r="462">
-      <c r="A462" s="16"/>
+      <c r="A462" s="15"/>
     </row>
     <row r="463">
-      <c r="A463" s="16"/>
+      <c r="A463" s="15"/>
     </row>
     <row r="464">
-      <c r="A464" s="15"/>
+      <c r="A464" s="14"/>
     </row>
     <row r="465">
-      <c r="A465" s="15"/>
+      <c r="A465" s="14"/>
     </row>
     <row r="466">
-      <c r="A466" s="15"/>
+      <c r="A466" s="14"/>
     </row>
     <row r="467">
-      <c r="A467" s="15"/>
+      <c r="A467" s="14"/>
     </row>
     <row r="468">
-      <c r="A468" s="15"/>
+      <c r="A468" s="14"/>
     </row>
     <row r="469">
-      <c r="A469" s="15"/>
+      <c r="A469" s="14"/>
     </row>
     <row r="470">
-      <c r="A470" s="15"/>
+      <c r="A470" s="14"/>
     </row>
     <row r="471">
-      <c r="A471" s="15"/>
+      <c r="A471" s="14"/>
     </row>
     <row r="472">
-      <c r="A472" s="15"/>
+      <c r="A472" s="14"/>
     </row>
     <row r="473">
-      <c r="A473" s="16"/>
+      <c r="A473" s="15"/>
     </row>
     <row r="474">
-      <c r="A474" s="16"/>
+      <c r="A474" s="15"/>
     </row>
     <row r="475">
-      <c r="A475" s="16"/>
+      <c r="A475" s="15"/>
     </row>
     <row r="476">
-      <c r="A476" s="15"/>
+      <c r="A476" s="14"/>
     </row>
     <row r="477">
-      <c r="A477" s="15"/>
+      <c r="A477" s="14"/>
     </row>
     <row r="478">
-      <c r="A478" s="15"/>
+      <c r="A478" s="14"/>
     </row>
     <row r="479">
-      <c r="A479" s="15"/>
+      <c r="A479" s="14"/>
     </row>
     <row r="480">
-      <c r="A480" s="15"/>
+      <c r="A480" s="14"/>
     </row>
     <row r="481">
-      <c r="A481" s="15"/>
+      <c r="A481" s="14"/>
     </row>
     <row r="482">
-      <c r="A482" s="15"/>
+      <c r="A482" s="14"/>
     </row>
     <row r="483">
-      <c r="A483" s="15"/>
+      <c r="A483" s="14"/>
     </row>
     <row r="484">
-      <c r="A484" s="15"/>
+      <c r="A484" s="14"/>
     </row>
     <row r="485">
-      <c r="A485" s="16"/>
+      <c r="A485" s="15"/>
     </row>
     <row r="486">
-      <c r="A486" s="16"/>
+      <c r="A486" s="15"/>
     </row>
     <row r="487">
-      <c r="A487" s="16"/>
+      <c r="A487" s="15"/>
     </row>
     <row r="488">
-      <c r="A488" s="15"/>
+      <c r="A488" s="14"/>
     </row>
     <row r="489">
-      <c r="A489" s="15"/>
+      <c r="A489" s="14"/>
     </row>
     <row r="490">
-      <c r="A490" s="15"/>
+      <c r="A490" s="14"/>
     </row>
     <row r="491">
-      <c r="A491" s="15"/>
+      <c r="A491" s="14"/>
     </row>
     <row r="492">
-      <c r="A492" s="15"/>
+      <c r="A492" s="14"/>
     </row>
     <row r="493">
-      <c r="A493" s="15"/>
+      <c r="A493" s="14"/>
     </row>
     <row r="494">
-      <c r="A494" s="15"/>
+      <c r="A494" s="14"/>
     </row>
     <row r="495">
-      <c r="A495" s="15"/>
+      <c r="A495" s="14"/>
     </row>
     <row r="496">
-      <c r="A496" s="15"/>
+      <c r="A496" s="14"/>
     </row>
     <row r="497">
-      <c r="A497" s="16"/>
+      <c r="A497" s="15"/>
     </row>
     <row r="498">
-      <c r="A498" s="16"/>
+      <c r="A498" s="15"/>
     </row>
     <row r="499">
-      <c r="A499" s="16"/>
+      <c r="A499" s="15"/>
     </row>
     <row r="500">
-      <c r="A500" s="15"/>
+      <c r="A500" s="14"/>
     </row>
     <row r="501">
-      <c r="A501" s="15"/>
+      <c r="A501" s="14"/>
     </row>
     <row r="502">
-      <c r="A502" s="15"/>
+      <c r="A502" s="14"/>
     </row>
     <row r="503">
-      <c r="A503" s="15"/>
+      <c r="A503" s="14"/>
     </row>
     <row r="504">
-      <c r="A504" s="15"/>
+      <c r="A504" s="14"/>
     </row>
     <row r="505">
-      <c r="A505" s="15"/>
+      <c r="A505" s="14"/>
     </row>
     <row r="506">
-      <c r="A506" s="15"/>
+      <c r="A506" s="14"/>
     </row>
     <row r="507">
-      <c r="A507" s="15"/>
+      <c r="A507" s="14"/>
     </row>
     <row r="508">
-      <c r="A508" s="15"/>
+      <c r="A508" s="14"/>
     </row>
     <row r="509">
-      <c r="A509" s="16"/>
+      <c r="A509" s="15"/>
     </row>
     <row r="510">
-      <c r="A510" s="16"/>
+      <c r="A510" s="15"/>
     </row>
     <row r="511">
-      <c r="A511" s="16"/>
+      <c r="A511" s="15"/>
     </row>
     <row r="512">
       <c r="A512" s="5"/>
